--- a/Plannings 2026 S26.xlsx
+++ b/Plannings 2026 S26.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A23AA2D1-9819-4B65-9C3A-D83FC30F8B22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{A23AA2D1-9819-4B65-9C3A-D83FC30F8B22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BE77D127-EEBA-4B11-B64D-E4268FA37DEA}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="151">
   <si>
     <t>Planning des salariés du 22/06/2026 au 28/06/2026</t>
   </si>
@@ -126,9 +126,6 @@
     <t>11:45/15:00</t>
   </si>
   <si>
-    <t>10:30/17:00</t>
-  </si>
-  <si>
     <t>COMMD</t>
   </si>
   <si>
@@ -450,9 +447,6 @@
     <t>18:30/23:30</t>
   </si>
   <si>
-    <t>11:50/17:00</t>
-  </si>
-  <si>
     <t>Commercial : EDF et BetssonLeagues</t>
   </si>
   <si>
@@ -472,6 +466,15 @@
   </si>
   <si>
     <t>EDF // ANNIV // FINALES LEAGUES</t>
+  </si>
+  <si>
+    <t>10:00/17:00</t>
+  </si>
+  <si>
+    <t>11:25/18:30</t>
+  </si>
+  <si>
+    <t>10:15/17:00</t>
   </si>
 </sst>
 </file>
@@ -985,7 +988,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1021,6 +1024,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1206,6 +1212,12 @@
     <xf numFmtId="0" fontId="15" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5270,6 +5282,314 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="2241176" y="2723029"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="103" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6C7669B8-BCA5-4733-81DE-47FB25117A0D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="4391025"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="104" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{77D8CB80-1702-4EE3-9D7B-BDF49E049259}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1219200" y="4391025"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="105" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6347A111-1ED8-4B80-836E-D5F3B3359280}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1828800" y="4391025"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="106" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5B2FD599-492F-45B5-B893-DEA300AB543A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1828800" y="4772025"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="107" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4F23C95C-35F8-412F-8468-1A1B3CE82A77}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1828800" y="5153025"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="108" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{937BD91D-3F12-47A4-9079-ABF15B051E30}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3048000" y="4391025"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="109" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{931ABFC2-BA31-46B2-84CF-FFE1562B4443}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3657600" y="4391025"/>
           <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -5680,162 +6000,162 @@
       <c r="H2" s="12"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B3" s="64" t="s">
+      <c r="B3" s="65" t="s">
+        <v>141</v>
+      </c>
+      <c r="C3" s="66"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="66"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="66"/>
+      <c r="H3" s="67"/>
+    </row>
+    <row r="4" spans="1:8" s="68" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="B4" s="69" t="s">
+        <v>142</v>
+      </c>
+      <c r="C4" s="69" t="s">
         <v>143</v>
       </c>
-      <c r="C3" s="65"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="66"/>
-    </row>
-    <row r="4" spans="1:8" s="67" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="B4" s="68" t="s">
+      <c r="D4" s="69" t="s">
         <v>144</v>
       </c>
-      <c r="C4" s="68" t="s">
+      <c r="E4" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="D4" s="68" t="s">
+      <c r="F4" s="69" t="s">
         <v>146</v>
       </c>
-      <c r="E4" s="68" t="s">
+      <c r="G4" s="69" t="s">
         <v>147</v>
       </c>
-      <c r="F4" s="68" t="s">
-        <v>148</v>
-      </c>
-      <c r="G4" s="68" t="s">
-        <v>149</v>
-      </c>
-      <c r="H4" s="68" t="s">
-        <v>76</v>
+      <c r="H4" s="69" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="E5" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="F5" s="15" t="s">
+      <c r="F5" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="G5" s="15" t="s">
+      <c r="G5" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="H5" s="15" t="s">
+      <c r="H5" s="16" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="16" t="s">
+      <c r="A6" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="17"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="18"/>
-      <c r="G6" s="54" t="s">
+      <c r="B6" s="18"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="55" t="s">
         <v>12</v>
       </c>
-      <c r="H6" s="19"/>
+      <c r="H6" s="20"/>
     </row>
     <row r="7" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="20"/>
-      <c r="B7" s="21"/>
-      <c r="C7" s="22"/>
-      <c r="D7" s="22"/>
-      <c r="E7" s="22"/>
-      <c r="F7" s="22"/>
-      <c r="G7" s="57" t="s">
+      <c r="A7" s="21"/>
+      <c r="B7" s="22"/>
+      <c r="C7" s="23"/>
+      <c r="D7" s="23"/>
+      <c r="E7" s="23"/>
+      <c r="F7" s="23"/>
+      <c r="G7" s="58" t="s">
         <v>13</v>
       </c>
-      <c r="H7" s="23"/>
+      <c r="H7" s="24"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="16" t="s">
+      <c r="A8" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="18"/>
-      <c r="C8" s="18"/>
-      <c r="D8" s="41" t="s">
+      <c r="B8" s="19"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="E8" s="18"/>
-      <c r="F8" s="18"/>
-      <c r="G8" s="18"/>
-      <c r="H8" s="19"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="19"/>
+      <c r="H8" s="20"/>
     </row>
     <row r="9" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="20"/>
-      <c r="B9" s="22"/>
-      <c r="C9" s="22"/>
-      <c r="D9" s="42" t="s">
+      <c r="A9" s="21"/>
+      <c r="B9" s="23"/>
+      <c r="C9" s="23"/>
+      <c r="D9" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="E9" s="22"/>
-      <c r="F9" s="22"/>
-      <c r="G9" s="22"/>
-      <c r="H9" s="23"/>
+      <c r="E9" s="23"/>
+      <c r="F9" s="23"/>
+      <c r="G9" s="23"/>
+      <c r="H9" s="24"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="16" t="s">
+      <c r="A10" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="18" t="s">
+      <c r="C10" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D10" s="62" t="s">
+      <c r="D10" s="63" t="s">
         <v>19</v>
       </c>
-      <c r="E10" s="41" t="s">
+      <c r="E10" s="42" t="s">
         <v>20</v>
       </c>
-      <c r="F10" s="18" t="s">
+      <c r="F10" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="G10" s="18"/>
-      <c r="H10" s="19"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="20"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="24"/>
+      <c r="A11" s="25"/>
       <c r="B11" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D11" s="60" t="s">
+      <c r="D11" s="61" t="s">
         <v>23</v>
       </c>
-      <c r="E11" s="43" t="s">
+      <c r="E11" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="F11" s="58" t="s">
-        <v>138</v>
+      <c r="F11" s="59" t="s">
+        <v>137</v>
       </c>
       <c r="G11" s="1"/>
-      <c r="H11" s="25"/>
+      <c r="H11" s="26"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="24"/>
-      <c r="B12" s="59" t="s">
+      <c r="A12" s="25"/>
+      <c r="B12" s="60" t="s">
         <v>19</v>
       </c>
       <c r="C12" s="1"/>
@@ -5847,11 +6167,11 @@
       </c>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
-      <c r="H12" s="25"/>
+      <c r="H12" s="26"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="24"/>
-      <c r="B13" s="60" t="s">
+      <c r="A13" s="25"/>
+      <c r="B13" s="61" t="s">
         <v>26</v>
       </c>
       <c r="C13" s="1"/>
@@ -5863,451 +6183,447 @@
       </c>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
-      <c r="H13" s="25"/>
+      <c r="H13" s="26"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="24"/>
-      <c r="B14" s="60"/>
+      <c r="A14" s="25"/>
+      <c r="B14" s="61"/>
       <c r="C14" s="1"/>
-      <c r="D14" s="44" t="s">
+      <c r="D14" s="45" t="s">
         <v>20</v>
       </c>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
-      <c r="H14" s="25"/>
+      <c r="H14" s="26"/>
     </row>
     <row r="15" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="20"/>
-      <c r="B15" s="61"/>
-      <c r="C15" s="22"/>
-      <c r="D15" s="42" t="s">
+      <c r="A15" s="21"/>
+      <c r="B15" s="62"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="43" t="s">
         <v>29</v>
       </c>
-      <c r="E15" s="22"/>
-      <c r="F15" s="22"/>
-      <c r="G15" s="22"/>
-      <c r="H15" s="23"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="23"/>
+      <c r="G15" s="23"/>
+      <c r="H15" s="24"/>
     </row>
     <row r="16" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="26" t="s">
+      <c r="A16" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="B16" s="27"/>
-      <c r="C16" s="28"/>
-      <c r="D16" s="28"/>
-      <c r="E16" s="28"/>
-      <c r="F16" s="28"/>
-      <c r="G16" s="28"/>
-      <c r="H16" s="29"/>
+      <c r="B16" s="28"/>
+      <c r="C16" s="29"/>
+      <c r="D16" s="29"/>
+      <c r="E16" s="29"/>
+      <c r="F16" s="29"/>
+      <c r="G16" s="29"/>
+      <c r="H16" s="30"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="16" t="s">
+      <c r="A17" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="B17" s="18" t="s">
+      <c r="B17" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="C17" s="18" t="s">
+      <c r="C17" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="D17" s="18" t="s">
+      <c r="D17" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="E17" s="18" t="s">
+      <c r="E17" s="59"/>
+      <c r="F17" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="F17" s="18" t="s">
+      <c r="G17" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="G17" s="18" t="s">
+      <c r="H17" s="59"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="13"/>
+      <c r="B18" s="59" t="s">
+        <v>138</v>
+      </c>
+      <c r="C18" s="59" t="s">
+        <v>148</v>
+      </c>
+      <c r="D18" s="59" t="s">
+        <v>33</v>
+      </c>
+      <c r="E18" s="59"/>
+      <c r="F18" s="59" t="s">
+        <v>149</v>
+      </c>
+      <c r="G18" s="59" t="s">
+        <v>150</v>
+      </c>
+      <c r="H18" s="59"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="13"/>
+      <c r="B19" s="59"/>
+      <c r="C19" s="59"/>
+      <c r="D19" s="75" t="s">
+        <v>34</v>
+      </c>
+      <c r="E19" s="59"/>
+      <c r="F19" s="59"/>
+      <c r="G19" s="59"/>
+      <c r="H19" s="59"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="13"/>
+      <c r="B20" s="59"/>
+      <c r="C20" s="59"/>
+      <c r="D20" s="76" t="s">
+        <v>35</v>
+      </c>
+      <c r="E20" s="59"/>
+      <c r="F20" s="59"/>
+      <c r="G20" s="59"/>
+      <c r="H20" s="59"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="13"/>
+      <c r="B21" s="59"/>
+      <c r="C21" s="59"/>
+      <c r="D21" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="H17" s="19"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="24"/>
-      <c r="B18" s="58" t="s">
-        <v>139</v>
-      </c>
-      <c r="C18" s="58" t="s">
-        <v>142</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F18" s="58" t="s">
-        <v>139</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="H18" s="25"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="24"/>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="59" t="s">
-        <v>35</v>
-      </c>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
-      <c r="H19" s="25"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="24"/>
-      <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
-      <c r="D20" s="60" t="s">
+      <c r="E21" s="59"/>
+      <c r="F21" s="59"/>
+      <c r="G21" s="59"/>
+      <c r="H21" s="59"/>
+    </row>
+    <row r="22" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="13"/>
+      <c r="B22" s="59"/>
+      <c r="C22" s="59"/>
+      <c r="D22" s="59" t="s">
         <v>36</v>
       </c>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
-      <c r="G20" s="1"/>
-      <c r="H20" s="25"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="24"/>
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-      <c r="D21" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
-      <c r="H21" s="25"/>
-    </row>
-    <row r="22" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="20"/>
-      <c r="B22" s="22"/>
-      <c r="C22" s="22"/>
-      <c r="D22" s="22" t="s">
+      <c r="E22" s="59"/>
+      <c r="F22" s="59"/>
+      <c r="G22" s="59"/>
+      <c r="H22" s="59"/>
+    </row>
+    <row r="23" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="38" t="s">
         <v>37</v>
       </c>
-      <c r="E22" s="22"/>
-      <c r="F22" s="22"/>
-      <c r="G22" s="22"/>
-      <c r="H22" s="23"/>
-    </row>
-    <row r="23" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="37" t="s">
+      <c r="B23" s="39"/>
+      <c r="C23" s="40"/>
+      <c r="D23" s="40"/>
+      <c r="E23" s="40"/>
+      <c r="F23" s="40"/>
+      <c r="G23" s="40"/>
+      <c r="H23" s="41"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="38"/>
-      <c r="C23" s="39"/>
-      <c r="D23" s="39"/>
-      <c r="E23" s="39"/>
-      <c r="F23" s="39"/>
-      <c r="G23" s="39"/>
-      <c r="H23" s="40"/>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="16" t="s">
+      <c r="B24" s="55" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="54" t="s">
+      <c r="C24" s="55" t="s">
+        <v>39</v>
+      </c>
+      <c r="D24" s="55" t="s">
+        <v>39</v>
+      </c>
+      <c r="E24" s="55" t="s">
+        <v>39</v>
+      </c>
+      <c r="F24" s="42" t="s">
         <v>40</v>
       </c>
-      <c r="C24" s="54" t="s">
-        <v>40</v>
-      </c>
-      <c r="D24" s="54" t="s">
-        <v>40</v>
-      </c>
-      <c r="E24" s="54" t="s">
-        <v>40</v>
-      </c>
-      <c r="F24" s="41" t="s">
+      <c r="G24" s="19"/>
+      <c r="H24" s="20"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="25"/>
+      <c r="B25" s="56" t="s">
         <v>41</v>
       </c>
-      <c r="G24" s="18"/>
-      <c r="H24" s="19"/>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="24"/>
-      <c r="B25" s="55" t="s">
+      <c r="C25" s="56" t="s">
+        <v>41</v>
+      </c>
+      <c r="D25" s="56" t="s">
         <v>42</v>
       </c>
-      <c r="C25" s="55" t="s">
-        <v>42</v>
-      </c>
-      <c r="D25" s="55" t="s">
+      <c r="E25" s="56" t="s">
         <v>43</v>
       </c>
-      <c r="E25" s="55" t="s">
+      <c r="F25" s="44" t="s">
         <v>44</v>
       </c>
-      <c r="F25" s="43" t="s">
+      <c r="G25" s="1"/>
+      <c r="H25" s="26"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="25"/>
+      <c r="B26" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="G25" s="1"/>
-      <c r="H25" s="25"/>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="24"/>
-      <c r="B26" s="2" t="s">
+      <c r="C26" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C26" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D26" s="56" t="s">
-        <v>40</v>
+      <c r="D26" s="57" t="s">
+        <v>39</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F26" s="43"/>
+      <c r="F26" s="44"/>
       <c r="G26" s="1"/>
-      <c r="H26" s="25"/>
+      <c r="H26" s="26"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="24"/>
+      <c r="A27" s="25"/>
       <c r="B27" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C27" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="D27" s="56" t="s">
         <v>49</v>
       </c>
-      <c r="D27" s="55" t="s">
+      <c r="E27" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E27" s="1" t="s">
+      <c r="F27" s="44"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="26"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="25"/>
+      <c r="B28" s="57" t="s">
+        <v>39</v>
+      </c>
+      <c r="C28" s="57" t="s">
+        <v>39</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E28" s="1"/>
+      <c r="F28" s="44"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="26"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="25"/>
+      <c r="B29" s="56" t="s">
         <v>51</v>
       </c>
-      <c r="F27" s="43"/>
-      <c r="G27" s="1"/>
-      <c r="H27" s="25"/>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="24"/>
-      <c r="B28" s="56" t="s">
-        <v>40</v>
-      </c>
-      <c r="C28" s="56" t="s">
-        <v>40</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E28" s="1"/>
-      <c r="F28" s="43"/>
-      <c r="G28" s="1"/>
-      <c r="H28" s="25"/>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="24"/>
-      <c r="B29" s="55" t="s">
+      <c r="C29" s="56" t="s">
         <v>52</v>
       </c>
-      <c r="C29" s="55" t="s">
+      <c r="D29" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D29" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="E29" s="1"/>
-      <c r="F29" s="43"/>
+      <c r="F29" s="44"/>
       <c r="G29" s="1"/>
-      <c r="H29" s="25"/>
+      <c r="H29" s="26"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="24"/>
-      <c r="B30" s="55"/>
+      <c r="A30" s="25"/>
+      <c r="B30" s="56"/>
       <c r="C30" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D30" s="56" t="s">
-        <v>40</v>
+      <c r="D30" s="57" t="s">
+        <v>39</v>
       </c>
       <c r="E30" s="1"/>
-      <c r="F30" s="43"/>
+      <c r="F30" s="44"/>
       <c r="G30" s="1"/>
-      <c r="H30" s="25"/>
+      <c r="H30" s="26"/>
     </row>
     <row r="31" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="20"/>
-      <c r="B31" s="57"/>
-      <c r="C31" s="22" t="s">
+      <c r="A31" s="21"/>
+      <c r="B31" s="58"/>
+      <c r="C31" s="23" t="s">
+        <v>54</v>
+      </c>
+      <c r="D31" s="58" t="s">
         <v>55</v>
       </c>
-      <c r="D31" s="57" t="s">
+      <c r="E31" s="23"/>
+      <c r="F31" s="43"/>
+      <c r="G31" s="23"/>
+      <c r="H31" s="24"/>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="E31" s="22"/>
-      <c r="F31" s="42"/>
-      <c r="G31" s="22"/>
-      <c r="H31" s="23"/>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="16" t="s">
+      <c r="B32" s="19"/>
+      <c r="C32" s="19"/>
+      <c r="D32" s="19"/>
+      <c r="E32" s="19"/>
+      <c r="F32" s="19"/>
+      <c r="G32" s="55" t="s">
+        <v>12</v>
+      </c>
+      <c r="H32" s="20"/>
+    </row>
+    <row r="33" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="21"/>
+      <c r="B33" s="23"/>
+      <c r="C33" s="23"/>
+      <c r="D33" s="23"/>
+      <c r="E33" s="23"/>
+      <c r="F33" s="23"/>
+      <c r="G33" s="58" t="s">
+        <v>13</v>
+      </c>
+      <c r="H33" s="24"/>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="B32" s="18"/>
-      <c r="C32" s="18"/>
-      <c r="D32" s="18"/>
-      <c r="E32" s="18"/>
-      <c r="F32" s="18"/>
-      <c r="G32" s="54" t="s">
-        <v>12</v>
-      </c>
-      <c r="H32" s="19"/>
-    </row>
-    <row r="33" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="20"/>
-      <c r="B33" s="22"/>
-      <c r="C33" s="22"/>
-      <c r="D33" s="22"/>
-      <c r="E33" s="22"/>
-      <c r="F33" s="22"/>
-      <c r="G33" s="57" t="s">
-        <v>13</v>
-      </c>
-      <c r="H33" s="23"/>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="16" t="s">
+      <c r="B34" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C34" s="49" t="s">
         <v>58</v>
       </c>
-      <c r="B34" s="18" t="s">
+      <c r="D34" s="55" t="s">
+        <v>59</v>
+      </c>
+      <c r="E34" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="C34" s="48" t="s">
-        <v>59</v>
-      </c>
-      <c r="D34" s="54" t="s">
+      <c r="F34" s="19"/>
+      <c r="G34" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="H34" s="20" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" s="25"/>
+      <c r="B35" s="59" t="s">
+        <v>139</v>
+      </c>
+      <c r="C35" s="47" t="s">
         <v>60</v>
       </c>
-      <c r="E34" s="18" t="s">
-        <v>18</v>
-      </c>
-      <c r="F34" s="18"/>
-      <c r="G34" s="18" t="s">
-        <v>18</v>
-      </c>
-      <c r="H34" s="19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" s="24"/>
-      <c r="B35" s="58" t="s">
-        <v>140</v>
-      </c>
-      <c r="C35" s="46" t="s">
+      <c r="D35" s="56" t="s">
         <v>61</v>
       </c>
-      <c r="D35" s="55" t="s">
+      <c r="E35" s="1" t="s">
         <v>62</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>63</v>
       </c>
       <c r="F35" s="1"/>
       <c r="G35" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="H35" s="26" t="s">
         <v>64</v>
       </c>
-      <c r="H35" s="25" t="s">
-        <v>65</v>
-      </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="24"/>
+      <c r="A36" s="25"/>
       <c r="B36" s="1"/>
-      <c r="C36" s="46"/>
+      <c r="C36" s="47"/>
       <c r="D36" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E36" s="44" t="s">
+      <c r="E36" s="45" t="s">
         <v>15</v>
       </c>
       <c r="F36" s="1"/>
-      <c r="G36" s="44" t="s">
+      <c r="G36" s="45" t="s">
         <v>15</v>
       </c>
-      <c r="H36" s="25"/>
+      <c r="H36" s="26"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37" s="24"/>
+      <c r="A37" s="25"/>
       <c r="B37" s="1"/>
-      <c r="C37" s="46"/>
+      <c r="C37" s="47"/>
       <c r="D37" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E37" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="F37" s="1"/>
+      <c r="G37" s="44" t="s">
         <v>66</v>
       </c>
-      <c r="E37" s="43" t="s">
-        <v>37</v>
-      </c>
-      <c r="F37" s="1"/>
-      <c r="G37" s="43" t="s">
-        <v>67</v>
-      </c>
-      <c r="H37" s="25"/>
+      <c r="H37" s="26"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="24"/>
+      <c r="A38" s="25"/>
       <c r="B38" s="1"/>
-      <c r="C38" s="46"/>
-      <c r="D38" s="56" t="s">
-        <v>60</v>
-      </c>
-      <c r="E38" s="43"/>
+      <c r="C38" s="47"/>
+      <c r="D38" s="57" t="s">
+        <v>59</v>
+      </c>
+      <c r="E38" s="44"/>
       <c r="F38" s="1"/>
       <c r="G38" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="H38" s="25"/>
+      <c r="H38" s="26"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="24"/>
+      <c r="A39" s="25"/>
       <c r="B39" s="1"/>
-      <c r="C39" s="46"/>
-      <c r="D39" s="55" t="s">
-        <v>68</v>
-      </c>
-      <c r="E39" s="43"/>
+      <c r="C39" s="47"/>
+      <c r="D39" s="56" t="s">
+        <v>67</v>
+      </c>
+      <c r="E39" s="44"/>
       <c r="F39" s="1"/>
       <c r="G39" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="H39" s="25"/>
+      <c r="H39" s="26"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="24"/>
+      <c r="A40" s="25"/>
       <c r="B40" s="1"/>
-      <c r="C40" s="46"/>
-      <c r="D40" s="44" t="s">
+      <c r="C40" s="47"/>
+      <c r="D40" s="45" t="s">
+        <v>68</v>
+      </c>
+      <c r="E40" s="44"/>
+      <c r="F40" s="1"/>
+      <c r="G40" s="46" t="s">
         <v>69</v>
       </c>
-      <c r="E40" s="43"/>
-      <c r="F40" s="1"/>
-      <c r="G40" s="45" t="s">
+      <c r="H40" s="26"/>
+    </row>
+    <row r="41" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="21"/>
+      <c r="B41" s="23"/>
+      <c r="C41" s="48"/>
+      <c r="D41" s="43" t="s">
         <v>70</v>
       </c>
-      <c r="H40" s="25"/>
-    </row>
-    <row r="41" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="20"/>
-      <c r="B41" s="22"/>
-      <c r="C41" s="47"/>
-      <c r="D41" s="42" t="s">
+      <c r="E41" s="43"/>
+      <c r="F41" s="23"/>
+      <c r="G41" s="48" t="s">
         <v>71</v>
       </c>
-      <c r="E41" s="42"/>
-      <c r="F41" s="22"/>
-      <c r="G41" s="47" t="s">
+      <c r="H41" s="24"/>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" s="33" t="s">
         <v>72</v>
-      </c>
-      <c r="H41" s="23"/>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" s="32" t="s">
-        <v>73</v>
       </c>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
@@ -6317,232 +6633,232 @@
       </c>
       <c r="F42" s="1"/>
       <c r="G42" s="1"/>
-      <c r="H42" s="25"/>
+      <c r="H42" s="26"/>
     </row>
     <row r="43" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="20"/>
-      <c r="B43" s="22"/>
-      <c r="C43" s="22"/>
-      <c r="D43" s="22"/>
-      <c r="E43" s="22" t="s">
-        <v>74</v>
-      </c>
-      <c r="F43" s="22"/>
-      <c r="G43" s="22"/>
-      <c r="H43" s="23"/>
+      <c r="A43" s="21"/>
+      <c r="B43" s="23"/>
+      <c r="C43" s="23"/>
+      <c r="D43" s="23"/>
+      <c r="E43" s="23" t="s">
+        <v>73</v>
+      </c>
+      <c r="F43" s="23"/>
+      <c r="G43" s="23"/>
+      <c r="H43" s="24"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="16" t="s">
+      <c r="A44" s="17" t="s">
+        <v>134</v>
+      </c>
+      <c r="B44" s="50" t="s">
         <v>135</v>
       </c>
-      <c r="B44" s="49" t="s">
-        <v>136</v>
-      </c>
-      <c r="C44" s="18"/>
-      <c r="D44" s="18" t="s">
+      <c r="C44" s="19"/>
+      <c r="D44" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="E44" s="18"/>
-      <c r="F44" s="18"/>
-      <c r="G44" s="51" t="s">
+      <c r="E44" s="19"/>
+      <c r="F44" s="19"/>
+      <c r="G44" s="52" t="s">
+        <v>75</v>
+      </c>
+      <c r="H44" s="20"/>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" s="25"/>
+      <c r="B45" s="1" t="s">
         <v>76</v>
-      </c>
-      <c r="H44" s="19"/>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" s="24"/>
-      <c r="B45" s="1" t="s">
-        <v>77</v>
       </c>
       <c r="C45" s="1"/>
       <c r="D45" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E45" s="1"/>
       <c r="F45" s="1"/>
-      <c r="G45" s="52" t="s">
-        <v>79</v>
-      </c>
-      <c r="H45" s="25"/>
+      <c r="G45" s="53" t="s">
+        <v>78</v>
+      </c>
+      <c r="H45" s="26"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="24"/>
-      <c r="B46" s="50" t="s">
-        <v>137</v>
+      <c r="A46" s="25"/>
+      <c r="B46" s="51" t="s">
+        <v>136</v>
       </c>
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
       <c r="E46" s="1"/>
       <c r="F46" s="1"/>
-      <c r="G46" s="52"/>
-      <c r="H46" s="25"/>
+      <c r="G46" s="53"/>
+      <c r="H46" s="26"/>
     </row>
     <row r="47" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="20"/>
-      <c r="B47" s="22" t="s">
+      <c r="A47" s="21"/>
+      <c r="B47" s="23" t="s">
+        <v>79</v>
+      </c>
+      <c r="C47" s="23"/>
+      <c r="D47" s="23"/>
+      <c r="E47" s="23"/>
+      <c r="F47" s="23"/>
+      <c r="G47" s="54"/>
+      <c r="H47" s="24"/>
+    </row>
+    <row r="48" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="27" t="s">
         <v>80</v>
       </c>
-      <c r="C47" s="22"/>
-      <c r="D47" s="22"/>
-      <c r="E47" s="22"/>
-      <c r="F47" s="22"/>
-      <c r="G47" s="53"/>
-      <c r="H47" s="23"/>
-    </row>
-    <row r="48" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="26" t="s">
+      <c r="B48" s="28"/>
+      <c r="C48" s="29"/>
+      <c r="D48" s="29"/>
+      <c r="E48" s="29"/>
+      <c r="F48" s="29"/>
+      <c r="G48" s="29"/>
+      <c r="H48" s="30"/>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="B48" s="27"/>
-      <c r="C48" s="28"/>
-      <c r="D48" s="28"/>
-      <c r="E48" s="28"/>
-      <c r="F48" s="28"/>
-      <c r="G48" s="28"/>
-      <c r="H48" s="29"/>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49" s="16" t="s">
+      <c r="B49" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C49" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D49" s="19"/>
+      <c r="E49" s="19"/>
+      <c r="F49" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="G49" s="19"/>
+      <c r="H49" s="20" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="21"/>
+      <c r="B50" s="64" t="s">
+        <v>140</v>
+      </c>
+      <c r="C50" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="D50" s="23"/>
+      <c r="E50" s="23"/>
+      <c r="F50" s="23" t="s">
         <v>82</v>
       </c>
-      <c r="B49" s="18" t="s">
+      <c r="G50" s="23"/>
+      <c r="H50" s="24" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="B51" s="19"/>
+      <c r="C51" s="19"/>
+      <c r="D51" s="19"/>
+      <c r="E51" s="19"/>
+      <c r="F51" s="19"/>
+      <c r="G51" s="19"/>
+      <c r="H51" s="70" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="21"/>
+      <c r="B52" s="23"/>
+      <c r="C52" s="23"/>
+      <c r="D52" s="23"/>
+      <c r="E52" s="23"/>
+      <c r="F52" s="23"/>
+      <c r="G52" s="23"/>
+      <c r="H52" s="71" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="34" t="s">
+        <v>85</v>
+      </c>
+      <c r="B53" s="35"/>
+      <c r="C53" s="36"/>
+      <c r="D53" s="36"/>
+      <c r="E53" s="36"/>
+      <c r="F53" s="36"/>
+      <c r="G53" s="36"/>
+      <c r="H53" s="37"/>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="B54" s="19"/>
+      <c r="C54" s="49" t="s">
+        <v>58</v>
+      </c>
+      <c r="D54" s="42" t="s">
+        <v>68</v>
+      </c>
+      <c r="E54" s="19"/>
+      <c r="F54" s="19"/>
+      <c r="G54" s="49" t="s">
+        <v>58</v>
+      </c>
+      <c r="H54" s="20"/>
+    </row>
+    <row r="55" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="21"/>
+      <c r="B55" s="23"/>
+      <c r="C55" s="48" t="s">
+        <v>60</v>
+      </c>
+      <c r="D55" s="43" t="s">
+        <v>70</v>
+      </c>
+      <c r="E55" s="23"/>
+      <c r="F55" s="23"/>
+      <c r="G55" s="48" t="s">
+        <v>87</v>
+      </c>
+      <c r="H55" s="24"/>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="B56" s="19"/>
+      <c r="C56" s="19"/>
+      <c r="D56" s="19"/>
+      <c r="E56" s="19"/>
+      <c r="F56" s="19"/>
+      <c r="G56" s="52" t="s">
+        <v>75</v>
+      </c>
+      <c r="H56" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="C49" s="18" t="s">
-        <v>18</v>
-      </c>
-      <c r="D49" s="18"/>
-      <c r="E49" s="18"/>
-      <c r="F49" s="18" t="s">
-        <v>18</v>
-      </c>
-      <c r="G49" s="18"/>
-      <c r="H49" s="19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="20"/>
-      <c r="B50" s="63" t="s">
-        <v>141</v>
-      </c>
-      <c r="C50" s="22" t="s">
-        <v>78</v>
-      </c>
-      <c r="D50" s="22"/>
-      <c r="E50" s="22"/>
-      <c r="F50" s="22" t="s">
-        <v>83</v>
-      </c>
-      <c r="G50" s="22"/>
-      <c r="H50" s="23" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A51" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="B51" s="18"/>
-      <c r="C51" s="18"/>
-      <c r="D51" s="18"/>
-      <c r="E51" s="18"/>
-      <c r="F51" s="18"/>
-      <c r="G51" s="18"/>
-      <c r="H51" s="69" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="20"/>
-      <c r="B52" s="22"/>
-      <c r="C52" s="22"/>
-      <c r="D52" s="22"/>
-      <c r="E52" s="22"/>
-      <c r="F52" s="22"/>
-      <c r="G52" s="22"/>
-      <c r="H52" s="70" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="33" t="s">
-        <v>86</v>
-      </c>
-      <c r="B53" s="34"/>
-      <c r="C53" s="35"/>
-      <c r="D53" s="35"/>
-      <c r="E53" s="35"/>
-      <c r="F53" s="35"/>
-      <c r="G53" s="35"/>
-      <c r="H53" s="36"/>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A54" s="16" t="s">
-        <v>87</v>
-      </c>
-      <c r="B54" s="18"/>
-      <c r="C54" s="48" t="s">
-        <v>59</v>
-      </c>
-      <c r="D54" s="41" t="s">
-        <v>69</v>
-      </c>
-      <c r="E54" s="18"/>
-      <c r="F54" s="18"/>
-      <c r="G54" s="48" t="s">
-        <v>59</v>
-      </c>
-      <c r="H54" s="19"/>
-    </row>
-    <row r="55" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="20"/>
-      <c r="B55" s="22"/>
-      <c r="C55" s="47" t="s">
-        <v>61</v>
-      </c>
-      <c r="D55" s="42" t="s">
-        <v>71</v>
-      </c>
-      <c r="E55" s="22"/>
-      <c r="F55" s="22"/>
-      <c r="G55" s="47" t="s">
-        <v>88</v>
-      </c>
-      <c r="H55" s="23"/>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A56" s="16" t="s">
-        <v>89</v>
-      </c>
-      <c r="B56" s="18"/>
-      <c r="C56" s="18"/>
-      <c r="D56" s="18"/>
-      <c r="E56" s="18"/>
-      <c r="F56" s="18"/>
-      <c r="G56" s="51" t="s">
-        <v>76</v>
-      </c>
-      <c r="H56" s="19" t="s">
-        <v>18</v>
-      </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" s="24"/>
+      <c r="A57" s="25"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
       <c r="D57" s="1"/>
       <c r="E57" s="1"/>
       <c r="F57" s="1"/>
-      <c r="G57" s="52" t="s">
+      <c r="G57" s="53" t="s">
+        <v>89</v>
+      </c>
+      <c r="H57" s="26" t="s">
         <v>90</v>
       </c>
-      <c r="H57" s="25" t="s">
-        <v>91</v>
-      </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A58" s="24"/>
+      <c r="A58" s="25"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
       <c r="D58" s="1"/>
@@ -6551,151 +6867,151 @@
       <c r="G58" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="H58" s="71" t="s">
-        <v>76</v>
+      <c r="H58" s="72" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A59" s="24"/>
+      <c r="A59" s="25"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
       <c r="D59" s="1"/>
       <c r="E59" s="1"/>
       <c r="F59" s="1"/>
       <c r="G59" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H59" s="73" t="s">
         <v>92</v>
       </c>
-      <c r="H59" s="72" t="s">
-        <v>93</v>
-      </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A60" s="24"/>
+      <c r="A60" s="25"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
       <c r="D60" s="1"/>
       <c r="E60" s="1"/>
       <c r="F60" s="1"/>
       <c r="G60" s="1"/>
-      <c r="H60" s="31" t="s">
+      <c r="H60" s="32" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61" s="24"/>
+      <c r="A61" s="25"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
       <c r="D61" s="1"/>
       <c r="E61" s="1"/>
       <c r="F61" s="1"/>
       <c r="G61" s="1"/>
-      <c r="H61" s="25" t="s">
-        <v>94</v>
+      <c r="H61" s="26" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A62" s="24"/>
+      <c r="A62" s="25"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
       <c r="D62" s="1"/>
       <c r="E62" s="1"/>
       <c r="F62" s="1"/>
       <c r="G62" s="1"/>
-      <c r="H62" s="31" t="s">
+      <c r="H62" s="32" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A63" s="24"/>
+      <c r="A63" s="25"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
       <c r="D63" s="1"/>
       <c r="E63" s="1"/>
       <c r="F63" s="1"/>
       <c r="G63" s="1"/>
-      <c r="H63" s="25" t="s">
-        <v>95</v>
+      <c r="H63" s="26" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A64" s="24"/>
+      <c r="A64" s="25"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
       <c r="D64" s="1"/>
       <c r="E64" s="1"/>
       <c r="F64" s="1"/>
       <c r="G64" s="1"/>
-      <c r="H64" s="71" t="s">
-        <v>76</v>
+      <c r="H64" s="72" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="65" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="20"/>
-      <c r="B65" s="22"/>
-      <c r="C65" s="22"/>
-      <c r="D65" s="22"/>
-      <c r="E65" s="22"/>
-      <c r="F65" s="22"/>
-      <c r="G65" s="22"/>
-      <c r="H65" s="70" t="s">
-        <v>90</v>
+      <c r="A65" s="21"/>
+      <c r="B65" s="23"/>
+      <c r="C65" s="23"/>
+      <c r="D65" s="23"/>
+      <c r="E65" s="23"/>
+      <c r="F65" s="23"/>
+      <c r="G65" s="23"/>
+      <c r="H65" s="71" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A66" s="16" t="s">
+      <c r="A66" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="B66" s="19"/>
+      <c r="C66" s="19"/>
+      <c r="D66" s="42" t="s">
+        <v>68</v>
+      </c>
+      <c r="E66" s="19"/>
+      <c r="F66" s="19"/>
+      <c r="G66" s="19"/>
+      <c r="H66" s="20"/>
+    </row>
+    <row r="67" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="21"/>
+      <c r="B67" s="23"/>
+      <c r="C67" s="23"/>
+      <c r="D67" s="43" t="s">
+        <v>70</v>
+      </c>
+      <c r="E67" s="23"/>
+      <c r="F67" s="23"/>
+      <c r="G67" s="23"/>
+      <c r="H67" s="24"/>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="B66" s="18"/>
-      <c r="C66" s="18"/>
-      <c r="D66" s="41" t="s">
-        <v>69</v>
-      </c>
-      <c r="E66" s="18"/>
-      <c r="F66" s="18"/>
-      <c r="G66" s="18"/>
-      <c r="H66" s="19"/>
-    </row>
-    <row r="67" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="20"/>
-      <c r="B67" s="22"/>
-      <c r="C67" s="22"/>
-      <c r="D67" s="42" t="s">
-        <v>71</v>
-      </c>
-      <c r="E67" s="22"/>
-      <c r="F67" s="22"/>
-      <c r="G67" s="22"/>
-      <c r="H67" s="23"/>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A68" s="16" t="s">
+      <c r="B68" s="19"/>
+      <c r="C68" s="19"/>
+      <c r="D68" s="19"/>
+      <c r="E68" s="19"/>
+      <c r="F68" s="19"/>
+      <c r="G68" s="19"/>
+      <c r="H68" s="70" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="21"/>
+      <c r="B69" s="23"/>
+      <c r="C69" s="23"/>
+      <c r="D69" s="23"/>
+      <c r="E69" s="23"/>
+      <c r="F69" s="23"/>
+      <c r="G69" s="23"/>
+      <c r="H69" s="71" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" s="33" t="s">
         <v>97</v>
-      </c>
-      <c r="B68" s="18"/>
-      <c r="C68" s="18"/>
-      <c r="D68" s="18"/>
-      <c r="E68" s="18"/>
-      <c r="F68" s="18"/>
-      <c r="G68" s="18"/>
-      <c r="H68" s="69" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="20"/>
-      <c r="B69" s="22"/>
-      <c r="C69" s="22"/>
-      <c r="D69" s="22"/>
-      <c r="E69" s="22"/>
-      <c r="F69" s="22"/>
-      <c r="G69" s="22"/>
-      <c r="H69" s="70" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A70" s="32" t="s">
-        <v>98</v>
       </c>
       <c r="B70" s="1"/>
       <c r="C70" s="1" t="s">
@@ -6711,28 +7027,28 @@
         <v>18</v>
       </c>
       <c r="G70" s="1"/>
-      <c r="H70" s="25"/>
+      <c r="H70" s="26"/>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A71" s="24"/>
+      <c r="A71" s="25"/>
       <c r="B71" s="1"/>
       <c r="C71" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D71" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="D71" s="1" t="s">
+      <c r="E71" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="E71" s="1" t="s">
+      <c r="F71" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="F71" s="1" t="s">
-        <v>102</v>
-      </c>
       <c r="G71" s="1"/>
-      <c r="H71" s="25"/>
+      <c r="H71" s="26"/>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A72" s="24"/>
+      <c r="A72" s="25"/>
       <c r="B72" s="1"/>
       <c r="C72" s="1"/>
       <c r="D72" s="2" t="s">
@@ -6741,240 +7057,240 @@
       <c r="E72" s="1"/>
       <c r="F72" s="1"/>
       <c r="G72" s="1"/>
-      <c r="H72" s="25"/>
+      <c r="H72" s="26"/>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A73" s="24"/>
+      <c r="A73" s="25"/>
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
       <c r="D73" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E73" s="1"/>
       <c r="F73" s="1"/>
       <c r="G73" s="1"/>
-      <c r="H73" s="25"/>
+      <c r="H73" s="26"/>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A74" s="24"/>
+      <c r="A74" s="25"/>
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
-      <c r="D74" s="44" t="s">
+      <c r="D74" s="45" t="s">
         <v>15</v>
       </c>
       <c r="E74" s="1"/>
       <c r="F74" s="1"/>
       <c r="G74" s="1"/>
-      <c r="H74" s="25"/>
+      <c r="H74" s="26"/>
     </row>
     <row r="75" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="20"/>
-      <c r="B75" s="22"/>
-      <c r="C75" s="22"/>
-      <c r="D75" s="42" t="s">
+      <c r="A75" s="21"/>
+      <c r="B75" s="23"/>
+      <c r="C75" s="23"/>
+      <c r="D75" s="43" t="s">
+        <v>103</v>
+      </c>
+      <c r="E75" s="23"/>
+      <c r="F75" s="23"/>
+      <c r="G75" s="23"/>
+      <c r="H75" s="24"/>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="E75" s="22"/>
-      <c r="F75" s="22"/>
-      <c r="G75" s="22"/>
-      <c r="H75" s="23"/>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A76" s="16" t="s">
-        <v>105</v>
-      </c>
-      <c r="B76" s="18"/>
-      <c r="C76" s="18"/>
-      <c r="D76" s="18"/>
-      <c r="E76" s="18"/>
-      <c r="F76" s="18"/>
-      <c r="G76" s="51" t="s">
-        <v>76</v>
-      </c>
-      <c r="H76" s="69" t="s">
-        <v>76</v>
+      <c r="B76" s="19"/>
+      <c r="C76" s="19"/>
+      <c r="D76" s="19"/>
+      <c r="E76" s="19"/>
+      <c r="F76" s="19"/>
+      <c r="G76" s="52" t="s">
+        <v>75</v>
+      </c>
+      <c r="H76" s="70" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A77" s="24"/>
+      <c r="A77" s="25"/>
       <c r="B77" s="1"/>
       <c r="C77" s="1"/>
       <c r="D77" s="1"/>
       <c r="E77" s="1"/>
       <c r="F77" s="1"/>
-      <c r="G77" s="52" t="s">
+      <c r="G77" s="53" t="s">
+        <v>105</v>
+      </c>
+      <c r="H77" s="73" t="s">
         <v>106</v>
       </c>
-      <c r="H77" s="72" t="s">
-        <v>107</v>
-      </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A78" s="24"/>
+      <c r="A78" s="25"/>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
       <c r="D78" s="1"/>
       <c r="E78" s="1"/>
       <c r="F78" s="1"/>
-      <c r="G78" s="45" t="s">
-        <v>59</v>
-      </c>
-      <c r="H78" s="71" t="s">
-        <v>76</v>
+      <c r="G78" s="46" t="s">
+        <v>58</v>
+      </c>
+      <c r="H78" s="72" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A79" s="24"/>
+      <c r="A79" s="25"/>
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
       <c r="D79" s="1"/>
       <c r="E79" s="1"/>
       <c r="F79" s="1"/>
-      <c r="G79" s="46" t="s">
-        <v>88</v>
-      </c>
-      <c r="H79" s="72" t="s">
-        <v>108</v>
+      <c r="G79" s="47" t="s">
+        <v>87</v>
+      </c>
+      <c r="H79" s="73" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A80" s="24"/>
+      <c r="A80" s="25"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
       <c r="D80" s="1"/>
       <c r="E80" s="1"/>
       <c r="F80" s="1"/>
-      <c r="G80" s="46"/>
-      <c r="H80" s="71" t="s">
-        <v>109</v>
+      <c r="G80" s="47"/>
+      <c r="H80" s="72" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A81" s="24"/>
+      <c r="A81" s="25"/>
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
       <c r="D81" s="1"/>
       <c r="E81" s="1"/>
       <c r="F81" s="1"/>
-      <c r="G81" s="46"/>
-      <c r="H81" s="72" t="s">
-        <v>110</v>
+      <c r="G81" s="47"/>
+      <c r="H81" s="73" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A82" s="24"/>
+      <c r="A82" s="25"/>
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
       <c r="D82" s="1"/>
       <c r="E82" s="1"/>
       <c r="F82" s="1"/>
-      <c r="G82" s="46"/>
-      <c r="H82" s="31" t="s">
+      <c r="G82" s="47"/>
+      <c r="H82" s="32" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="83" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="20"/>
-      <c r="B83" s="22"/>
-      <c r="C83" s="22"/>
-      <c r="D83" s="22"/>
-      <c r="E83" s="22"/>
-      <c r="F83" s="22"/>
-      <c r="G83" s="47"/>
-      <c r="H83" s="23" t="s">
+      <c r="A83" s="21"/>
+      <c r="B83" s="23"/>
+      <c r="C83" s="23"/>
+      <c r="D83" s="23"/>
+      <c r="E83" s="23"/>
+      <c r="F83" s="23"/>
+      <c r="G83" s="48"/>
+      <c r="H83" s="24" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="27" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="84" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="26" t="s">
+      <c r="B84" s="28"/>
+      <c r="C84" s="29"/>
+      <c r="D84" s="29"/>
+      <c r="E84" s="29"/>
+      <c r="F84" s="29"/>
+      <c r="G84" s="29"/>
+      <c r="H84" s="30"/>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" s="17" t="s">
         <v>112</v>
       </c>
-      <c r="B84" s="27"/>
-      <c r="C84" s="28"/>
-      <c r="D84" s="28"/>
-      <c r="E84" s="28"/>
-      <c r="F84" s="28"/>
-      <c r="G84" s="28"/>
-      <c r="H84" s="29"/>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A85" s="16" t="s">
-        <v>113</v>
-      </c>
-      <c r="B85" s="18"/>
-      <c r="C85" s="18"/>
-      <c r="D85" s="18"/>
-      <c r="E85" s="18"/>
-      <c r="F85" s="18"/>
-      <c r="G85" s="54" t="s">
+      <c r="B85" s="19"/>
+      <c r="C85" s="19"/>
+      <c r="D85" s="19"/>
+      <c r="E85" s="19"/>
+      <c r="F85" s="19"/>
+      <c r="G85" s="55" t="s">
         <v>12</v>
       </c>
-      <c r="H85" s="19"/>
+      <c r="H85" s="20"/>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A86" s="24"/>
+      <c r="A86" s="25"/>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
       <c r="D86" s="1"/>
       <c r="E86" s="1"/>
       <c r="F86" s="1"/>
-      <c r="G86" s="55" t="s">
+      <c r="G86" s="56" t="s">
         <v>13</v>
       </c>
-      <c r="H86" s="25"/>
+      <c r="H86" s="26"/>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A87" s="24"/>
+      <c r="A87" s="25"/>
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
       <c r="D87" s="1"/>
       <c r="E87" s="1"/>
       <c r="F87" s="1"/>
-      <c r="G87" s="56" t="s">
+      <c r="G87" s="57" t="s">
         <v>12</v>
       </c>
-      <c r="H87" s="25"/>
+      <c r="H87" s="26"/>
     </row>
     <row r="88" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="20"/>
-      <c r="B88" s="22"/>
-      <c r="C88" s="22"/>
-      <c r="D88" s="22"/>
-      <c r="E88" s="22"/>
-      <c r="F88" s="22"/>
-      <c r="G88" s="57" t="s">
-        <v>42</v>
-      </c>
-      <c r="H88" s="23"/>
+      <c r="A88" s="21"/>
+      <c r="B88" s="23"/>
+      <c r="C88" s="23"/>
+      <c r="D88" s="23"/>
+      <c r="E88" s="23"/>
+      <c r="F88" s="23"/>
+      <c r="G88" s="58" t="s">
+        <v>41</v>
+      </c>
+      <c r="H88" s="24"/>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A89" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="B89" s="18"/>
-      <c r="C89" s="18"/>
-      <c r="D89" s="18"/>
-      <c r="E89" s="18"/>
-      <c r="F89" s="18"/>
-      <c r="G89" s="51" t="s">
-        <v>76</v>
-      </c>
-      <c r="H89" s="19"/>
+      <c r="A89" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="B89" s="19"/>
+      <c r="C89" s="19"/>
+      <c r="D89" s="19"/>
+      <c r="E89" s="19"/>
+      <c r="F89" s="19"/>
+      <c r="G89" s="52" t="s">
+        <v>75</v>
+      </c>
+      <c r="H89" s="20"/>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A90" s="24"/>
+      <c r="A90" s="25"/>
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
       <c r="D90" s="1"/>
       <c r="E90" s="1"/>
       <c r="F90" s="1"/>
-      <c r="G90" s="52" t="s">
+      <c r="G90" s="53" t="s">
         <v>27</v>
       </c>
-      <c r="H90" s="25"/>
+      <c r="H90" s="26"/>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A91" s="24"/>
+      <c r="A91" s="25"/>
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
       <c r="D91" s="1"/>
@@ -6983,48 +7299,48 @@
       <c r="G91" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="H91" s="25"/>
+      <c r="H91" s="26"/>
     </row>
     <row r="92" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="20"/>
-      <c r="B92" s="22"/>
-      <c r="C92" s="22"/>
-      <c r="D92" s="22"/>
-      <c r="E92" s="22"/>
-      <c r="F92" s="22"/>
-      <c r="G92" s="22" t="s">
+      <c r="A92" s="21"/>
+      <c r="B92" s="23"/>
+      <c r="C92" s="23"/>
+      <c r="D92" s="23"/>
+      <c r="E92" s="23"/>
+      <c r="F92" s="23"/>
+      <c r="G92" s="23" t="s">
+        <v>114</v>
+      </c>
+      <c r="H92" s="24"/>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" s="17" t="s">
         <v>115</v>
       </c>
-      <c r="H92" s="23"/>
-    </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A93" s="16" t="s">
-        <v>116</v>
-      </c>
-      <c r="B93" s="18"/>
-      <c r="C93" s="18"/>
-      <c r="D93" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="E93" s="18"/>
-      <c r="F93" s="18"/>
-      <c r="G93" s="18"/>
-      <c r="H93" s="19"/>
+      <c r="B93" s="19"/>
+      <c r="C93" s="19"/>
+      <c r="D93" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="E93" s="19"/>
+      <c r="F93" s="19"/>
+      <c r="G93" s="19"/>
+      <c r="H93" s="20"/>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A94" s="24"/>
+      <c r="A94" s="25"/>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
       <c r="D94" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E94" s="1"/>
       <c r="F94" s="1"/>
       <c r="G94" s="1"/>
-      <c r="H94" s="25"/>
+      <c r="H94" s="26"/>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A95" s="24"/>
+      <c r="A95" s="25"/>
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
       <c r="D95" s="2" t="s">
@@ -7033,106 +7349,106 @@
       <c r="E95" s="1"/>
       <c r="F95" s="1"/>
       <c r="G95" s="1"/>
-      <c r="H95" s="25"/>
+      <c r="H95" s="26"/>
     </row>
     <row r="96" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="20"/>
-      <c r="B96" s="22"/>
-      <c r="C96" s="22"/>
-      <c r="D96" s="22" t="s">
-        <v>78</v>
-      </c>
-      <c r="E96" s="22"/>
-      <c r="F96" s="22"/>
-      <c r="G96" s="22"/>
-      <c r="H96" s="23"/>
+      <c r="A96" s="21"/>
+      <c r="B96" s="23"/>
+      <c r="C96" s="23"/>
+      <c r="D96" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="E96" s="23"/>
+      <c r="F96" s="23"/>
+      <c r="G96" s="23"/>
+      <c r="H96" s="24"/>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A97" s="16" t="s">
-        <v>118</v>
-      </c>
-      <c r="B97" s="18"/>
-      <c r="C97" s="18"/>
-      <c r="D97" s="18"/>
-      <c r="E97" s="18"/>
-      <c r="F97" s="18"/>
-      <c r="G97" s="54" t="s">
-        <v>60</v>
-      </c>
-      <c r="H97" s="69" t="s">
-        <v>76</v>
+      <c r="A97" s="17" t="s">
+        <v>117</v>
+      </c>
+      <c r="B97" s="19"/>
+      <c r="C97" s="19"/>
+      <c r="D97" s="19"/>
+      <c r="E97" s="19"/>
+      <c r="F97" s="19"/>
+      <c r="G97" s="55" t="s">
+        <v>59</v>
+      </c>
+      <c r="H97" s="70" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A98" s="24"/>
+      <c r="A98" s="25"/>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
       <c r="D98" s="1"/>
       <c r="E98" s="1"/>
       <c r="F98" s="1"/>
-      <c r="G98" s="55" t="s">
-        <v>119</v>
-      </c>
-      <c r="H98" s="72" t="s">
-        <v>106</v>
+      <c r="G98" s="56" t="s">
+        <v>118</v>
+      </c>
+      <c r="H98" s="73" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A99" s="24"/>
+      <c r="A99" s="25"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
       <c r="D99" s="1"/>
       <c r="E99" s="1"/>
       <c r="F99" s="1"/>
-      <c r="G99" s="56" t="s">
+      <c r="G99" s="57" t="s">
         <v>12</v>
       </c>
-      <c r="H99" s="72"/>
+      <c r="H99" s="73"/>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A100" s="24"/>
+      <c r="A100" s="25"/>
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
       <c r="D100" s="1"/>
       <c r="E100" s="1"/>
       <c r="F100" s="1"/>
-      <c r="G100" s="55" t="s">
-        <v>62</v>
-      </c>
-      <c r="H100" s="72"/>
+      <c r="G100" s="56" t="s">
+        <v>61</v>
+      </c>
+      <c r="H100" s="73"/>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A101" s="24"/>
+      <c r="A101" s="25"/>
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
       <c r="D101" s="1"/>
       <c r="E101" s="1"/>
       <c r="F101" s="1"/>
-      <c r="G101" s="73" t="s">
-        <v>76</v>
-      </c>
-      <c r="H101" s="72"/>
+      <c r="G101" s="74" t="s">
+        <v>75</v>
+      </c>
+      <c r="H101" s="73"/>
     </row>
     <row r="102" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="20"/>
-      <c r="B102" s="22"/>
-      <c r="C102" s="22"/>
-      <c r="D102" s="22"/>
-      <c r="E102" s="22"/>
-      <c r="F102" s="22"/>
-      <c r="G102" s="53" t="s">
-        <v>120</v>
-      </c>
-      <c r="H102" s="70"/>
+      <c r="A102" s="21"/>
+      <c r="B102" s="23"/>
+      <c r="C102" s="23"/>
+      <c r="D102" s="23"/>
+      <c r="E102" s="23"/>
+      <c r="F102" s="23"/>
+      <c r="G102" s="54" t="s">
+        <v>119</v>
+      </c>
+      <c r="H102" s="71"/>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B103" s="30"/>
-      <c r="C103" s="30"/>
-      <c r="D103" s="30"/>
-      <c r="E103" s="30"/>
-      <c r="F103" s="30"/>
-      <c r="G103" s="30"/>
-      <c r="H103" s="30"/>
+      <c r="B103" s="31"/>
+      <c r="C103" s="31"/>
+      <c r="D103" s="31"/>
+      <c r="E103" s="31"/>
+      <c r="F103" s="31"/>
+      <c r="G103" s="31"/>
+      <c r="H103" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="30">
@@ -7184,36 +7500,36 @@
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B5" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B5" s="14" t="s">
-        <v>122</v>
-      </c>
-      <c r="C5" s="14"/>
-      <c r="D5" s="14"/>
-      <c r="E5" s="14"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>3</v>
       </c>
       <c r="B6" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="C6" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="D6" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="E6" s="6" t="s">
         <v>125</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -7320,7 +7636,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B13" s="7">
         <v>0</v>
@@ -7337,7 +7653,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B14" s="7">
         <v>0</v>
@@ -7354,7 +7670,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B15" s="7">
         <v>0</v>
@@ -7371,7 +7687,7 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B16" s="7">
         <v>0</v>
@@ -7388,7 +7704,7 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B17" s="7">
         <v>0</v>
@@ -7405,7 +7721,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B18" s="7">
         <v>0</v>
@@ -7422,7 +7738,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B19" s="7">
         <v>0</v>
@@ -7439,7 +7755,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B20" s="7">
         <v>0</v>
@@ -7456,7 +7772,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B21" s="7">
         <v>0</v>
@@ -7473,7 +7789,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B22" s="7">
         <v>0</v>
@@ -7490,7 +7806,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B23" s="7">
         <v>0</v>
@@ -7507,7 +7823,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B24" s="7">
         <v>0</v>
@@ -7524,7 +7840,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B25" s="7">
         <v>0</v>
@@ -7541,7 +7857,7 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B26" s="7">
         <v>0</v>
@@ -7558,7 +7874,7 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B27" s="7">
         <v>0</v>
@@ -7575,7 +7891,7 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B28" s="7">
         <v>0</v>
@@ -7592,7 +7908,7 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B29" s="7">
         <v>0</v>
@@ -7609,7 +7925,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B30" s="7">
         <v>0</v>
@@ -7626,7 +7942,7 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B31" s="7">
         <v>0</v>
@@ -7643,7 +7959,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B32" s="7">
         <v>0</v>
@@ -7660,7 +7976,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B33" s="7">
         <v>0</v>
@@ -7710,40 +8026,40 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="B4" s="11" t="s">
         <v>127</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B5" s="11"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="B7" s="11" t="s">
         <v>131</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="B8" s="11" t="s">
         <v>133</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -7918,13 +8234,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{405C9297-F11E-4578-88EA-89CDFD73950B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C9482BC0-D9A0-4F2E-A662-55F6A6E1E8C5}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{495D27A4-2557-4648-A851-BB5BC020AD7E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DA586971-1ADE-4638-9DB3-7A0A07ABD948}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5600366F-407E-4B2B-BFE4-5449C85FBAFC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA842A77-17E4-4803-881D-F58312C9A224}"/>
 </file>
--- a/Plannings 2026 S26.xlsx
+++ b/Plannings 2026 S26.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="8_{A23AA2D1-9819-4B65-9C3A-D83FC30F8B22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BE77D127-EEBA-4B11-B64D-E4268FA37DEA}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="8_{A23AA2D1-9819-4B65-9C3A-D83FC30F8B22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DCE23DB7-D103-4D89-99E7-0D32315F5783}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="152">
   <si>
     <t>Planning des salariés du 22/06/2026 au 28/06/2026</t>
   </si>
@@ -435,9 +435,6 @@
     <t>FORP VDC</t>
   </si>
   <si>
-    <t>09:45/13:15</t>
-  </si>
-  <si>
     <t>11:45/17:00</t>
   </si>
   <si>
@@ -475,6 +472,12 @@
   </si>
   <si>
     <t>10:15/17:00</t>
+  </si>
+  <si>
+    <t>11:45/16:30</t>
+  </si>
+  <si>
+    <t>09:45/13:00</t>
   </si>
 </sst>
 </file>
@@ -988,7 +991,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1167,18 +1170,6 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1218,6 +1209,12 @@
     <xf numFmtId="0" fontId="16" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5590,6 +5587,446 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="3657600" y="4391025"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="110" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5E11E667-BCB5-4EB1-B679-508B36CE3BB1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="2295525"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="111" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1F346B36-B49F-4C01-89C5-D785CB6802C5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="2676525"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="112" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3D3A596E-3F14-4212-8CA9-41F8D2D79956}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1219200" y="2295525"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="113" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9B0376B6-6366-408A-868E-C3E5B29CD7A2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1828800" y="2295525"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="114" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{257B316F-EE6B-4EF7-8F2B-89C2D483A2FF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1828800" y="2676525"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="115" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BFABF675-D5EE-496F-AFBA-1BBA689333F2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1828800" y="3057525"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="116" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{68A3E215-42C0-4FDA-BDF1-CFE864063B92}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2438400" y="2295525"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="117" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{58FC21F7-F7BE-49C4-882A-2D9AF8FE52D4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2438400" y="2676525"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="118" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D8C9CF28-6387-4A30-BE59-F70C9EE8DC20}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2438400" y="3057525"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="119" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8FB689B7-1847-4C5B-BC62-6E7A4F0E994B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3048000" y="2295525"/>
           <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -6000,36 +6437,36 @@
       <c r="H2" s="12"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B3" s="65" t="s">
+      <c r="B3" s="61" t="s">
+        <v>140</v>
+      </c>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="63"/>
+    </row>
+    <row r="4" spans="1:8" s="64" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="B4" s="65" t="s">
         <v>141</v>
       </c>
-      <c r="C3" s="66"/>
-      <c r="D3" s="66"/>
-      <c r="E3" s="66"/>
-      <c r="F3" s="66"/>
-      <c r="G3" s="66"/>
-      <c r="H3" s="67"/>
-    </row>
-    <row r="4" spans="1:8" s="68" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="B4" s="69" t="s">
+      <c r="C4" s="65" t="s">
         <v>142</v>
       </c>
-      <c r="C4" s="69" t="s">
+      <c r="D4" s="65" t="s">
         <v>143</v>
       </c>
-      <c r="D4" s="69" t="s">
+      <c r="E4" s="65" t="s">
         <v>144</v>
       </c>
-      <c r="E4" s="69" t="s">
+      <c r="F4" s="65" t="s">
         <v>145</v>
       </c>
-      <c r="F4" s="69" t="s">
+      <c r="G4" s="65" t="s">
         <v>146</v>
       </c>
-      <c r="G4" s="69" t="s">
-        <v>147</v>
-      </c>
-      <c r="H4" s="69" t="s">
+      <c r="H4" s="65" t="s">
         <v>75</v>
       </c>
     </row>
@@ -6115,99 +6552,103 @@
       <c r="A10" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="C10" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="D10" s="63" t="s">
+      <c r="D10" s="71" t="s">
         <v>19</v>
       </c>
-      <c r="E10" s="42" t="s">
-        <v>20</v>
-      </c>
-      <c r="F10" s="19" t="s">
+      <c r="E10" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="G10" s="19"/>
-      <c r="H10" s="20"/>
+      <c r="F10" s="51" t="s">
+        <v>18</v>
+      </c>
+      <c r="G10" s="51"/>
+      <c r="H10" s="59"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="25"/>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="59" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="59" t="s">
         <v>22</v>
       </c>
-      <c r="D11" s="61" t="s">
+      <c r="D11" s="72" t="s">
         <v>23</v>
       </c>
-      <c r="E11" s="44" t="s">
-        <v>24</v>
+      <c r="E11" s="59" t="s">
+        <v>150</v>
       </c>
       <c r="F11" s="59" t="s">
-        <v>137</v>
-      </c>
-      <c r="G11" s="1"/>
-      <c r="H11" s="26"/>
+        <v>151</v>
+      </c>
+      <c r="G11" s="59"/>
+      <c r="H11" s="59"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="25"/>
-      <c r="B12" s="60" t="s">
+      <c r="B12" s="71" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="1"/>
-      <c r="D12" s="2" t="s">
+      <c r="C12" s="59"/>
+      <c r="D12" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="26"/>
+      <c r="E12" s="73" t="s">
+        <v>20</v>
+      </c>
+      <c r="F12" s="59"/>
+      <c r="G12" s="59"/>
+      <c r="H12" s="59"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="25"/>
-      <c r="B13" s="61" t="s">
+      <c r="B13" s="72" t="s">
         <v>26</v>
       </c>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1" t="s">
+      <c r="C13" s="59"/>
+      <c r="D13" s="59" t="s">
         <v>27</v>
       </c>
-      <c r="E13" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="26"/>
+      <c r="E13" s="74" t="s">
+        <v>24</v>
+      </c>
+      <c r="F13" s="59"/>
+      <c r="G13" s="59"/>
+      <c r="H13" s="59"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="25"/>
-      <c r="B14" s="61"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="45" t="s">
+      <c r="B14" s="72"/>
+      <c r="C14" s="59"/>
+      <c r="D14" s="73" t="s">
         <v>20</v>
       </c>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="26"/>
+      <c r="E14" s="51" t="s">
+        <v>18</v>
+      </c>
+      <c r="F14" s="59"/>
+      <c r="G14" s="59"/>
+      <c r="H14" s="59"/>
     </row>
     <row r="15" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="21"/>
-      <c r="B15" s="62"/>
-      <c r="C15" s="23"/>
-      <c r="D15" s="43" t="s">
+      <c r="B15" s="72"/>
+      <c r="C15" s="59"/>
+      <c r="D15" s="74" t="s">
         <v>29</v>
       </c>
-      <c r="E15" s="23"/>
-      <c r="F15" s="23"/>
-      <c r="G15" s="23"/>
-      <c r="H15" s="24"/>
+      <c r="E15" s="59" t="s">
+        <v>28</v>
+      </c>
+      <c r="F15" s="59"/>
+      <c r="G15" s="59"/>
+      <c r="H15" s="59"/>
     </row>
     <row r="16" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="27" t="s">
@@ -6246,20 +6687,20 @@
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="13"/>
       <c r="B18" s="59" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C18" s="59" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D18" s="59" t="s">
         <v>33</v>
       </c>
       <c r="E18" s="59"/>
       <c r="F18" s="59" t="s">
+        <v>148</v>
+      </c>
+      <c r="G18" s="59" t="s">
         <v>149</v>
-      </c>
-      <c r="G18" s="59" t="s">
-        <v>150</v>
       </c>
       <c r="H18" s="59"/>
     </row>
@@ -6267,7 +6708,7 @@
       <c r="A19" s="13"/>
       <c r="B19" s="59"/>
       <c r="C19" s="59"/>
-      <c r="D19" s="75" t="s">
+      <c r="D19" s="71" t="s">
         <v>34</v>
       </c>
       <c r="E19" s="59"/>
@@ -6279,7 +6720,7 @@
       <c r="A20" s="13"/>
       <c r="B20" s="59"/>
       <c r="C20" s="59"/>
-      <c r="D20" s="76" t="s">
+      <c r="D20" s="72" t="s">
         <v>35</v>
       </c>
       <c r="E20" s="59"/>
@@ -6514,7 +6955,7 @@
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="25"/>
       <c r="B35" s="59" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C35" s="47" t="s">
         <v>60</v>
@@ -6739,8 +7180,8 @@
     </row>
     <row r="50" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="21"/>
-      <c r="B50" s="64" t="s">
-        <v>140</v>
+      <c r="B50" s="60" t="s">
+        <v>139</v>
       </c>
       <c r="C50" s="23" t="s">
         <v>77</v>
@@ -6765,7 +7206,7 @@
       <c r="E51" s="19"/>
       <c r="F51" s="19"/>
       <c r="G51" s="19"/>
-      <c r="H51" s="70" t="s">
+      <c r="H51" s="66" t="s">
         <v>75</v>
       </c>
     </row>
@@ -6777,7 +7218,7 @@
       <c r="E52" s="23"/>
       <c r="F52" s="23"/>
       <c r="G52" s="23"/>
-      <c r="H52" s="71" t="s">
+      <c r="H52" s="67" t="s">
         <v>78</v>
       </c>
     </row>
@@ -6867,7 +7308,7 @@
       <c r="G58" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="H58" s="72" t="s">
+      <c r="H58" s="68" t="s">
         <v>75</v>
       </c>
     </row>
@@ -6881,7 +7322,7 @@
       <c r="G59" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="H59" s="73" t="s">
+      <c r="H59" s="69" t="s">
         <v>92</v>
       </c>
     </row>
@@ -6941,7 +7382,7 @@
       <c r="E64" s="1"/>
       <c r="F64" s="1"/>
       <c r="G64" s="1"/>
-      <c r="H64" s="72" t="s">
+      <c r="H64" s="68" t="s">
         <v>75</v>
       </c>
     </row>
@@ -6953,7 +7394,7 @@
       <c r="E65" s="23"/>
       <c r="F65" s="23"/>
       <c r="G65" s="23"/>
-      <c r="H65" s="71" t="s">
+      <c r="H65" s="67" t="s">
         <v>89</v>
       </c>
     </row>
@@ -6993,7 +7434,7 @@
       <c r="E68" s="19"/>
       <c r="F68" s="19"/>
       <c r="G68" s="19"/>
-      <c r="H68" s="70" t="s">
+      <c r="H68" s="66" t="s">
         <v>75</v>
       </c>
     </row>
@@ -7005,7 +7446,7 @@
       <c r="E69" s="23"/>
       <c r="F69" s="23"/>
       <c r="G69" s="23"/>
-      <c r="H69" s="71" t="s">
+      <c r="H69" s="67" t="s">
         <v>78</v>
       </c>
     </row>
@@ -7107,7 +7548,7 @@
       <c r="G76" s="52" t="s">
         <v>75</v>
       </c>
-      <c r="H76" s="70" t="s">
+      <c r="H76" s="66" t="s">
         <v>75</v>
       </c>
     </row>
@@ -7121,7 +7562,7 @@
       <c r="G77" s="53" t="s">
         <v>105</v>
       </c>
-      <c r="H77" s="73" t="s">
+      <c r="H77" s="69" t="s">
         <v>106</v>
       </c>
     </row>
@@ -7135,7 +7576,7 @@
       <c r="G78" s="46" t="s">
         <v>58</v>
       </c>
-      <c r="H78" s="72" t="s">
+      <c r="H78" s="68" t="s">
         <v>75</v>
       </c>
     </row>
@@ -7149,7 +7590,7 @@
       <c r="G79" s="47" t="s">
         <v>87</v>
       </c>
-      <c r="H79" s="73" t="s">
+      <c r="H79" s="69" t="s">
         <v>107</v>
       </c>
     </row>
@@ -7161,7 +7602,7 @@
       <c r="E80" s="1"/>
       <c r="F80" s="1"/>
       <c r="G80" s="47"/>
-      <c r="H80" s="72" t="s">
+      <c r="H80" s="68" t="s">
         <v>108</v>
       </c>
     </row>
@@ -7173,7 +7614,7 @@
       <c r="E81" s="1"/>
       <c r="F81" s="1"/>
       <c r="G81" s="47"/>
-      <c r="H81" s="73" t="s">
+      <c r="H81" s="69" t="s">
         <v>109</v>
       </c>
     </row>
@@ -7375,7 +7816,7 @@
       <c r="G97" s="55" t="s">
         <v>59</v>
       </c>
-      <c r="H97" s="70" t="s">
+      <c r="H97" s="66" t="s">
         <v>75</v>
       </c>
     </row>
@@ -7389,7 +7830,7 @@
       <c r="G98" s="56" t="s">
         <v>118</v>
       </c>
-      <c r="H98" s="73" t="s">
+      <c r="H98" s="69" t="s">
         <v>105</v>
       </c>
     </row>
@@ -7403,7 +7844,7 @@
       <c r="G99" s="57" t="s">
         <v>12</v>
       </c>
-      <c r="H99" s="73"/>
+      <c r="H99" s="69"/>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" s="25"/>
@@ -7415,7 +7856,7 @@
       <c r="G100" s="56" t="s">
         <v>61</v>
       </c>
-      <c r="H100" s="73"/>
+      <c r="H100" s="69"/>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" s="25"/>
@@ -7424,10 +7865,10 @@
       <c r="D101" s="1"/>
       <c r="E101" s="1"/>
       <c r="F101" s="1"/>
-      <c r="G101" s="74" t="s">
+      <c r="G101" s="70" t="s">
         <v>75</v>
       </c>
-      <c r="H101" s="73"/>
+      <c r="H101" s="69"/>
     </row>
     <row r="102" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A102" s="21"/>
@@ -7439,7 +7880,7 @@
       <c r="G102" s="54" t="s">
         <v>119</v>
       </c>
-      <c r="H102" s="71"/>
+      <c r="H102" s="67"/>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B103" s="31"/>
@@ -8234,13 +8675,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C9482BC0-D9A0-4F2E-A662-55F6A6E1E8C5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82C34503-2CEC-4D68-80CD-B28E1A8DE2C4}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DA586971-1ADE-4638-9DB3-7A0A07ABD948}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{21680000-0FA8-4848-A547-28CF206D5CC1}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA842A77-17E4-4803-881D-F58312C9A224}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5799426A-8929-4C41-8FE8-4FA90918C70D}"/>
 </file>
--- a/Plannings 2026 S26.xlsx
+++ b/Plannings 2026 S26.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="8_{A23AA2D1-9819-4B65-9C3A-D83FC30F8B22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DCE23DB7-D103-4D89-99E7-0D32315F5783}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{A23AA2D1-9819-4B65-9C3A-D83FC30F8B22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BE77D127-EEBA-4B11-B64D-E4268FA37DEA}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="151">
   <si>
     <t>Planning des salariés du 22/06/2026 au 28/06/2026</t>
   </si>
@@ -435,6 +435,9 @@
     <t>FORP VDC</t>
   </si>
   <si>
+    <t>09:45/13:15</t>
+  </si>
+  <si>
     <t>11:45/17:00</t>
   </si>
   <si>
@@ -472,12 +475,6 @@
   </si>
   <si>
     <t>10:15/17:00</t>
-  </si>
-  <si>
-    <t>11:45/16:30</t>
-  </si>
-  <si>
-    <t>09:45/13:00</t>
   </si>
 </sst>
 </file>
@@ -991,7 +988,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1170,6 +1167,18 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1209,12 +1218,6 @@
     <xf numFmtId="0" fontId="16" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5587,446 +5590,6 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="3657600" y="4391025"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="110" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5E11E667-BCB5-4EB1-B679-508B36CE3BB1}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="609600" y="2295525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="111" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1F346B36-B49F-4C01-89C5-D785CB6802C5}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="609600" y="2676525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="112" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3D3A596E-3F14-4212-8CA9-41F8D2D79956}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1219200" y="2295525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="113" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9B0376B6-6366-408A-868E-C3E5B29CD7A2}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1828800" y="2295525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="114" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{257B316F-EE6B-4EF7-8F2B-89C2D483A2FF}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1828800" y="2676525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="115" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BFABF675-D5EE-496F-AFBA-1BBA689333F2}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1828800" y="3057525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="116" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{68A3E215-42C0-4FDA-BDF1-CFE864063B92}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2438400" y="2295525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="117" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{58FC21F7-F7BE-49C4-882A-2D9AF8FE52D4}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2438400" y="2676525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="118" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D8C9CF28-6387-4A30-BE59-F70C9EE8DC20}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2438400" y="3057525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="119" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8FB689B7-1847-4C5B-BC62-6E7A4F0E994B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3048000" y="2295525"/>
           <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -6437,36 +6000,36 @@
       <c r="H2" s="12"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B3" s="61" t="s">
-        <v>140</v>
-      </c>
-      <c r="C3" s="62"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="63"/>
-    </row>
-    <row r="4" spans="1:8" s="64" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="B4" s="65" t="s">
+      <c r="B3" s="65" t="s">
         <v>141</v>
       </c>
-      <c r="C4" s="65" t="s">
+      <c r="C3" s="66"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="66"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="66"/>
+      <c r="H3" s="67"/>
+    </row>
+    <row r="4" spans="1:8" s="68" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="B4" s="69" t="s">
         <v>142</v>
       </c>
-      <c r="D4" s="65" t="s">
+      <c r="C4" s="69" t="s">
         <v>143</v>
       </c>
-      <c r="E4" s="65" t="s">
+      <c r="D4" s="69" t="s">
         <v>144</v>
       </c>
-      <c r="F4" s="65" t="s">
+      <c r="E4" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="G4" s="65" t="s">
+      <c r="F4" s="69" t="s">
         <v>146</v>
       </c>
-      <c r="H4" s="65" t="s">
+      <c r="G4" s="69" t="s">
+        <v>147</v>
+      </c>
+      <c r="H4" s="69" t="s">
         <v>75</v>
       </c>
     </row>
@@ -6552,103 +6115,99 @@
       <c r="A10" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="51" t="s">
+      <c r="B10" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="51" t="s">
+      <c r="C10" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D10" s="71" t="s">
+      <c r="D10" s="63" t="s">
         <v>19</v>
       </c>
-      <c r="E10" s="51" t="s">
+      <c r="E10" s="42" t="s">
+        <v>20</v>
+      </c>
+      <c r="F10" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="F10" s="51" t="s">
-        <v>18</v>
-      </c>
-      <c r="G10" s="51"/>
-      <c r="H10" s="59"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="20"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="25"/>
-      <c r="B11" s="59" t="s">
+      <c r="B11" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="59" t="s">
+      <c r="C11" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D11" s="72" t="s">
+      <c r="D11" s="61" t="s">
         <v>23</v>
       </c>
-      <c r="E11" s="59" t="s">
-        <v>150</v>
+      <c r="E11" s="44" t="s">
+        <v>24</v>
       </c>
       <c r="F11" s="59" t="s">
-        <v>151</v>
-      </c>
-      <c r="G11" s="59"/>
-      <c r="H11" s="59"/>
+        <v>137</v>
+      </c>
+      <c r="G11" s="1"/>
+      <c r="H11" s="26"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="25"/>
-      <c r="B12" s="71" t="s">
+      <c r="B12" s="60" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="59"/>
-      <c r="D12" s="51" t="s">
+      <c r="C12" s="1"/>
+      <c r="D12" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E12" s="73" t="s">
-        <v>20</v>
-      </c>
-      <c r="F12" s="59"/>
-      <c r="G12" s="59"/>
-      <c r="H12" s="59"/>
+      <c r="E12" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="26"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="25"/>
-      <c r="B13" s="72" t="s">
+      <c r="B13" s="61" t="s">
         <v>26</v>
       </c>
-      <c r="C13" s="59"/>
-      <c r="D13" s="59" t="s">
+      <c r="C13" s="1"/>
+      <c r="D13" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E13" s="74" t="s">
-        <v>24</v>
-      </c>
-      <c r="F13" s="59"/>
-      <c r="G13" s="59"/>
-      <c r="H13" s="59"/>
+      <c r="E13" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="26"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="25"/>
-      <c r="B14" s="72"/>
-      <c r="C14" s="59"/>
-      <c r="D14" s="73" t="s">
+      <c r="B14" s="61"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="E14" s="51" t="s">
-        <v>18</v>
-      </c>
-      <c r="F14" s="59"/>
-      <c r="G14" s="59"/>
-      <c r="H14" s="59"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="26"/>
     </row>
     <row r="15" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="21"/>
-      <c r="B15" s="72"/>
-      <c r="C15" s="59"/>
-      <c r="D15" s="74" t="s">
+      <c r="B15" s="62"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="43" t="s">
         <v>29</v>
       </c>
-      <c r="E15" s="59" t="s">
-        <v>28</v>
-      </c>
-      <c r="F15" s="59"/>
-      <c r="G15" s="59"/>
-      <c r="H15" s="59"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="23"/>
+      <c r="G15" s="23"/>
+      <c r="H15" s="24"/>
     </row>
     <row r="16" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="27" t="s">
@@ -6687,20 +6246,20 @@
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="13"/>
       <c r="B18" s="59" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C18" s="59" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D18" s="59" t="s">
         <v>33</v>
       </c>
       <c r="E18" s="59"/>
       <c r="F18" s="59" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G18" s="59" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H18" s="59"/>
     </row>
@@ -6708,7 +6267,7 @@
       <c r="A19" s="13"/>
       <c r="B19" s="59"/>
       <c r="C19" s="59"/>
-      <c r="D19" s="71" t="s">
+      <c r="D19" s="75" t="s">
         <v>34</v>
       </c>
       <c r="E19" s="59"/>
@@ -6720,7 +6279,7 @@
       <c r="A20" s="13"/>
       <c r="B20" s="59"/>
       <c r="C20" s="59"/>
-      <c r="D20" s="72" t="s">
+      <c r="D20" s="76" t="s">
         <v>35</v>
       </c>
       <c r="E20" s="59"/>
@@ -6955,7 +6514,7 @@
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="25"/>
       <c r="B35" s="59" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C35" s="47" t="s">
         <v>60</v>
@@ -7180,8 +6739,8 @@
     </row>
     <row r="50" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="21"/>
-      <c r="B50" s="60" t="s">
-        <v>139</v>
+      <c r="B50" s="64" t="s">
+        <v>140</v>
       </c>
       <c r="C50" s="23" t="s">
         <v>77</v>
@@ -7206,7 +6765,7 @@
       <c r="E51" s="19"/>
       <c r="F51" s="19"/>
       <c r="G51" s="19"/>
-      <c r="H51" s="66" t="s">
+      <c r="H51" s="70" t="s">
         <v>75</v>
       </c>
     </row>
@@ -7218,7 +6777,7 @@
       <c r="E52" s="23"/>
       <c r="F52" s="23"/>
       <c r="G52" s="23"/>
-      <c r="H52" s="67" t="s">
+      <c r="H52" s="71" t="s">
         <v>78</v>
       </c>
     </row>
@@ -7308,7 +6867,7 @@
       <c r="G58" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="H58" s="68" t="s">
+      <c r="H58" s="72" t="s">
         <v>75</v>
       </c>
     </row>
@@ -7322,7 +6881,7 @@
       <c r="G59" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="H59" s="69" t="s">
+      <c r="H59" s="73" t="s">
         <v>92</v>
       </c>
     </row>
@@ -7382,7 +6941,7 @@
       <c r="E64" s="1"/>
       <c r="F64" s="1"/>
       <c r="G64" s="1"/>
-      <c r="H64" s="68" t="s">
+      <c r="H64" s="72" t="s">
         <v>75</v>
       </c>
     </row>
@@ -7394,7 +6953,7 @@
       <c r="E65" s="23"/>
       <c r="F65" s="23"/>
       <c r="G65" s="23"/>
-      <c r="H65" s="67" t="s">
+      <c r="H65" s="71" t="s">
         <v>89</v>
       </c>
     </row>
@@ -7434,7 +6993,7 @@
       <c r="E68" s="19"/>
       <c r="F68" s="19"/>
       <c r="G68" s="19"/>
-      <c r="H68" s="66" t="s">
+      <c r="H68" s="70" t="s">
         <v>75</v>
       </c>
     </row>
@@ -7446,7 +7005,7 @@
       <c r="E69" s="23"/>
       <c r="F69" s="23"/>
       <c r="G69" s="23"/>
-      <c r="H69" s="67" t="s">
+      <c r="H69" s="71" t="s">
         <v>78</v>
       </c>
     </row>
@@ -7548,7 +7107,7 @@
       <c r="G76" s="52" t="s">
         <v>75</v>
       </c>
-      <c r="H76" s="66" t="s">
+      <c r="H76" s="70" t="s">
         <v>75</v>
       </c>
     </row>
@@ -7562,7 +7121,7 @@
       <c r="G77" s="53" t="s">
         <v>105</v>
       </c>
-      <c r="H77" s="69" t="s">
+      <c r="H77" s="73" t="s">
         <v>106</v>
       </c>
     </row>
@@ -7576,7 +7135,7 @@
       <c r="G78" s="46" t="s">
         <v>58</v>
       </c>
-      <c r="H78" s="68" t="s">
+      <c r="H78" s="72" t="s">
         <v>75</v>
       </c>
     </row>
@@ -7590,7 +7149,7 @@
       <c r="G79" s="47" t="s">
         <v>87</v>
       </c>
-      <c r="H79" s="69" t="s">
+      <c r="H79" s="73" t="s">
         <v>107</v>
       </c>
     </row>
@@ -7602,7 +7161,7 @@
       <c r="E80" s="1"/>
       <c r="F80" s="1"/>
       <c r="G80" s="47"/>
-      <c r="H80" s="68" t="s">
+      <c r="H80" s="72" t="s">
         <v>108</v>
       </c>
     </row>
@@ -7614,7 +7173,7 @@
       <c r="E81" s="1"/>
       <c r="F81" s="1"/>
       <c r="G81" s="47"/>
-      <c r="H81" s="69" t="s">
+      <c r="H81" s="73" t="s">
         <v>109</v>
       </c>
     </row>
@@ -7816,7 +7375,7 @@
       <c r="G97" s="55" t="s">
         <v>59</v>
       </c>
-      <c r="H97" s="66" t="s">
+      <c r="H97" s="70" t="s">
         <v>75</v>
       </c>
     </row>
@@ -7830,7 +7389,7 @@
       <c r="G98" s="56" t="s">
         <v>118</v>
       </c>
-      <c r="H98" s="69" t="s">
+      <c r="H98" s="73" t="s">
         <v>105</v>
       </c>
     </row>
@@ -7844,7 +7403,7 @@
       <c r="G99" s="57" t="s">
         <v>12</v>
       </c>
-      <c r="H99" s="69"/>
+      <c r="H99" s="73"/>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" s="25"/>
@@ -7856,7 +7415,7 @@
       <c r="G100" s="56" t="s">
         <v>61</v>
       </c>
-      <c r="H100" s="69"/>
+      <c r="H100" s="73"/>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" s="25"/>
@@ -7865,10 +7424,10 @@
       <c r="D101" s="1"/>
       <c r="E101" s="1"/>
       <c r="F101" s="1"/>
-      <c r="G101" s="70" t="s">
+      <c r="G101" s="74" t="s">
         <v>75</v>
       </c>
-      <c r="H101" s="69"/>
+      <c r="H101" s="73"/>
     </row>
     <row r="102" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A102" s="21"/>
@@ -7880,7 +7439,7 @@
       <c r="G102" s="54" t="s">
         <v>119</v>
       </c>
-      <c r="H102" s="67"/>
+      <c r="H102" s="71"/>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B103" s="31"/>
@@ -8675,13 +8234,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82C34503-2CEC-4D68-80CD-B28E1A8DE2C4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C9482BC0-D9A0-4F2E-A662-55F6A6E1E8C5}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{21680000-0FA8-4848-A547-28CF206D5CC1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DA586971-1ADE-4638-9DB3-7A0A07ABD948}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5799426A-8929-4C41-8FE8-4FA90918C70D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA842A77-17E4-4803-881D-F58312C9A224}"/>
 </file>
--- a/Plannings 2026 S26.xlsx
+++ b/Plannings 2026 S26.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="8_{A23AA2D1-9819-4B65-9C3A-D83FC30F8B22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DCE23DB7-D103-4D89-99E7-0D32315F5783}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="8_{A23AA2D1-9819-4B65-9C3A-D83FC30F8B22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{47D258CF-975F-4986-A9AD-0C2B3793AEDE}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="153">
   <si>
     <t>Planning des salariés du 22/06/2026 au 28/06/2026</t>
   </si>
@@ -210,9 +210,6 @@
     <t>13:45/15:45</t>
   </si>
   <si>
-    <t>17:00/18:00</t>
-  </si>
-  <si>
     <t>08:50/10:00</t>
   </si>
   <si>
@@ -478,6 +475,12 @@
   </si>
   <si>
     <t>09:45/13:00</t>
+  </si>
+  <si>
+    <t>16:00/19:00</t>
+  </si>
+  <si>
+    <t>16:30/18:00</t>
   </si>
 </sst>
 </file>
@@ -991,7 +994,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1027,9 +1030,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1215,6 +1215,24 @@
     <xf numFmtId="0" fontId="16" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6027,6 +6045,94 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="3048000" y="2295525"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="120" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1AD1DE96-4C49-40A8-BEB7-1693E16AFBC2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3048000" y="5915025"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="121" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FDD7FE20-7B57-417D-A345-88667E1FD488}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3048000" y="6296025"/>
           <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -6437,208 +6543,208 @@
       <c r="H2" s="12"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B3" s="61" t="s">
+      <c r="B3" s="60" t="s">
+        <v>139</v>
+      </c>
+      <c r="C3" s="61"/>
+      <c r="D3" s="61"/>
+      <c r="E3" s="61"/>
+      <c r="F3" s="61"/>
+      <c r="G3" s="61"/>
+      <c r="H3" s="62"/>
+    </row>
+    <row r="4" spans="1:8" s="63" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="B4" s="64" t="s">
         <v>140</v>
       </c>
-      <c r="C3" s="62"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="63"/>
-    </row>
-    <row r="4" spans="1:8" s="64" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="B4" s="65" t="s">
+      <c r="C4" s="64" t="s">
         <v>141</v>
       </c>
-      <c r="C4" s="65" t="s">
+      <c r="D4" s="64" t="s">
         <v>142</v>
       </c>
-      <c r="D4" s="65" t="s">
+      <c r="E4" s="64" t="s">
         <v>143</v>
       </c>
-      <c r="E4" s="65" t="s">
+      <c r="F4" s="64" t="s">
         <v>144</v>
       </c>
-      <c r="F4" s="65" t="s">
+      <c r="G4" s="64" t="s">
         <v>145</v>
       </c>
-      <c r="G4" s="65" t="s">
-        <v>146</v>
-      </c>
-      <c r="H4" s="65" t="s">
-        <v>75</v>
+      <c r="H4" s="64" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="16" t="s">
+      <c r="A5" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="16" t="s">
+      <c r="D5" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="16" t="s">
+      <c r="E5" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="F5" s="16" t="s">
+      <c r="F5" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="G5" s="16" t="s">
+      <c r="G5" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="H5" s="16" t="s">
+      <c r="H5" s="15" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="17" t="s">
+      <c r="A6" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="18"/>
-      <c r="C6" s="19"/>
-      <c r="D6" s="19"/>
-      <c r="E6" s="19"/>
-      <c r="F6" s="19"/>
-      <c r="G6" s="55" t="s">
+      <c r="B6" s="17"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="54" t="s">
         <v>12</v>
       </c>
-      <c r="H6" s="20"/>
+      <c r="H6" s="19"/>
     </row>
     <row r="7" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="21"/>
-      <c r="B7" s="22"/>
-      <c r="C7" s="23"/>
-      <c r="D7" s="23"/>
-      <c r="E7" s="23"/>
-      <c r="F7" s="23"/>
-      <c r="G7" s="58" t="s">
+      <c r="A7" s="20"/>
+      <c r="B7" s="21"/>
+      <c r="C7" s="22"/>
+      <c r="D7" s="22"/>
+      <c r="E7" s="22"/>
+      <c r="F7" s="22"/>
+      <c r="G7" s="57" t="s">
         <v>13</v>
       </c>
-      <c r="H7" s="24"/>
+      <c r="H7" s="23"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="17" t="s">
+      <c r="A8" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="19"/>
-      <c r="C8" s="19"/>
-      <c r="D8" s="42" t="s">
+      <c r="B8" s="18"/>
+      <c r="C8" s="18"/>
+      <c r="D8" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="E8" s="19"/>
-      <c r="F8" s="19"/>
-      <c r="G8" s="19"/>
-      <c r="H8" s="20"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="19"/>
     </row>
     <row r="9" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="21"/>
-      <c r="B9" s="23"/>
-      <c r="C9" s="23"/>
-      <c r="D9" s="43" t="s">
+      <c r="A9" s="20"/>
+      <c r="B9" s="22"/>
+      <c r="C9" s="22"/>
+      <c r="D9" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="E9" s="23"/>
-      <c r="F9" s="23"/>
-      <c r="G9" s="23"/>
-      <c r="H9" s="24"/>
+      <c r="E9" s="22"/>
+      <c r="F9" s="22"/>
+      <c r="G9" s="22"/>
+      <c r="H9" s="23"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="17" t="s">
+      <c r="A10" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="51" t="s">
+      <c r="B10" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="51" t="s">
+      <c r="C10" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="D10" s="71" t="s">
+      <c r="D10" s="75" t="s">
         <v>19</v>
       </c>
-      <c r="E10" s="51" t="s">
+      <c r="E10" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="F10" s="51" t="s">
+      <c r="F10" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="G10" s="51"/>
-      <c r="H10" s="59"/>
+      <c r="G10" s="49"/>
+      <c r="H10" s="76"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="25"/>
-      <c r="B11" s="59" t="s">
+      <c r="A11" s="24"/>
+      <c r="B11" s="58" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="59" t="s">
+      <c r="C11" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="D11" s="72" t="s">
+      <c r="D11" s="71" t="s">
         <v>23</v>
       </c>
-      <c r="E11" s="59" t="s">
+      <c r="E11" s="58" t="s">
+        <v>149</v>
+      </c>
+      <c r="F11" s="58" t="s">
         <v>150</v>
       </c>
-      <c r="F11" s="59" t="s">
-        <v>151</v>
-      </c>
-      <c r="G11" s="59"/>
-      <c r="H11" s="59"/>
+      <c r="G11" s="58"/>
+      <c r="H11" s="77"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="25"/>
-      <c r="B12" s="71" t="s">
+      <c r="A12" s="24"/>
+      <c r="B12" s="70" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="59"/>
-      <c r="D12" s="51" t="s">
+      <c r="C12" s="58"/>
+      <c r="D12" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="E12" s="73" t="s">
+      <c r="E12" s="72" t="s">
         <v>20</v>
       </c>
-      <c r="F12" s="59"/>
-      <c r="G12" s="59"/>
-      <c r="H12" s="59"/>
+      <c r="F12" s="58"/>
+      <c r="G12" s="58"/>
+      <c r="H12" s="77"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="25"/>
-      <c r="B13" s="72" t="s">
+      <c r="A13" s="24"/>
+      <c r="B13" s="71" t="s">
         <v>26</v>
       </c>
-      <c r="C13" s="59"/>
-      <c r="D13" s="59" t="s">
+      <c r="C13" s="58"/>
+      <c r="D13" s="58" t="s">
         <v>27</v>
       </c>
-      <c r="E13" s="74" t="s">
+      <c r="E13" s="73" t="s">
         <v>24</v>
       </c>
-      <c r="F13" s="59"/>
-      <c r="G13" s="59"/>
-      <c r="H13" s="59"/>
+      <c r="F13" s="58"/>
+      <c r="G13" s="58"/>
+      <c r="H13" s="77"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="25"/>
-      <c r="B14" s="72"/>
-      <c r="C14" s="59"/>
-      <c r="D14" s="73" t="s">
+      <c r="A14" s="24"/>
+      <c r="B14" s="71"/>
+      <c r="C14" s="58"/>
+      <c r="D14" s="72" t="s">
         <v>20</v>
       </c>
-      <c r="E14" s="51" t="s">
+      <c r="E14" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="F14" s="59"/>
-      <c r="G14" s="59"/>
-      <c r="H14" s="59"/>
+      <c r="F14" s="58"/>
+      <c r="G14" s="58"/>
+      <c r="H14" s="77"/>
     </row>
     <row r="15" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="21"/>
-      <c r="B15" s="72"/>
+      <c r="A15" s="20"/>
+      <c r="B15" s="78"/>
       <c r="C15" s="59"/>
       <c r="D15" s="74" t="s">
         <v>29</v>
@@ -6648,100 +6754,100 @@
       </c>
       <c r="F15" s="59"/>
       <c r="G15" s="59"/>
-      <c r="H15" s="59"/>
+      <c r="H15" s="79"/>
     </row>
     <row r="16" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="27" t="s">
+      <c r="A16" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="B16" s="28"/>
-      <c r="C16" s="29"/>
-      <c r="D16" s="29"/>
-      <c r="E16" s="29"/>
-      <c r="F16" s="29"/>
-      <c r="G16" s="29"/>
-      <c r="H16" s="30"/>
+      <c r="B16" s="27"/>
+      <c r="C16" s="28"/>
+      <c r="D16" s="28"/>
+      <c r="E16" s="28"/>
+      <c r="F16" s="28"/>
+      <c r="G16" s="28"/>
+      <c r="H16" s="29"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="13" t="s">
+      <c r="A17" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="B17" s="51" t="s">
+      <c r="B17" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="C17" s="51" t="s">
+      <c r="C17" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="D17" s="51" t="s">
+      <c r="D17" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="E17" s="59"/>
-      <c r="F17" s="51" t="s">
+      <c r="E17" s="49"/>
+      <c r="F17" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="G17" s="51" t="s">
+      <c r="G17" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="H17" s="59"/>
+      <c r="H17" s="76"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="13"/>
-      <c r="B18" s="59" t="s">
-        <v>137</v>
-      </c>
-      <c r="C18" s="59" t="s">
+      <c r="A18" s="24"/>
+      <c r="B18" s="58" t="s">
+        <v>136</v>
+      </c>
+      <c r="C18" s="58" t="s">
+        <v>146</v>
+      </c>
+      <c r="D18" s="58" t="s">
+        <v>33</v>
+      </c>
+      <c r="E18" s="58"/>
+      <c r="F18" s="58" t="s">
         <v>147</v>
       </c>
-      <c r="D18" s="59" t="s">
-        <v>33</v>
-      </c>
-      <c r="E18" s="59"/>
-      <c r="F18" s="59" t="s">
+      <c r="G18" s="58" t="s">
         <v>148</v>
       </c>
-      <c r="G18" s="59" t="s">
-        <v>149</v>
-      </c>
-      <c r="H18" s="59"/>
+      <c r="H18" s="77"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="13"/>
-      <c r="B19" s="59"/>
-      <c r="C19" s="59"/>
-      <c r="D19" s="71" t="s">
+      <c r="A19" s="24"/>
+      <c r="B19" s="58"/>
+      <c r="C19" s="58"/>
+      <c r="D19" s="70" t="s">
         <v>34</v>
       </c>
-      <c r="E19" s="59"/>
-      <c r="F19" s="59"/>
-      <c r="G19" s="59"/>
-      <c r="H19" s="59"/>
+      <c r="E19" s="58"/>
+      <c r="F19" s="58"/>
+      <c r="G19" s="58"/>
+      <c r="H19" s="77"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="13"/>
-      <c r="B20" s="59"/>
-      <c r="C20" s="59"/>
-      <c r="D20" s="72" t="s">
+      <c r="A20" s="24"/>
+      <c r="B20" s="58"/>
+      <c r="C20" s="58"/>
+      <c r="D20" s="71" t="s">
         <v>35</v>
       </c>
-      <c r="E20" s="59"/>
-      <c r="F20" s="59"/>
-      <c r="G20" s="59"/>
-      <c r="H20" s="59"/>
+      <c r="E20" s="58"/>
+      <c r="F20" s="58"/>
+      <c r="G20" s="58"/>
+      <c r="H20" s="77"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="13"/>
-      <c r="B21" s="59"/>
-      <c r="C21" s="59"/>
-      <c r="D21" s="51" t="s">
+      <c r="A21" s="24"/>
+      <c r="B21" s="58"/>
+      <c r="C21" s="58"/>
+      <c r="D21" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="E21" s="59"/>
-      <c r="F21" s="59"/>
-      <c r="G21" s="59"/>
-      <c r="H21" s="59"/>
+      <c r="E21" s="58"/>
+      <c r="F21" s="58"/>
+      <c r="G21" s="58"/>
+      <c r="H21" s="77"/>
     </row>
     <row r="22" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="13"/>
+      <c r="A22" s="20"/>
       <c r="B22" s="59"/>
       <c r="C22" s="59"/>
       <c r="D22" s="59" t="s">
@@ -6750,321 +6856,325 @@
       <c r="E22" s="59"/>
       <c r="F22" s="59"/>
       <c r="G22" s="59"/>
-      <c r="H22" s="59"/>
+      <c r="H22" s="79"/>
     </row>
     <row r="23" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="38" t="s">
+      <c r="A23" s="37" t="s">
         <v>37</v>
       </c>
-      <c r="B23" s="39"/>
-      <c r="C23" s="40"/>
-      <c r="D23" s="40"/>
-      <c r="E23" s="40"/>
-      <c r="F23" s="40"/>
-      <c r="G23" s="40"/>
-      <c r="H23" s="41"/>
+      <c r="B23" s="38"/>
+      <c r="C23" s="39"/>
+      <c r="D23" s="39"/>
+      <c r="E23" s="39"/>
+      <c r="F23" s="39"/>
+      <c r="G23" s="39"/>
+      <c r="H23" s="40"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="17" t="s">
+      <c r="A24" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="B24" s="55" t="s">
+      <c r="B24" s="54" t="s">
         <v>39</v>
       </c>
-      <c r="C24" s="55" t="s">
+      <c r="C24" s="54" t="s">
         <v>39</v>
       </c>
-      <c r="D24" s="55" t="s">
+      <c r="D24" s="54" t="s">
         <v>39</v>
       </c>
-      <c r="E24" s="55" t="s">
+      <c r="E24" s="54" t="s">
         <v>39</v>
       </c>
-      <c r="F24" s="42" t="s">
-        <v>40</v>
-      </c>
-      <c r="G24" s="19"/>
-      <c r="H24" s="20"/>
+      <c r="F24" s="49" t="s">
+        <v>18</v>
+      </c>
+      <c r="G24" s="18"/>
+      <c r="H24" s="19"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="25"/>
-      <c r="B25" s="56" t="s">
+      <c r="A25" s="24"/>
+      <c r="B25" s="55" t="s">
         <v>41</v>
       </c>
-      <c r="C25" s="56" t="s">
+      <c r="C25" s="55" t="s">
         <v>41</v>
       </c>
-      <c r="D25" s="56" t="s">
+      <c r="D25" s="55" t="s">
         <v>42</v>
       </c>
-      <c r="E25" s="56" t="s">
+      <c r="E25" s="55" t="s">
         <v>43</v>
       </c>
-      <c r="F25" s="44" t="s">
-        <v>44</v>
+      <c r="F25" s="58" t="s">
+        <v>151</v>
       </c>
       <c r="G25" s="1"/>
-      <c r="H25" s="26"/>
+      <c r="H25" s="25"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="25"/>
+      <c r="A26" s="24"/>
       <c r="B26" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="D26" s="57" t="s">
+      <c r="D26" s="56" t="s">
         <v>39</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F26" s="44"/>
+      <c r="F26" s="72" t="s">
+        <v>40</v>
+      </c>
       <c r="G26" s="1"/>
-      <c r="H26" s="26"/>
+      <c r="H26" s="25"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="25"/>
+      <c r="A27" s="24"/>
       <c r="B27" s="1" t="s">
         <v>47</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="D27" s="56" t="s">
+      <c r="D27" s="55" t="s">
         <v>49</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="F27" s="44"/>
+      <c r="F27" s="73" t="s">
+        <v>44</v>
+      </c>
       <c r="G27" s="1"/>
-      <c r="H27" s="26"/>
+      <c r="H27" s="25"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="25"/>
-      <c r="B28" s="57" t="s">
+      <c r="A28" s="24"/>
+      <c r="B28" s="56" t="s">
         <v>39</v>
       </c>
-      <c r="C28" s="57" t="s">
+      <c r="C28" s="56" t="s">
         <v>39</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>46</v>
       </c>
       <c r="E28" s="1"/>
-      <c r="F28" s="44"/>
+      <c r="F28" s="73"/>
       <c r="G28" s="1"/>
-      <c r="H28" s="26"/>
+      <c r="H28" s="25"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="25"/>
-      <c r="B29" s="56" t="s">
+      <c r="A29" s="24"/>
+      <c r="B29" s="55" t="s">
         <v>51</v>
       </c>
-      <c r="C29" s="56" t="s">
+      <c r="C29" s="55" t="s">
         <v>52</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>53</v>
       </c>
       <c r="E29" s="1"/>
-      <c r="F29" s="44"/>
+      <c r="F29" s="73"/>
       <c r="G29" s="1"/>
-      <c r="H29" s="26"/>
+      <c r="H29" s="25"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="25"/>
-      <c r="B30" s="56"/>
+      <c r="A30" s="24"/>
+      <c r="B30" s="55"/>
       <c r="C30" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D30" s="57" t="s">
+      <c r="D30" s="56" t="s">
         <v>39</v>
       </c>
       <c r="E30" s="1"/>
-      <c r="F30" s="44"/>
+      <c r="F30" s="73"/>
       <c r="G30" s="1"/>
-      <c r="H30" s="26"/>
+      <c r="H30" s="25"/>
     </row>
     <row r="31" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="21"/>
-      <c r="B31" s="58"/>
-      <c r="C31" s="23" t="s">
+      <c r="A31" s="20"/>
+      <c r="B31" s="57"/>
+      <c r="C31" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="D31" s="58" t="s">
+      <c r="D31" s="57" t="s">
         <v>55</v>
       </c>
-      <c r="E31" s="23"/>
-      <c r="F31" s="43"/>
-      <c r="G31" s="23"/>
-      <c r="H31" s="24"/>
+      <c r="E31" s="22"/>
+      <c r="F31" s="74"/>
+      <c r="G31" s="22"/>
+      <c r="H31" s="23"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="17" t="s">
+      <c r="A32" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="B32" s="19"/>
-      <c r="C32" s="19"/>
-      <c r="D32" s="19"/>
-      <c r="E32" s="19"/>
-      <c r="F32" s="19"/>
-      <c r="G32" s="55" t="s">
+      <c r="B32" s="18"/>
+      <c r="C32" s="18"/>
+      <c r="D32" s="18"/>
+      <c r="E32" s="18"/>
+      <c r="F32" s="18"/>
+      <c r="G32" s="54" t="s">
         <v>12</v>
       </c>
-      <c r="H32" s="20"/>
+      <c r="H32" s="19"/>
     </row>
     <row r="33" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="21"/>
-      <c r="B33" s="23"/>
-      <c r="C33" s="23"/>
-      <c r="D33" s="23"/>
-      <c r="E33" s="23"/>
-      <c r="F33" s="23"/>
-      <c r="G33" s="58" t="s">
+      <c r="A33" s="20"/>
+      <c r="B33" s="22"/>
+      <c r="C33" s="22"/>
+      <c r="D33" s="22"/>
+      <c r="E33" s="22"/>
+      <c r="F33" s="22"/>
+      <c r="G33" s="57" t="s">
         <v>13</v>
       </c>
-      <c r="H33" s="24"/>
+      <c r="H33" s="23"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="17" t="s">
+      <c r="A34" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="B34" s="19" t="s">
+      <c r="B34" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="C34" s="49" t="s">
+      <c r="C34" s="48" t="s">
         <v>58</v>
       </c>
-      <c r="D34" s="55" t="s">
+      <c r="D34" s="54" t="s">
         <v>59</v>
       </c>
-      <c r="E34" s="19" t="s">
+      <c r="E34" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="F34" s="19"/>
-      <c r="G34" s="19" t="s">
+      <c r="F34" s="18"/>
+      <c r="G34" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="H34" s="20" t="s">
+      <c r="H34" s="19" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" s="25"/>
-      <c r="B35" s="59" t="s">
-        <v>138</v>
-      </c>
-      <c r="C35" s="47" t="s">
+      <c r="A35" s="24"/>
+      <c r="B35" s="58" t="s">
+        <v>137</v>
+      </c>
+      <c r="C35" s="46" t="s">
         <v>60</v>
       </c>
-      <c r="D35" s="56" t="s">
+      <c r="D35" s="55" t="s">
         <v>61</v>
       </c>
-      <c r="E35" s="1" t="s">
-        <v>62</v>
+      <c r="E35" s="58" t="s">
+        <v>152</v>
       </c>
       <c r="F35" s="1"/>
       <c r="G35" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="H35" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="H35" s="26" t="s">
-        <v>64</v>
-      </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="25"/>
+      <c r="A36" s="24"/>
       <c r="B36" s="1"/>
-      <c r="C36" s="47"/>
+      <c r="C36" s="46"/>
       <c r="D36" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E36" s="45" t="s">
+      <c r="E36" s="44" t="s">
         <v>15</v>
       </c>
       <c r="F36" s="1"/>
-      <c r="G36" s="45" t="s">
+      <c r="G36" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="H36" s="26"/>
+      <c r="H36" s="25"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37" s="25"/>
+      <c r="A37" s="24"/>
       <c r="B37" s="1"/>
-      <c r="C37" s="47"/>
+      <c r="C37" s="46"/>
       <c r="D37" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E37" s="43" t="s">
+        <v>36</v>
+      </c>
+      <c r="F37" s="1"/>
+      <c r="G37" s="43" t="s">
         <v>65</v>
       </c>
-      <c r="E37" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="F37" s="1"/>
-      <c r="G37" s="44" t="s">
-        <v>66</v>
-      </c>
-      <c r="H37" s="26"/>
+      <c r="H37" s="25"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="25"/>
+      <c r="A38" s="24"/>
       <c r="B38" s="1"/>
-      <c r="C38" s="47"/>
-      <c r="D38" s="57" t="s">
+      <c r="C38" s="46"/>
+      <c r="D38" s="56" t="s">
         <v>59</v>
       </c>
-      <c r="E38" s="44"/>
+      <c r="E38" s="43"/>
       <c r="F38" s="1"/>
       <c r="G38" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="H38" s="26"/>
+      <c r="H38" s="25"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="25"/>
+      <c r="A39" s="24"/>
       <c r="B39" s="1"/>
-      <c r="C39" s="47"/>
-      <c r="D39" s="56" t="s">
-        <v>67</v>
-      </c>
-      <c r="E39" s="44"/>
+      <c r="C39" s="46"/>
+      <c r="D39" s="55" t="s">
+        <v>66</v>
+      </c>
+      <c r="E39" s="43"/>
       <c r="F39" s="1"/>
       <c r="G39" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="H39" s="26"/>
+      <c r="H39" s="25"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="25"/>
+      <c r="A40" s="24"/>
       <c r="B40" s="1"/>
-      <c r="C40" s="47"/>
-      <c r="D40" s="45" t="s">
+      <c r="C40" s="46"/>
+      <c r="D40" s="44" t="s">
+        <v>67</v>
+      </c>
+      <c r="E40" s="43"/>
+      <c r="F40" s="1"/>
+      <c r="G40" s="45" t="s">
         <v>68</v>
       </c>
-      <c r="E40" s="44"/>
-      <c r="F40" s="1"/>
-      <c r="G40" s="46" t="s">
+      <c r="H40" s="25"/>
+    </row>
+    <row r="41" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="20"/>
+      <c r="B41" s="22"/>
+      <c r="C41" s="47"/>
+      <c r="D41" s="42" t="s">
         <v>69</v>
       </c>
-      <c r="H40" s="26"/>
-    </row>
-    <row r="41" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="21"/>
-      <c r="B41" s="23"/>
-      <c r="C41" s="48"/>
-      <c r="D41" s="43" t="s">
+      <c r="E41" s="42"/>
+      <c r="F41" s="22"/>
+      <c r="G41" s="47" t="s">
         <v>70</v>
       </c>
-      <c r="E41" s="43"/>
-      <c r="F41" s="23"/>
-      <c r="G41" s="48" t="s">
+      <c r="H41" s="23"/>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" s="32" t="s">
         <v>71</v>
-      </c>
-      <c r="H41" s="24"/>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" s="33" t="s">
-        <v>72</v>
       </c>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
@@ -7074,232 +7184,232 @@
       </c>
       <c r="F42" s="1"/>
       <c r="G42" s="1"/>
-      <c r="H42" s="26"/>
+      <c r="H42" s="25"/>
     </row>
     <row r="43" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="21"/>
-      <c r="B43" s="23"/>
-      <c r="C43" s="23"/>
-      <c r="D43" s="23"/>
-      <c r="E43" s="23" t="s">
-        <v>73</v>
-      </c>
-      <c r="F43" s="23"/>
-      <c r="G43" s="23"/>
-      <c r="H43" s="24"/>
+      <c r="A43" s="20"/>
+      <c r="B43" s="22"/>
+      <c r="C43" s="22"/>
+      <c r="D43" s="22"/>
+      <c r="E43" s="22" t="s">
+        <v>72</v>
+      </c>
+      <c r="F43" s="22"/>
+      <c r="G43" s="22"/>
+      <c r="H43" s="23"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="17" t="s">
+      <c r="A44" s="16" t="s">
+        <v>133</v>
+      </c>
+      <c r="B44" s="49" t="s">
         <v>134</v>
       </c>
-      <c r="B44" s="50" t="s">
-        <v>135</v>
-      </c>
-      <c r="C44" s="19"/>
-      <c r="D44" s="19" t="s">
+      <c r="C44" s="18"/>
+      <c r="D44" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="E44" s="19"/>
-      <c r="F44" s="19"/>
-      <c r="G44" s="52" t="s">
+      <c r="E44" s="18"/>
+      <c r="F44" s="18"/>
+      <c r="G44" s="51" t="s">
+        <v>74</v>
+      </c>
+      <c r="H44" s="19"/>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" s="24"/>
+      <c r="B45" s="1" t="s">
         <v>75</v>
-      </c>
-      <c r="H44" s="20"/>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" s="25"/>
-      <c r="B45" s="1" t="s">
-        <v>76</v>
       </c>
       <c r="C45" s="1"/>
       <c r="D45" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E45" s="1"/>
       <c r="F45" s="1"/>
-      <c r="G45" s="53" t="s">
-        <v>78</v>
-      </c>
-      <c r="H45" s="26"/>
+      <c r="G45" s="52" t="s">
+        <v>77</v>
+      </c>
+      <c r="H45" s="25"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="25"/>
-      <c r="B46" s="51" t="s">
-        <v>136</v>
+      <c r="A46" s="24"/>
+      <c r="B46" s="50" t="s">
+        <v>135</v>
       </c>
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
       <c r="E46" s="1"/>
       <c r="F46" s="1"/>
-      <c r="G46" s="53"/>
-      <c r="H46" s="26"/>
+      <c r="G46" s="52"/>
+      <c r="H46" s="25"/>
     </row>
     <row r="47" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="21"/>
-      <c r="B47" s="23" t="s">
+      <c r="A47" s="20"/>
+      <c r="B47" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="C47" s="22"/>
+      <c r="D47" s="22"/>
+      <c r="E47" s="22"/>
+      <c r="F47" s="22"/>
+      <c r="G47" s="53"/>
+      <c r="H47" s="23"/>
+    </row>
+    <row r="48" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="26" t="s">
         <v>79</v>
       </c>
-      <c r="C47" s="23"/>
-      <c r="D47" s="23"/>
-      <c r="E47" s="23"/>
-      <c r="F47" s="23"/>
-      <c r="G47" s="54"/>
-      <c r="H47" s="24"/>
-    </row>
-    <row r="48" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="27" t="s">
+      <c r="B48" s="27"/>
+      <c r="C48" s="28"/>
+      <c r="D48" s="28"/>
+      <c r="E48" s="28"/>
+      <c r="F48" s="28"/>
+      <c r="G48" s="28"/>
+      <c r="H48" s="29"/>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="B48" s="28"/>
-      <c r="C48" s="29"/>
-      <c r="D48" s="29"/>
-      <c r="E48" s="29"/>
-      <c r="F48" s="29"/>
-      <c r="G48" s="29"/>
-      <c r="H48" s="30"/>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49" s="17" t="s">
+      <c r="B49" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="C49" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="D49" s="18"/>
+      <c r="E49" s="18"/>
+      <c r="F49" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="G49" s="18"/>
+      <c r="H49" s="19" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="20"/>
+      <c r="B50" s="59" t="s">
+        <v>138</v>
+      </c>
+      <c r="C50" s="22" t="s">
+        <v>76</v>
+      </c>
+      <c r="D50" s="22"/>
+      <c r="E50" s="22"/>
+      <c r="F50" s="22" t="s">
         <v>81</v>
       </c>
-      <c r="B49" s="19" t="s">
+      <c r="G50" s="22"/>
+      <c r="H50" s="23" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="B51" s="18"/>
+      <c r="C51" s="18"/>
+      <c r="D51" s="18"/>
+      <c r="E51" s="18"/>
+      <c r="F51" s="18"/>
+      <c r="G51" s="18"/>
+      <c r="H51" s="65" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="20"/>
+      <c r="B52" s="22"/>
+      <c r="C52" s="22"/>
+      <c r="D52" s="22"/>
+      <c r="E52" s="22"/>
+      <c r="F52" s="22"/>
+      <c r="G52" s="22"/>
+      <c r="H52" s="66" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="33" t="s">
+        <v>84</v>
+      </c>
+      <c r="B53" s="34"/>
+      <c r="C53" s="35"/>
+      <c r="D53" s="35"/>
+      <c r="E53" s="35"/>
+      <c r="F53" s="35"/>
+      <c r="G53" s="35"/>
+      <c r="H53" s="36"/>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="B54" s="18"/>
+      <c r="C54" s="48" t="s">
+        <v>58</v>
+      </c>
+      <c r="D54" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="E54" s="18"/>
+      <c r="F54" s="18"/>
+      <c r="G54" s="48" t="s">
+        <v>58</v>
+      </c>
+      <c r="H54" s="19"/>
+    </row>
+    <row r="55" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="20"/>
+      <c r="B55" s="22"/>
+      <c r="C55" s="47" t="s">
+        <v>60</v>
+      </c>
+      <c r="D55" s="42" t="s">
+        <v>69</v>
+      </c>
+      <c r="E55" s="22"/>
+      <c r="F55" s="22"/>
+      <c r="G55" s="47" t="s">
+        <v>86</v>
+      </c>
+      <c r="H55" s="23"/>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="B56" s="18"/>
+      <c r="C56" s="18"/>
+      <c r="D56" s="18"/>
+      <c r="E56" s="18"/>
+      <c r="F56" s="18"/>
+      <c r="G56" s="51" t="s">
+        <v>74</v>
+      </c>
+      <c r="H56" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="C49" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="D49" s="19"/>
-      <c r="E49" s="19"/>
-      <c r="F49" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="G49" s="19"/>
-      <c r="H49" s="20" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="21"/>
-      <c r="B50" s="60" t="s">
-        <v>139</v>
-      </c>
-      <c r="C50" s="23" t="s">
-        <v>77</v>
-      </c>
-      <c r="D50" s="23"/>
-      <c r="E50" s="23"/>
-      <c r="F50" s="23" t="s">
-        <v>82</v>
-      </c>
-      <c r="G50" s="23"/>
-      <c r="H50" s="24" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A51" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="B51" s="19"/>
-      <c r="C51" s="19"/>
-      <c r="D51" s="19"/>
-      <c r="E51" s="19"/>
-      <c r="F51" s="19"/>
-      <c r="G51" s="19"/>
-      <c r="H51" s="66" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="21"/>
-      <c r="B52" s="23"/>
-      <c r="C52" s="23"/>
-      <c r="D52" s="23"/>
-      <c r="E52" s="23"/>
-      <c r="F52" s="23"/>
-      <c r="G52" s="23"/>
-      <c r="H52" s="67" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="34" t="s">
-        <v>85</v>
-      </c>
-      <c r="B53" s="35"/>
-      <c r="C53" s="36"/>
-      <c r="D53" s="36"/>
-      <c r="E53" s="36"/>
-      <c r="F53" s="36"/>
-      <c r="G53" s="36"/>
-      <c r="H53" s="37"/>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A54" s="17" t="s">
-        <v>86</v>
-      </c>
-      <c r="B54" s="19"/>
-      <c r="C54" s="49" t="s">
-        <v>58</v>
-      </c>
-      <c r="D54" s="42" t="s">
-        <v>68</v>
-      </c>
-      <c r="E54" s="19"/>
-      <c r="F54" s="19"/>
-      <c r="G54" s="49" t="s">
-        <v>58</v>
-      </c>
-      <c r="H54" s="20"/>
-    </row>
-    <row r="55" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="21"/>
-      <c r="B55" s="23"/>
-      <c r="C55" s="48" t="s">
-        <v>60</v>
-      </c>
-      <c r="D55" s="43" t="s">
-        <v>70</v>
-      </c>
-      <c r="E55" s="23"/>
-      <c r="F55" s="23"/>
-      <c r="G55" s="48" t="s">
-        <v>87</v>
-      </c>
-      <c r="H55" s="24"/>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A56" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="B56" s="19"/>
-      <c r="C56" s="19"/>
-      <c r="D56" s="19"/>
-      <c r="E56" s="19"/>
-      <c r="F56" s="19"/>
-      <c r="G56" s="52" t="s">
-        <v>75</v>
-      </c>
-      <c r="H56" s="20" t="s">
-        <v>18</v>
-      </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" s="25"/>
+      <c r="A57" s="24"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
       <c r="D57" s="1"/>
       <c r="E57" s="1"/>
       <c r="F57" s="1"/>
-      <c r="G57" s="53" t="s">
+      <c r="G57" s="52" t="s">
+        <v>88</v>
+      </c>
+      <c r="H57" s="25" t="s">
         <v>89</v>
       </c>
-      <c r="H57" s="26" t="s">
-        <v>90</v>
-      </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A58" s="25"/>
+      <c r="A58" s="24"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
       <c r="D58" s="1"/>
@@ -7308,151 +7418,151 @@
       <c r="G58" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="H58" s="68" t="s">
-        <v>75</v>
+      <c r="H58" s="67" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A59" s="25"/>
+      <c r="A59" s="24"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
       <c r="D59" s="1"/>
       <c r="E59" s="1"/>
       <c r="F59" s="1"/>
       <c r="G59" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="H59" s="68" t="s">
         <v>91</v>
       </c>
-      <c r="H59" s="69" t="s">
-        <v>92</v>
-      </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A60" s="25"/>
+      <c r="A60" s="24"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
       <c r="D60" s="1"/>
       <c r="E60" s="1"/>
       <c r="F60" s="1"/>
       <c r="G60" s="1"/>
-      <c r="H60" s="32" t="s">
+      <c r="H60" s="31" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61" s="25"/>
+      <c r="A61" s="24"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
       <c r="D61" s="1"/>
       <c r="E61" s="1"/>
       <c r="F61" s="1"/>
       <c r="G61" s="1"/>
-      <c r="H61" s="26" t="s">
-        <v>93</v>
+      <c r="H61" s="25" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A62" s="25"/>
+      <c r="A62" s="24"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
       <c r="D62" s="1"/>
       <c r="E62" s="1"/>
       <c r="F62" s="1"/>
       <c r="G62" s="1"/>
-      <c r="H62" s="32" t="s">
+      <c r="H62" s="31" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A63" s="25"/>
+      <c r="A63" s="24"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
       <c r="D63" s="1"/>
       <c r="E63" s="1"/>
       <c r="F63" s="1"/>
       <c r="G63" s="1"/>
-      <c r="H63" s="26" t="s">
-        <v>94</v>
+      <c r="H63" s="25" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A64" s="25"/>
+      <c r="A64" s="24"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
       <c r="D64" s="1"/>
       <c r="E64" s="1"/>
       <c r="F64" s="1"/>
       <c r="G64" s="1"/>
-      <c r="H64" s="68" t="s">
-        <v>75</v>
+      <c r="H64" s="67" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="65" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="21"/>
-      <c r="B65" s="23"/>
-      <c r="C65" s="23"/>
-      <c r="D65" s="23"/>
-      <c r="E65" s="23"/>
-      <c r="F65" s="23"/>
-      <c r="G65" s="23"/>
-      <c r="H65" s="67" t="s">
-        <v>89</v>
+      <c r="A65" s="20"/>
+      <c r="B65" s="22"/>
+      <c r="C65" s="22"/>
+      <c r="D65" s="22"/>
+      <c r="E65" s="22"/>
+      <c r="F65" s="22"/>
+      <c r="G65" s="22"/>
+      <c r="H65" s="66" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A66" s="17" t="s">
+      <c r="A66" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="B66" s="18"/>
+      <c r="C66" s="18"/>
+      <c r="D66" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="E66" s="18"/>
+      <c r="F66" s="18"/>
+      <c r="G66" s="18"/>
+      <c r="H66" s="19"/>
+    </row>
+    <row r="67" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="20"/>
+      <c r="B67" s="22"/>
+      <c r="C67" s="22"/>
+      <c r="D67" s="42" t="s">
+        <v>69</v>
+      </c>
+      <c r="E67" s="22"/>
+      <c r="F67" s="22"/>
+      <c r="G67" s="22"/>
+      <c r="H67" s="23"/>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="B66" s="19"/>
-      <c r="C66" s="19"/>
-      <c r="D66" s="42" t="s">
-        <v>68</v>
-      </c>
-      <c r="E66" s="19"/>
-      <c r="F66" s="19"/>
-      <c r="G66" s="19"/>
-      <c r="H66" s="20"/>
-    </row>
-    <row r="67" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="21"/>
-      <c r="B67" s="23"/>
-      <c r="C67" s="23"/>
-      <c r="D67" s="43" t="s">
-        <v>70</v>
-      </c>
-      <c r="E67" s="23"/>
-      <c r="F67" s="23"/>
-      <c r="G67" s="23"/>
-      <c r="H67" s="24"/>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A68" s="17" t="s">
+      <c r="B68" s="18"/>
+      <c r="C68" s="18"/>
+      <c r="D68" s="18"/>
+      <c r="E68" s="18"/>
+      <c r="F68" s="18"/>
+      <c r="G68" s="18"/>
+      <c r="H68" s="65" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="20"/>
+      <c r="B69" s="22"/>
+      <c r="C69" s="22"/>
+      <c r="D69" s="22"/>
+      <c r="E69" s="22"/>
+      <c r="F69" s="22"/>
+      <c r="G69" s="22"/>
+      <c r="H69" s="66" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" s="32" t="s">
         <v>96</v>
-      </c>
-      <c r="B68" s="19"/>
-      <c r="C68" s="19"/>
-      <c r="D68" s="19"/>
-      <c r="E68" s="19"/>
-      <c r="F68" s="19"/>
-      <c r="G68" s="19"/>
-      <c r="H68" s="66" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="21"/>
-      <c r="B69" s="23"/>
-      <c r="C69" s="23"/>
-      <c r="D69" s="23"/>
-      <c r="E69" s="23"/>
-      <c r="F69" s="23"/>
-      <c r="G69" s="23"/>
-      <c r="H69" s="67" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A70" s="33" t="s">
-        <v>97</v>
       </c>
       <c r="B70" s="1"/>
       <c r="C70" s="1" t="s">
@@ -7468,28 +7578,28 @@
         <v>18</v>
       </c>
       <c r="G70" s="1"/>
-      <c r="H70" s="26"/>
+      <c r="H70" s="25"/>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A71" s="25"/>
+      <c r="A71" s="24"/>
       <c r="B71" s="1"/>
       <c r="C71" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D71" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="D71" s="1" t="s">
+      <c r="E71" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="E71" s="1" t="s">
+      <c r="F71" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="F71" s="1" t="s">
-        <v>101</v>
-      </c>
       <c r="G71" s="1"/>
-      <c r="H71" s="26"/>
+      <c r="H71" s="25"/>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A72" s="25"/>
+      <c r="A72" s="24"/>
       <c r="B72" s="1"/>
       <c r="C72" s="1"/>
       <c r="D72" s="2" t="s">
@@ -7498,240 +7608,240 @@
       <c r="E72" s="1"/>
       <c r="F72" s="1"/>
       <c r="G72" s="1"/>
-      <c r="H72" s="26"/>
+      <c r="H72" s="25"/>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A73" s="25"/>
+      <c r="A73" s="24"/>
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
       <c r="D73" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E73" s="1"/>
       <c r="F73" s="1"/>
       <c r="G73" s="1"/>
-      <c r="H73" s="26"/>
+      <c r="H73" s="25"/>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A74" s="25"/>
+      <c r="A74" s="24"/>
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
-      <c r="D74" s="45" t="s">
+      <c r="D74" s="44" t="s">
         <v>15</v>
       </c>
       <c r="E74" s="1"/>
       <c r="F74" s="1"/>
       <c r="G74" s="1"/>
-      <c r="H74" s="26"/>
+      <c r="H74" s="25"/>
     </row>
     <row r="75" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="21"/>
-      <c r="B75" s="23"/>
-      <c r="C75" s="23"/>
-      <c r="D75" s="43" t="s">
+      <c r="A75" s="20"/>
+      <c r="B75" s="22"/>
+      <c r="C75" s="22"/>
+      <c r="D75" s="42" t="s">
+        <v>102</v>
+      </c>
+      <c r="E75" s="22"/>
+      <c r="F75" s="22"/>
+      <c r="G75" s="22"/>
+      <c r="H75" s="23"/>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="E75" s="23"/>
-      <c r="F75" s="23"/>
-      <c r="G75" s="23"/>
-      <c r="H75" s="24"/>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A76" s="17" t="s">
-        <v>104</v>
-      </c>
-      <c r="B76" s="19"/>
-      <c r="C76" s="19"/>
-      <c r="D76" s="19"/>
-      <c r="E76" s="19"/>
-      <c r="F76" s="19"/>
-      <c r="G76" s="52" t="s">
-        <v>75</v>
-      </c>
-      <c r="H76" s="66" t="s">
-        <v>75</v>
+      <c r="B76" s="18"/>
+      <c r="C76" s="18"/>
+      <c r="D76" s="18"/>
+      <c r="E76" s="18"/>
+      <c r="F76" s="18"/>
+      <c r="G76" s="51" t="s">
+        <v>74</v>
+      </c>
+      <c r="H76" s="65" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A77" s="25"/>
+      <c r="A77" s="24"/>
       <c r="B77" s="1"/>
       <c r="C77" s="1"/>
       <c r="D77" s="1"/>
       <c r="E77" s="1"/>
       <c r="F77" s="1"/>
-      <c r="G77" s="53" t="s">
+      <c r="G77" s="52" t="s">
+        <v>104</v>
+      </c>
+      <c r="H77" s="68" t="s">
         <v>105</v>
       </c>
-      <c r="H77" s="69" t="s">
-        <v>106</v>
-      </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A78" s="25"/>
+      <c r="A78" s="24"/>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
       <c r="D78" s="1"/>
       <c r="E78" s="1"/>
       <c r="F78" s="1"/>
-      <c r="G78" s="46" t="s">
+      <c r="G78" s="45" t="s">
         <v>58</v>
       </c>
-      <c r="H78" s="68" t="s">
-        <v>75</v>
+      <c r="H78" s="67" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A79" s="25"/>
+      <c r="A79" s="24"/>
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
       <c r="D79" s="1"/>
       <c r="E79" s="1"/>
       <c r="F79" s="1"/>
-      <c r="G79" s="47" t="s">
-        <v>87</v>
-      </c>
-      <c r="H79" s="69" t="s">
-        <v>107</v>
+      <c r="G79" s="46" t="s">
+        <v>86</v>
+      </c>
+      <c r="H79" s="68" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A80" s="25"/>
+      <c r="A80" s="24"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
       <c r="D80" s="1"/>
       <c r="E80" s="1"/>
       <c r="F80" s="1"/>
-      <c r="G80" s="47"/>
-      <c r="H80" s="68" t="s">
-        <v>108</v>
+      <c r="G80" s="46"/>
+      <c r="H80" s="67" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A81" s="25"/>
+      <c r="A81" s="24"/>
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
       <c r="D81" s="1"/>
       <c r="E81" s="1"/>
       <c r="F81" s="1"/>
-      <c r="G81" s="47"/>
-      <c r="H81" s="69" t="s">
-        <v>109</v>
+      <c r="G81" s="46"/>
+      <c r="H81" s="68" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A82" s="25"/>
+      <c r="A82" s="24"/>
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
       <c r="D82" s="1"/>
       <c r="E82" s="1"/>
       <c r="F82" s="1"/>
-      <c r="G82" s="47"/>
-      <c r="H82" s="32" t="s">
+      <c r="G82" s="46"/>
+      <c r="H82" s="31" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="83" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="21"/>
-      <c r="B83" s="23"/>
-      <c r="C83" s="23"/>
-      <c r="D83" s="23"/>
-      <c r="E83" s="23"/>
-      <c r="F83" s="23"/>
-      <c r="G83" s="48"/>
-      <c r="H83" s="24" t="s">
+      <c r="A83" s="20"/>
+      <c r="B83" s="22"/>
+      <c r="C83" s="22"/>
+      <c r="D83" s="22"/>
+      <c r="E83" s="22"/>
+      <c r="F83" s="22"/>
+      <c r="G83" s="47"/>
+      <c r="H83" s="23" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="26" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="84" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="27" t="s">
+      <c r="B84" s="27"/>
+      <c r="C84" s="28"/>
+      <c r="D84" s="28"/>
+      <c r="E84" s="28"/>
+      <c r="F84" s="28"/>
+      <c r="G84" s="28"/>
+      <c r="H84" s="29"/>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" s="16" t="s">
         <v>111</v>
       </c>
-      <c r="B84" s="28"/>
-      <c r="C84" s="29"/>
-      <c r="D84" s="29"/>
-      <c r="E84" s="29"/>
-      <c r="F84" s="29"/>
-      <c r="G84" s="29"/>
-      <c r="H84" s="30"/>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A85" s="17" t="s">
-        <v>112</v>
-      </c>
-      <c r="B85" s="19"/>
-      <c r="C85" s="19"/>
-      <c r="D85" s="19"/>
-      <c r="E85" s="19"/>
-      <c r="F85" s="19"/>
-      <c r="G85" s="55" t="s">
+      <c r="B85" s="18"/>
+      <c r="C85" s="18"/>
+      <c r="D85" s="18"/>
+      <c r="E85" s="18"/>
+      <c r="F85" s="18"/>
+      <c r="G85" s="54" t="s">
         <v>12</v>
       </c>
-      <c r="H85" s="20"/>
+      <c r="H85" s="19"/>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A86" s="25"/>
+      <c r="A86" s="24"/>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
       <c r="D86" s="1"/>
       <c r="E86" s="1"/>
       <c r="F86" s="1"/>
-      <c r="G86" s="56" t="s">
+      <c r="G86" s="55" t="s">
         <v>13</v>
       </c>
-      <c r="H86" s="26"/>
+      <c r="H86" s="25"/>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A87" s="25"/>
+      <c r="A87" s="24"/>
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
       <c r="D87" s="1"/>
       <c r="E87" s="1"/>
       <c r="F87" s="1"/>
-      <c r="G87" s="57" t="s">
+      <c r="G87" s="56" t="s">
         <v>12</v>
       </c>
-      <c r="H87" s="26"/>
+      <c r="H87" s="25"/>
     </row>
     <row r="88" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="21"/>
-      <c r="B88" s="23"/>
-      <c r="C88" s="23"/>
-      <c r="D88" s="23"/>
-      <c r="E88" s="23"/>
-      <c r="F88" s="23"/>
-      <c r="G88" s="58" t="s">
+      <c r="A88" s="20"/>
+      <c r="B88" s="22"/>
+      <c r="C88" s="22"/>
+      <c r="D88" s="22"/>
+      <c r="E88" s="22"/>
+      <c r="F88" s="22"/>
+      <c r="G88" s="57" t="s">
         <v>41</v>
       </c>
-      <c r="H88" s="24"/>
+      <c r="H88" s="23"/>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A89" s="17" t="s">
-        <v>113</v>
-      </c>
-      <c r="B89" s="19"/>
-      <c r="C89" s="19"/>
-      <c r="D89" s="19"/>
-      <c r="E89" s="19"/>
-      <c r="F89" s="19"/>
-      <c r="G89" s="52" t="s">
-        <v>75</v>
-      </c>
-      <c r="H89" s="20"/>
+      <c r="A89" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="B89" s="18"/>
+      <c r="C89" s="18"/>
+      <c r="D89" s="18"/>
+      <c r="E89" s="18"/>
+      <c r="F89" s="18"/>
+      <c r="G89" s="51" t="s">
+        <v>74</v>
+      </c>
+      <c r="H89" s="19"/>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A90" s="25"/>
+      <c r="A90" s="24"/>
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
       <c r="D90" s="1"/>
       <c r="E90" s="1"/>
       <c r="F90" s="1"/>
-      <c r="G90" s="53" t="s">
+      <c r="G90" s="52" t="s">
         <v>27</v>
       </c>
-      <c r="H90" s="26"/>
+      <c r="H90" s="25"/>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A91" s="25"/>
+      <c r="A91" s="24"/>
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
       <c r="D91" s="1"/>
@@ -7740,48 +7850,48 @@
       <c r="G91" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="H91" s="26"/>
+      <c r="H91" s="25"/>
     </row>
     <row r="92" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="21"/>
-      <c r="B92" s="23"/>
-      <c r="C92" s="23"/>
-      <c r="D92" s="23"/>
-      <c r="E92" s="23"/>
-      <c r="F92" s="23"/>
-      <c r="G92" s="23" t="s">
+      <c r="A92" s="20"/>
+      <c r="B92" s="22"/>
+      <c r="C92" s="22"/>
+      <c r="D92" s="22"/>
+      <c r="E92" s="22"/>
+      <c r="F92" s="22"/>
+      <c r="G92" s="22" t="s">
+        <v>113</v>
+      </c>
+      <c r="H92" s="23"/>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" s="16" t="s">
         <v>114</v>
       </c>
-      <c r="H92" s="24"/>
-    </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A93" s="17" t="s">
-        <v>115</v>
-      </c>
-      <c r="B93" s="19"/>
-      <c r="C93" s="19"/>
-      <c r="D93" s="19" t="s">
+      <c r="B93" s="18"/>
+      <c r="C93" s="18"/>
+      <c r="D93" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="E93" s="19"/>
-      <c r="F93" s="19"/>
-      <c r="G93" s="19"/>
-      <c r="H93" s="20"/>
+      <c r="E93" s="18"/>
+      <c r="F93" s="18"/>
+      <c r="G93" s="18"/>
+      <c r="H93" s="19"/>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A94" s="25"/>
+      <c r="A94" s="24"/>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
       <c r="D94" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E94" s="1"/>
       <c r="F94" s="1"/>
       <c r="G94" s="1"/>
-      <c r="H94" s="26"/>
+      <c r="H94" s="25"/>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A95" s="25"/>
+      <c r="A95" s="24"/>
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
       <c r="D95" s="2" t="s">
@@ -7790,106 +7900,106 @@
       <c r="E95" s="1"/>
       <c r="F95" s="1"/>
       <c r="G95" s="1"/>
-      <c r="H95" s="26"/>
+      <c r="H95" s="25"/>
     </row>
     <row r="96" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="21"/>
-      <c r="B96" s="23"/>
-      <c r="C96" s="23"/>
-      <c r="D96" s="23" t="s">
-        <v>77</v>
-      </c>
-      <c r="E96" s="23"/>
-      <c r="F96" s="23"/>
-      <c r="G96" s="23"/>
-      <c r="H96" s="24"/>
+      <c r="A96" s="20"/>
+      <c r="B96" s="22"/>
+      <c r="C96" s="22"/>
+      <c r="D96" s="22" t="s">
+        <v>76</v>
+      </c>
+      <c r="E96" s="22"/>
+      <c r="F96" s="22"/>
+      <c r="G96" s="22"/>
+      <c r="H96" s="23"/>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A97" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="B97" s="19"/>
-      <c r="C97" s="19"/>
-      <c r="D97" s="19"/>
-      <c r="E97" s="19"/>
-      <c r="F97" s="19"/>
-      <c r="G97" s="55" t="s">
+      <c r="A97" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="B97" s="18"/>
+      <c r="C97" s="18"/>
+      <c r="D97" s="18"/>
+      <c r="E97" s="18"/>
+      <c r="F97" s="18"/>
+      <c r="G97" s="54" t="s">
         <v>59</v>
       </c>
-      <c r="H97" s="66" t="s">
-        <v>75</v>
+      <c r="H97" s="65" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A98" s="25"/>
+      <c r="A98" s="24"/>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
       <c r="D98" s="1"/>
       <c r="E98" s="1"/>
       <c r="F98" s="1"/>
-      <c r="G98" s="56" t="s">
-        <v>118</v>
-      </c>
-      <c r="H98" s="69" t="s">
-        <v>105</v>
+      <c r="G98" s="55" t="s">
+        <v>117</v>
+      </c>
+      <c r="H98" s="68" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A99" s="25"/>
+      <c r="A99" s="24"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
       <c r="D99" s="1"/>
       <c r="E99" s="1"/>
       <c r="F99" s="1"/>
-      <c r="G99" s="57" t="s">
+      <c r="G99" s="56" t="s">
         <v>12</v>
       </c>
-      <c r="H99" s="69"/>
+      <c r="H99" s="68"/>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A100" s="25"/>
+      <c r="A100" s="24"/>
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
       <c r="D100" s="1"/>
       <c r="E100" s="1"/>
       <c r="F100" s="1"/>
-      <c r="G100" s="56" t="s">
+      <c r="G100" s="55" t="s">
         <v>61</v>
       </c>
-      <c r="H100" s="69"/>
+      <c r="H100" s="68"/>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A101" s="25"/>
+      <c r="A101" s="24"/>
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
       <c r="D101" s="1"/>
       <c r="E101" s="1"/>
       <c r="F101" s="1"/>
-      <c r="G101" s="70" t="s">
-        <v>75</v>
-      </c>
-      <c r="H101" s="69"/>
+      <c r="G101" s="69" t="s">
+        <v>74</v>
+      </c>
+      <c r="H101" s="68"/>
     </row>
     <row r="102" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="21"/>
-      <c r="B102" s="23"/>
-      <c r="C102" s="23"/>
-      <c r="D102" s="23"/>
-      <c r="E102" s="23"/>
-      <c r="F102" s="23"/>
-      <c r="G102" s="54" t="s">
-        <v>119</v>
-      </c>
-      <c r="H102" s="67"/>
+      <c r="A102" s="20"/>
+      <c r="B102" s="22"/>
+      <c r="C102" s="22"/>
+      <c r="D102" s="22"/>
+      <c r="E102" s="22"/>
+      <c r="F102" s="22"/>
+      <c r="G102" s="53" t="s">
+        <v>118</v>
+      </c>
+      <c r="H102" s="66"/>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B103" s="31"/>
-      <c r="C103" s="31"/>
-      <c r="D103" s="31"/>
-      <c r="E103" s="31"/>
-      <c r="F103" s="31"/>
-      <c r="G103" s="31"/>
-      <c r="H103" s="31"/>
+      <c r="B103" s="30"/>
+      <c r="C103" s="30"/>
+      <c r="D103" s="30"/>
+      <c r="E103" s="30"/>
+      <c r="F103" s="30"/>
+      <c r="G103" s="30"/>
+      <c r="H103" s="30"/>
     </row>
   </sheetData>
   <mergeCells count="30">
@@ -7941,36 +8051,36 @@
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B5" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="C4" s="14"/>
-      <c r="D4" s="14"/>
-      <c r="E4" s="14"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B5" s="15" t="s">
-        <v>121</v>
-      </c>
-      <c r="C5" s="15"/>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>3</v>
       </c>
       <c r="B6" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="C6" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="D6" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="E6" s="6" t="s">
         <v>124</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -8145,7 +8255,7 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B17" s="7">
         <v>0</v>
@@ -8162,7 +8272,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B18" s="7">
         <v>0</v>
@@ -8179,7 +8289,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B19" s="7">
         <v>0</v>
@@ -8196,7 +8306,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B20" s="7">
         <v>0</v>
@@ -8213,7 +8323,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B21" s="7">
         <v>0</v>
@@ -8230,7 +8340,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B22" s="7">
         <v>0</v>
@@ -8247,7 +8357,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B23" s="7">
         <v>0</v>
@@ -8264,7 +8374,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B24" s="7">
         <v>0</v>
@@ -8281,7 +8391,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B25" s="7">
         <v>0</v>
@@ -8298,7 +8408,7 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B26" s="7">
         <v>0</v>
@@ -8315,7 +8425,7 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B27" s="7">
         <v>0</v>
@@ -8332,7 +8442,7 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B28" s="7">
         <v>0</v>
@@ -8349,7 +8459,7 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B29" s="7">
         <v>0</v>
@@ -8366,7 +8476,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B30" s="7">
         <v>0</v>
@@ -8383,7 +8493,7 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B31" s="7">
         <v>0</v>
@@ -8400,7 +8510,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B32" s="7">
         <v>0</v>
@@ -8417,7 +8527,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B33" s="7">
         <v>0</v>
@@ -8467,40 +8577,40 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="B4" s="11" t="s">
         <v>126</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B5" s="11"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="B7" s="11" t="s">
         <v>130</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="B8" s="11" t="s">
         <v>132</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>133</v>
       </c>
     </row>
   </sheetData>
@@ -8675,13 +8785,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82C34503-2CEC-4D68-80CD-B28E1A8DE2C4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3713B2CD-EB58-4EDD-A1CF-7CE9D2FEB953}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{21680000-0FA8-4848-A547-28CF206D5CC1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EF564202-A8B2-42F4-8C04-CEEABC9A516D}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5799426A-8929-4C41-8FE8-4FA90918C70D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{30DC5C72-25ED-4AA2-9EF1-8528BF18B506}"/>
 </file>
--- a/Plannings 2026 S26.xlsx
+++ b/Plannings 2026 S26.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="8_{A23AA2D1-9819-4B65-9C3A-D83FC30F8B22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{47D258CF-975F-4986-A9AD-0C2B3793AEDE}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="8_{A23AA2D1-9819-4B65-9C3A-D83FC30F8B22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5B285F09-A81C-42CB-AF32-5E43987A31CE}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -240,9 +240,6 @@
     <t>DOVINA Théo</t>
   </si>
   <si>
-    <t>20:00/24:00</t>
-  </si>
-  <si>
     <t>FREIXEDAS-BERENGUER Maxime</t>
   </si>
   <si>
@@ -481,6 +478,9 @@
   </si>
   <si>
     <t>16:30/18:00</t>
+  </si>
+  <si>
+    <t>18:30/24:00</t>
   </si>
 </sst>
 </file>
@@ -6544,7 +6544,7 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B3" s="60" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C3" s="61"/>
       <c r="D3" s="61"/>
@@ -6555,25 +6555,25 @@
     </row>
     <row r="4" spans="1:8" s="63" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B4" s="64" t="s">
+        <v>139</v>
+      </c>
+      <c r="C4" s="64" t="s">
         <v>140</v>
       </c>
-      <c r="C4" s="64" t="s">
+      <c r="D4" s="64" t="s">
         <v>141</v>
       </c>
-      <c r="D4" s="64" t="s">
+      <c r="E4" s="64" t="s">
         <v>142</v>
       </c>
-      <c r="E4" s="64" t="s">
+      <c r="F4" s="64" t="s">
         <v>143</v>
       </c>
-      <c r="F4" s="64" t="s">
+      <c r="G4" s="64" t="s">
         <v>144</v>
       </c>
-      <c r="G4" s="64" t="s">
-        <v>145</v>
-      </c>
       <c r="H4" s="64" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -6688,10 +6688,10 @@
         <v>23</v>
       </c>
       <c r="E11" s="58" t="s">
+        <v>148</v>
+      </c>
+      <c r="F11" s="58" t="s">
         <v>149</v>
-      </c>
-      <c r="F11" s="58" t="s">
-        <v>150</v>
       </c>
       <c r="G11" s="58"/>
       <c r="H11" s="77"/>
@@ -6793,20 +6793,20 @@
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="24"/>
       <c r="B18" s="58" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C18" s="58" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D18" s="58" t="s">
         <v>33</v>
       </c>
       <c r="E18" s="58"/>
       <c r="F18" s="58" t="s">
+        <v>146</v>
+      </c>
+      <c r="G18" s="58" t="s">
         <v>147</v>
-      </c>
-      <c r="G18" s="58" t="s">
-        <v>148</v>
       </c>
       <c r="H18" s="77"/>
     </row>
@@ -6907,7 +6907,7 @@
         <v>43</v>
       </c>
       <c r="F25" s="58" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G25" s="1"/>
       <c r="H25" s="25"/>
@@ -7065,7 +7065,7 @@
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="24"/>
       <c r="B35" s="58" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C35" s="46" t="s">
         <v>60</v>
@@ -7074,7 +7074,7 @@
         <v>61</v>
       </c>
       <c r="E35" s="58" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F35" s="1"/>
       <c r="G35" s="1" t="s">
@@ -7191,8 +7191,8 @@
       <c r="B43" s="22"/>
       <c r="C43" s="22"/>
       <c r="D43" s="22"/>
-      <c r="E43" s="22" t="s">
-        <v>72</v>
+      <c r="E43" s="59" t="s">
+        <v>152</v>
       </c>
       <c r="F43" s="22"/>
       <c r="G43" s="22"/>
@@ -7200,10 +7200,10 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="B44" s="49" t="s">
         <v>133</v>
-      </c>
-      <c r="B44" s="49" t="s">
-        <v>134</v>
       </c>
       <c r="C44" s="18"/>
       <c r="D44" s="18" t="s">
@@ -7212,30 +7212,30 @@
       <c r="E44" s="18"/>
       <c r="F44" s="18"/>
       <c r="G44" s="51" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H44" s="19"/>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="24"/>
       <c r="B45" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C45" s="1"/>
       <c r="D45" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E45" s="1"/>
       <c r="F45" s="1"/>
       <c r="G45" s="52" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H45" s="25"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="24"/>
       <c r="B46" s="50" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
@@ -7247,7 +7247,7 @@
     <row r="47" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="20"/>
       <c r="B47" s="22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C47" s="22"/>
       <c r="D47" s="22"/>
@@ -7258,7 +7258,7 @@
     </row>
     <row r="48" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="26" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B48" s="27"/>
       <c r="C48" s="28"/>
@@ -7270,7 +7270,7 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B49" s="18" t="s">
         <v>18</v>
@@ -7291,24 +7291,24 @@
     <row r="50" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="20"/>
       <c r="B50" s="59" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C50" s="22" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D50" s="22"/>
       <c r="E50" s="22"/>
       <c r="F50" s="22" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G50" s="22"/>
       <c r="H50" s="23" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="16" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B51" s="18"/>
       <c r="C51" s="18"/>
@@ -7317,7 +7317,7 @@
       <c r="F51" s="18"/>
       <c r="G51" s="18"/>
       <c r="H51" s="65" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -7329,12 +7329,12 @@
       <c r="F52" s="22"/>
       <c r="G52" s="22"/>
       <c r="H52" s="66" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="33" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B53" s="34"/>
       <c r="C53" s="35"/>
@@ -7346,7 +7346,7 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="16" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B54" s="18"/>
       <c r="C54" s="48" t="s">
@@ -7374,13 +7374,13 @@
       <c r="E55" s="22"/>
       <c r="F55" s="22"/>
       <c r="G55" s="47" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H55" s="23"/>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="16" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B56" s="18"/>
       <c r="C56" s="18"/>
@@ -7388,7 +7388,7 @@
       <c r="E56" s="18"/>
       <c r="F56" s="18"/>
       <c r="G56" s="51" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H56" s="19" t="s">
         <v>18</v>
@@ -7402,10 +7402,10 @@
       <c r="E57" s="1"/>
       <c r="F57" s="1"/>
       <c r="G57" s="52" t="s">
+        <v>87</v>
+      </c>
+      <c r="H57" s="25" t="s">
         <v>88</v>
-      </c>
-      <c r="H57" s="25" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
@@ -7419,7 +7419,7 @@
         <v>18</v>
       </c>
       <c r="H58" s="67" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
@@ -7430,10 +7430,10 @@
       <c r="E59" s="1"/>
       <c r="F59" s="1"/>
       <c r="G59" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="H59" s="68" t="s">
         <v>90</v>
-      </c>
-      <c r="H59" s="68" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
@@ -7457,7 +7457,7 @@
       <c r="F61" s="1"/>
       <c r="G61" s="1"/>
       <c r="H61" s="25" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
@@ -7481,7 +7481,7 @@
       <c r="F63" s="1"/>
       <c r="G63" s="1"/>
       <c r="H63" s="25" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
@@ -7493,7 +7493,7 @@
       <c r="F64" s="1"/>
       <c r="G64" s="1"/>
       <c r="H64" s="67" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="65" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -7505,12 +7505,12 @@
       <c r="F65" s="22"/>
       <c r="G65" s="22"/>
       <c r="H65" s="66" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B66" s="18"/>
       <c r="C66" s="18"/>
@@ -7536,7 +7536,7 @@
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" s="16" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B68" s="18"/>
       <c r="C68" s="18"/>
@@ -7545,7 +7545,7 @@
       <c r="F68" s="18"/>
       <c r="G68" s="18"/>
       <c r="H68" s="65" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="69" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -7557,12 +7557,12 @@
       <c r="F69" s="22"/>
       <c r="G69" s="22"/>
       <c r="H69" s="66" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" s="32" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B70" s="1"/>
       <c r="C70" s="1" t="s">
@@ -7584,16 +7584,16 @@
       <c r="A71" s="24"/>
       <c r="B71" s="1"/>
       <c r="C71" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D71" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="D71" s="1" t="s">
+      <c r="E71" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="E71" s="1" t="s">
+      <c r="F71" s="1" t="s">
         <v>99</v>
-      </c>
-      <c r="F71" s="1" t="s">
-        <v>100</v>
       </c>
       <c r="G71" s="1"/>
       <c r="H71" s="25"/>
@@ -7615,7 +7615,7 @@
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
       <c r="D73" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E73" s="1"/>
       <c r="F73" s="1"/>
@@ -7639,7 +7639,7 @@
       <c r="B75" s="22"/>
       <c r="C75" s="22"/>
       <c r="D75" s="42" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E75" s="22"/>
       <c r="F75" s="22"/>
@@ -7648,7 +7648,7 @@
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" s="16" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B76" s="18"/>
       <c r="C76" s="18"/>
@@ -7656,10 +7656,10 @@
       <c r="E76" s="18"/>
       <c r="F76" s="18"/>
       <c r="G76" s="51" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H76" s="65" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
@@ -7670,10 +7670,10 @@
       <c r="E77" s="1"/>
       <c r="F77" s="1"/>
       <c r="G77" s="52" t="s">
+        <v>103</v>
+      </c>
+      <c r="H77" s="68" t="s">
         <v>104</v>
-      </c>
-      <c r="H77" s="68" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
@@ -7687,7 +7687,7 @@
         <v>58</v>
       </c>
       <c r="H78" s="67" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
@@ -7698,10 +7698,10 @@
       <c r="E79" s="1"/>
       <c r="F79" s="1"/>
       <c r="G79" s="46" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H79" s="68" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
@@ -7713,7 +7713,7 @@
       <c r="F80" s="1"/>
       <c r="G80" s="46"/>
       <c r="H80" s="67" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
@@ -7725,7 +7725,7 @@
       <c r="F81" s="1"/>
       <c r="G81" s="46"/>
       <c r="H81" s="68" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
@@ -7749,12 +7749,12 @@
       <c r="F83" s="22"/>
       <c r="G83" s="47"/>
       <c r="H83" s="23" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="84" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="26" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B84" s="27"/>
       <c r="C84" s="28"/>
@@ -7766,7 +7766,7 @@
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" s="16" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B85" s="18"/>
       <c r="C85" s="18"/>
@@ -7816,7 +7816,7 @@
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" s="16" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B89" s="18"/>
       <c r="C89" s="18"/>
@@ -7824,7 +7824,7 @@
       <c r="E89" s="18"/>
       <c r="F89" s="18"/>
       <c r="G89" s="51" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H89" s="19"/>
     </row>
@@ -7860,13 +7860,13 @@
       <c r="E92" s="22"/>
       <c r="F92" s="22"/>
       <c r="G92" s="22" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H92" s="23"/>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" s="16" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B93" s="18"/>
       <c r="C93" s="18"/>
@@ -7883,7 +7883,7 @@
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
       <c r="D94" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E94" s="1"/>
       <c r="F94" s="1"/>
@@ -7907,7 +7907,7 @@
       <c r="B96" s="22"/>
       <c r="C96" s="22"/>
       <c r="D96" s="22" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E96" s="22"/>
       <c r="F96" s="22"/>
@@ -7916,7 +7916,7 @@
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" s="16" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B97" s="18"/>
       <c r="C97" s="18"/>
@@ -7927,7 +7927,7 @@
         <v>59</v>
       </c>
       <c r="H97" s="65" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
@@ -7938,10 +7938,10 @@
       <c r="E98" s="1"/>
       <c r="F98" s="1"/>
       <c r="G98" s="55" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H98" s="68" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
@@ -7976,7 +7976,7 @@
       <c r="E101" s="1"/>
       <c r="F101" s="1"/>
       <c r="G101" s="69" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H101" s="68"/>
     </row>
@@ -7988,7 +7988,7 @@
       <c r="E102" s="22"/>
       <c r="F102" s="22"/>
       <c r="G102" s="53" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H102" s="66"/>
     </row>
@@ -8052,7 +8052,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B4" s="13" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C4" s="13"/>
       <c r="D4" s="13"/>
@@ -8060,7 +8060,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B5" s="14" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C5" s="14"/>
       <c r="D5" s="14"/>
@@ -8071,16 +8071,16 @@
         <v>3</v>
       </c>
       <c r="B6" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="C6" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="D6" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="E6" s="6" t="s">
         <v>123</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -8272,7 +8272,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B18" s="7">
         <v>0</v>
@@ -8289,7 +8289,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B19" s="7">
         <v>0</v>
@@ -8306,7 +8306,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B20" s="7">
         <v>0</v>
@@ -8323,7 +8323,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B21" s="7">
         <v>0</v>
@@ -8340,7 +8340,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B22" s="7">
         <v>0</v>
@@ -8357,7 +8357,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B23" s="7">
         <v>0</v>
@@ -8374,7 +8374,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B24" s="7">
         <v>0</v>
@@ -8391,7 +8391,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B25" s="7">
         <v>0</v>
@@ -8408,7 +8408,7 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B26" s="7">
         <v>0</v>
@@ -8425,7 +8425,7 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B27" s="7">
         <v>0</v>
@@ -8442,7 +8442,7 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B28" s="7">
         <v>0</v>
@@ -8459,7 +8459,7 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B29" s="7">
         <v>0</v>
@@ -8476,7 +8476,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B30" s="7">
         <v>0</v>
@@ -8493,7 +8493,7 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B31" s="7">
         <v>0</v>
@@ -8510,7 +8510,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B32" s="7">
         <v>0</v>
@@ -8527,7 +8527,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B33" s="7">
         <v>0</v>
@@ -8577,40 +8577,40 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="B4" s="11" t="s">
         <v>125</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B5" s="11"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="B7" s="11" t="s">
         <v>129</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="B8" s="11" t="s">
         <v>131</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>132</v>
       </c>
     </row>
   </sheetData>
@@ -8785,13 +8785,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3713B2CD-EB58-4EDD-A1CF-7CE9D2FEB953}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{237B6F2F-DDC0-43CB-AD4A-7D13B3C1AC2A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EF564202-A8B2-42F4-8C04-CEEABC9A516D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{79ADD44D-1503-49B4-97A7-4450ECE9CCBB}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{30DC5C72-25ED-4AA2-9EF1-8528BF18B506}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74364E4E-0E00-4523-B096-2A8C621F84C3}"/>
 </file>
--- a/Plannings 2026 S26.xlsx
+++ b/Plannings 2026 S26.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="8_{A23AA2D1-9819-4B65-9C3A-D83FC30F8B22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5B285F09-A81C-42CB-AF32-5E43987A31CE}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{A23AA2D1-9819-4B65-9C3A-D83FC30F8B22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BE77D127-EEBA-4B11-B64D-E4268FA37DEA}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="151">
   <si>
     <t>Planning des salariés du 22/06/2026 au 28/06/2026</t>
   </si>
@@ -210,6 +210,9 @@
     <t>13:45/15:45</t>
   </si>
   <si>
+    <t>17:00/18:00</t>
+  </si>
+  <si>
     <t>08:50/10:00</t>
   </si>
   <si>
@@ -240,6 +243,9 @@
     <t>DOVINA Théo</t>
   </si>
   <si>
+    <t>20:00/24:00</t>
+  </si>
+  <si>
     <t>FREIXEDAS-BERENGUER Maxime</t>
   </si>
   <si>
@@ -429,6 +435,9 @@
     <t>FORP VDC</t>
   </si>
   <si>
+    <t>09:45/13:15</t>
+  </si>
+  <si>
     <t>11:45/17:00</t>
   </si>
   <si>
@@ -466,21 +475,6 @@
   </si>
   <si>
     <t>10:15/17:00</t>
-  </si>
-  <si>
-    <t>11:45/16:30</t>
-  </si>
-  <si>
-    <t>09:45/13:00</t>
-  </si>
-  <si>
-    <t>16:00/19:00</t>
-  </si>
-  <si>
-    <t>16:30/18:00</t>
-  </si>
-  <si>
-    <t>18:30/24:00</t>
   </si>
 </sst>
 </file>
@@ -994,7 +988,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1030,6 +1024,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1170,6 +1167,18 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1209,30 +1218,6 @@
     <xf numFmtId="0" fontId="16" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5605,534 +5590,6 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="3657600" y="4391025"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="110" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5E11E667-BCB5-4EB1-B679-508B36CE3BB1}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="609600" y="2295525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="111" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1F346B36-B49F-4C01-89C5-D785CB6802C5}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="609600" y="2676525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="112" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3D3A596E-3F14-4212-8CA9-41F8D2D79956}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1219200" y="2295525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="113" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9B0376B6-6366-408A-868E-C3E5B29CD7A2}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1828800" y="2295525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="114" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{257B316F-EE6B-4EF7-8F2B-89C2D483A2FF}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1828800" y="2676525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="115" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BFABF675-D5EE-496F-AFBA-1BBA689333F2}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1828800" y="3057525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="116" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{68A3E215-42C0-4FDA-BDF1-CFE864063B92}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2438400" y="2295525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="117" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{58FC21F7-F7BE-49C4-882A-2D9AF8FE52D4}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2438400" y="2676525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="118" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D8C9CF28-6387-4A30-BE59-F70C9EE8DC20}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2438400" y="3057525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="119" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8FB689B7-1847-4C5B-BC62-6E7A4F0E994B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3048000" y="2295525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="120" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1AD1DE96-4C49-40A8-BEB7-1693E16AFBC2}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3048000" y="5915025"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="121" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FDD7FE20-7B57-417D-A345-88667E1FD488}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3048000" y="6296025"/>
           <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -6543,311 +6000,307 @@
       <c r="H2" s="12"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B3" s="60" t="s">
+      <c r="B3" s="65" t="s">
+        <v>141</v>
+      </c>
+      <c r="C3" s="66"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="66"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="66"/>
+      <c r="H3" s="67"/>
+    </row>
+    <row r="4" spans="1:8" s="68" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="B4" s="69" t="s">
+        <v>142</v>
+      </c>
+      <c r="C4" s="69" t="s">
+        <v>143</v>
+      </c>
+      <c r="D4" s="69" t="s">
+        <v>144</v>
+      </c>
+      <c r="E4" s="69" t="s">
+        <v>145</v>
+      </c>
+      <c r="F4" s="69" t="s">
+        <v>146</v>
+      </c>
+      <c r="G4" s="69" t="s">
+        <v>147</v>
+      </c>
+      <c r="H4" s="69" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="F5" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="G5" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="H5" s="16" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="18"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="55" t="s">
+        <v>12</v>
+      </c>
+      <c r="H6" s="20"/>
+    </row>
+    <row r="7" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="21"/>
+      <c r="B7" s="22"/>
+      <c r="C7" s="23"/>
+      <c r="D7" s="23"/>
+      <c r="E7" s="23"/>
+      <c r="F7" s="23"/>
+      <c r="G7" s="58" t="s">
+        <v>13</v>
+      </c>
+      <c r="H7" s="24"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="19"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="42" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" s="19"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="19"/>
+      <c r="H8" s="20"/>
+    </row>
+    <row r="9" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="21"/>
+      <c r="B9" s="23"/>
+      <c r="C9" s="23"/>
+      <c r="D9" s="43" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" s="23"/>
+      <c r="F9" s="23"/>
+      <c r="G9" s="23"/>
+      <c r="H9" s="24"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" s="63" t="s">
+        <v>19</v>
+      </c>
+      <c r="E10" s="42" t="s">
+        <v>20</v>
+      </c>
+      <c r="F10" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="G10" s="19"/>
+      <c r="H10" s="20"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="25"/>
+      <c r="B11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" s="61" t="s">
+        <v>23</v>
+      </c>
+      <c r="E11" s="44" t="s">
+        <v>24</v>
+      </c>
+      <c r="F11" s="59" t="s">
+        <v>137</v>
+      </c>
+      <c r="G11" s="1"/>
+      <c r="H11" s="26"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="25"/>
+      <c r="B12" s="60" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="1"/>
+      <c r="D12" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="26"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="25"/>
+      <c r="B13" s="61" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="26"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="25"/>
+      <c r="B14" s="61"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="45" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="26"/>
+    </row>
+    <row r="15" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="21"/>
+      <c r="B15" s="62"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="43" t="s">
+        <v>29</v>
+      </c>
+      <c r="E15" s="23"/>
+      <c r="F15" s="23"/>
+      <c r="G15" s="23"/>
+      <c r="H15" s="24"/>
+    </row>
+    <row r="16" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="27" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="28"/>
+      <c r="C16" s="29"/>
+      <c r="D16" s="29"/>
+      <c r="E16" s="29"/>
+      <c r="F16" s="29"/>
+      <c r="G16" s="29"/>
+      <c r="H16" s="30"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" s="51" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="51" t="s">
+        <v>18</v>
+      </c>
+      <c r="D17" s="51" t="s">
+        <v>18</v>
+      </c>
+      <c r="E17" s="59"/>
+      <c r="F17" s="51" t="s">
+        <v>18</v>
+      </c>
+      <c r="G17" s="51" t="s">
+        <v>18</v>
+      </c>
+      <c r="H17" s="59"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="13"/>
+      <c r="B18" s="59" t="s">
         <v>138</v>
       </c>
-      <c r="C3" s="61"/>
-      <c r="D3" s="61"/>
-      <c r="E3" s="61"/>
-      <c r="F3" s="61"/>
-      <c r="G3" s="61"/>
-      <c r="H3" s="62"/>
-    </row>
-    <row r="4" spans="1:8" s="63" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="B4" s="64" t="s">
-        <v>139</v>
-      </c>
-      <c r="C4" s="64" t="s">
-        <v>140</v>
-      </c>
-      <c r="D4" s="64" t="s">
-        <v>141</v>
-      </c>
-      <c r="E4" s="64" t="s">
-        <v>142</v>
-      </c>
-      <c r="F4" s="64" t="s">
-        <v>143</v>
-      </c>
-      <c r="G4" s="64" t="s">
-        <v>144</v>
-      </c>
-      <c r="H4" s="64" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="D5" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E5" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="F5" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="G5" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="H5" s="15" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="17"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="18"/>
-      <c r="G6" s="54" t="s">
-        <v>12</v>
-      </c>
-      <c r="H6" s="19"/>
-    </row>
-    <row r="7" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="20"/>
-      <c r="B7" s="21"/>
-      <c r="C7" s="22"/>
-      <c r="D7" s="22"/>
-      <c r="E7" s="22"/>
-      <c r="F7" s="22"/>
-      <c r="G7" s="57" t="s">
-        <v>13</v>
-      </c>
-      <c r="H7" s="23"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="18"/>
-      <c r="C8" s="18"/>
-      <c r="D8" s="41" t="s">
-        <v>15</v>
-      </c>
-      <c r="E8" s="18"/>
-      <c r="F8" s="18"/>
-      <c r="G8" s="18"/>
-      <c r="H8" s="19"/>
-    </row>
-    <row r="9" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="20"/>
-      <c r="B9" s="22"/>
-      <c r="C9" s="22"/>
-      <c r="D9" s="42" t="s">
-        <v>16</v>
-      </c>
-      <c r="E9" s="22"/>
-      <c r="F9" s="22"/>
-      <c r="G9" s="22"/>
-      <c r="H9" s="23"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" s="49" t="s">
+      <c r="C18" s="59" t="s">
+        <v>148</v>
+      </c>
+      <c r="D18" s="59" t="s">
+        <v>33</v>
+      </c>
+      <c r="E18" s="59"/>
+      <c r="F18" s="59" t="s">
+        <v>149</v>
+      </c>
+      <c r="G18" s="59" t="s">
+        <v>150</v>
+      </c>
+      <c r="H18" s="59"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="13"/>
+      <c r="B19" s="59"/>
+      <c r="C19" s="59"/>
+      <c r="D19" s="75" t="s">
+        <v>34</v>
+      </c>
+      <c r="E19" s="59"/>
+      <c r="F19" s="59"/>
+      <c r="G19" s="59"/>
+      <c r="H19" s="59"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="13"/>
+      <c r="B20" s="59"/>
+      <c r="C20" s="59"/>
+      <c r="D20" s="76" t="s">
+        <v>35</v>
+      </c>
+      <c r="E20" s="59"/>
+      <c r="F20" s="59"/>
+      <c r="G20" s="59"/>
+      <c r="H20" s="59"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="13"/>
+      <c r="B21" s="59"/>
+      <c r="C21" s="59"/>
+      <c r="D21" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="49" t="s">
-        <v>18</v>
-      </c>
-      <c r="D10" s="75" t="s">
-        <v>19</v>
-      </c>
-      <c r="E10" s="49" t="s">
-        <v>18</v>
-      </c>
-      <c r="F10" s="49" t="s">
-        <v>18</v>
-      </c>
-      <c r="G10" s="49"/>
-      <c r="H10" s="76"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="24"/>
-      <c r="B11" s="58" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" s="58" t="s">
-        <v>22</v>
-      </c>
-      <c r="D11" s="71" t="s">
-        <v>23</v>
-      </c>
-      <c r="E11" s="58" t="s">
-        <v>148</v>
-      </c>
-      <c r="F11" s="58" t="s">
-        <v>149</v>
-      </c>
-      <c r="G11" s="58"/>
-      <c r="H11" s="77"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="24"/>
-      <c r="B12" s="70" t="s">
-        <v>19</v>
-      </c>
-      <c r="C12" s="58"/>
-      <c r="D12" s="50" t="s">
-        <v>18</v>
-      </c>
-      <c r="E12" s="72" t="s">
-        <v>20</v>
-      </c>
-      <c r="F12" s="58"/>
-      <c r="G12" s="58"/>
-      <c r="H12" s="77"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="24"/>
-      <c r="B13" s="71" t="s">
-        <v>26</v>
-      </c>
-      <c r="C13" s="58"/>
-      <c r="D13" s="58" t="s">
-        <v>27</v>
-      </c>
-      <c r="E13" s="73" t="s">
-        <v>24</v>
-      </c>
-      <c r="F13" s="58"/>
-      <c r="G13" s="58"/>
-      <c r="H13" s="77"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="24"/>
-      <c r="B14" s="71"/>
-      <c r="C14" s="58"/>
-      <c r="D14" s="72" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="50" t="s">
-        <v>18</v>
-      </c>
-      <c r="F14" s="58"/>
-      <c r="G14" s="58"/>
-      <c r="H14" s="77"/>
-    </row>
-    <row r="15" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="20"/>
-      <c r="B15" s="78"/>
-      <c r="C15" s="59"/>
-      <c r="D15" s="74" t="s">
-        <v>29</v>
-      </c>
-      <c r="E15" s="59" t="s">
-        <v>28</v>
-      </c>
-      <c r="F15" s="59"/>
-      <c r="G15" s="59"/>
-      <c r="H15" s="79"/>
-    </row>
-    <row r="16" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="B16" s="27"/>
-      <c r="C16" s="28"/>
-      <c r="D16" s="28"/>
-      <c r="E16" s="28"/>
-      <c r="F16" s="28"/>
-      <c r="G16" s="28"/>
-      <c r="H16" s="29"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="B17" s="49" t="s">
-        <v>18</v>
-      </c>
-      <c r="C17" s="49" t="s">
-        <v>18</v>
-      </c>
-      <c r="D17" s="49" t="s">
-        <v>18</v>
-      </c>
-      <c r="E17" s="49"/>
-      <c r="F17" s="49" t="s">
-        <v>18</v>
-      </c>
-      <c r="G17" s="49" t="s">
-        <v>18</v>
-      </c>
-      <c r="H17" s="76"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="24"/>
-      <c r="B18" s="58" t="s">
-        <v>135</v>
-      </c>
-      <c r="C18" s="58" t="s">
-        <v>145</v>
-      </c>
-      <c r="D18" s="58" t="s">
-        <v>33</v>
-      </c>
-      <c r="E18" s="58"/>
-      <c r="F18" s="58" t="s">
-        <v>146</v>
-      </c>
-      <c r="G18" s="58" t="s">
-        <v>147</v>
-      </c>
-      <c r="H18" s="77"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="24"/>
-      <c r="B19" s="58"/>
-      <c r="C19" s="58"/>
-      <c r="D19" s="70" t="s">
-        <v>34</v>
-      </c>
-      <c r="E19" s="58"/>
-      <c r="F19" s="58"/>
-      <c r="G19" s="58"/>
-      <c r="H19" s="77"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="24"/>
-      <c r="B20" s="58"/>
-      <c r="C20" s="58"/>
-      <c r="D20" s="71" t="s">
-        <v>35</v>
-      </c>
-      <c r="E20" s="58"/>
-      <c r="F20" s="58"/>
-      <c r="G20" s="58"/>
-      <c r="H20" s="77"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="24"/>
-      <c r="B21" s="58"/>
-      <c r="C21" s="58"/>
-      <c r="D21" s="50" t="s">
-        <v>18</v>
-      </c>
-      <c r="E21" s="58"/>
-      <c r="F21" s="58"/>
-      <c r="G21" s="58"/>
-      <c r="H21" s="77"/>
+      <c r="E21" s="59"/>
+      <c r="F21" s="59"/>
+      <c r="G21" s="59"/>
+      <c r="H21" s="59"/>
     </row>
     <row r="22" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="20"/>
+      <c r="A22" s="13"/>
       <c r="B22" s="59"/>
       <c r="C22" s="59"/>
       <c r="D22" s="59" t="s">
@@ -6856,325 +6309,321 @@
       <c r="E22" s="59"/>
       <c r="F22" s="59"/>
       <c r="G22" s="59"/>
-      <c r="H22" s="79"/>
+      <c r="H22" s="59"/>
     </row>
     <row r="23" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="37" t="s">
+      <c r="A23" s="38" t="s">
         <v>37</v>
       </c>
-      <c r="B23" s="38"/>
-      <c r="C23" s="39"/>
-      <c r="D23" s="39"/>
-      <c r="E23" s="39"/>
-      <c r="F23" s="39"/>
-      <c r="G23" s="39"/>
-      <c r="H23" s="40"/>
+      <c r="B23" s="39"/>
+      <c r="C23" s="40"/>
+      <c r="D23" s="40"/>
+      <c r="E23" s="40"/>
+      <c r="F23" s="40"/>
+      <c r="G23" s="40"/>
+      <c r="H23" s="41"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="16" t="s">
+      <c r="A24" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="B24" s="54" t="s">
+      <c r="B24" s="55" t="s">
         <v>39</v>
       </c>
-      <c r="C24" s="54" t="s">
+      <c r="C24" s="55" t="s">
         <v>39</v>
       </c>
-      <c r="D24" s="54" t="s">
+      <c r="D24" s="55" t="s">
         <v>39</v>
       </c>
-      <c r="E24" s="54" t="s">
+      <c r="E24" s="55" t="s">
         <v>39</v>
       </c>
-      <c r="F24" s="49" t="s">
-        <v>18</v>
-      </c>
-      <c r="G24" s="18"/>
-      <c r="H24" s="19"/>
+      <c r="F24" s="42" t="s">
+        <v>40</v>
+      </c>
+      <c r="G24" s="19"/>
+      <c r="H24" s="20"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="24"/>
-      <c r="B25" s="55" t="s">
+      <c r="A25" s="25"/>
+      <c r="B25" s="56" t="s">
         <v>41</v>
       </c>
-      <c r="C25" s="55" t="s">
+      <c r="C25" s="56" t="s">
         <v>41</v>
       </c>
-      <c r="D25" s="55" t="s">
+      <c r="D25" s="56" t="s">
         <v>42</v>
       </c>
-      <c r="E25" s="55" t="s">
+      <c r="E25" s="56" t="s">
         <v>43</v>
       </c>
-      <c r="F25" s="58" t="s">
-        <v>150</v>
+      <c r="F25" s="44" t="s">
+        <v>44</v>
       </c>
       <c r="G25" s="1"/>
-      <c r="H25" s="25"/>
+      <c r="H25" s="26"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="24"/>
+      <c r="A26" s="25"/>
       <c r="B26" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="D26" s="56" t="s">
+      <c r="D26" s="57" t="s">
         <v>39</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F26" s="72" t="s">
-        <v>40</v>
-      </c>
+      <c r="F26" s="44"/>
       <c r="G26" s="1"/>
-      <c r="H26" s="25"/>
+      <c r="H26" s="26"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="24"/>
+      <c r="A27" s="25"/>
       <c r="B27" s="1" t="s">
         <v>47</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="D27" s="55" t="s">
+      <c r="D27" s="56" t="s">
         <v>49</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="F27" s="73" t="s">
-        <v>44</v>
-      </c>
+      <c r="F27" s="44"/>
       <c r="G27" s="1"/>
-      <c r="H27" s="25"/>
+      <c r="H27" s="26"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="24"/>
-      <c r="B28" s="56" t="s">
+      <c r="A28" s="25"/>
+      <c r="B28" s="57" t="s">
         <v>39</v>
       </c>
-      <c r="C28" s="56" t="s">
+      <c r="C28" s="57" t="s">
         <v>39</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>46</v>
       </c>
       <c r="E28" s="1"/>
-      <c r="F28" s="73"/>
+      <c r="F28" s="44"/>
       <c r="G28" s="1"/>
-      <c r="H28" s="25"/>
+      <c r="H28" s="26"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="24"/>
-      <c r="B29" s="55" t="s">
+      <c r="A29" s="25"/>
+      <c r="B29" s="56" t="s">
         <v>51</v>
       </c>
-      <c r="C29" s="55" t="s">
+      <c r="C29" s="56" t="s">
         <v>52</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>53</v>
       </c>
       <c r="E29" s="1"/>
-      <c r="F29" s="73"/>
+      <c r="F29" s="44"/>
       <c r="G29" s="1"/>
-      <c r="H29" s="25"/>
+      <c r="H29" s="26"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="24"/>
-      <c r="B30" s="55"/>
+      <c r="A30" s="25"/>
+      <c r="B30" s="56"/>
       <c r="C30" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D30" s="56" t="s">
+      <c r="D30" s="57" t="s">
         <v>39</v>
       </c>
       <c r="E30" s="1"/>
-      <c r="F30" s="73"/>
+      <c r="F30" s="44"/>
       <c r="G30" s="1"/>
-      <c r="H30" s="25"/>
+      <c r="H30" s="26"/>
     </row>
     <row r="31" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="20"/>
-      <c r="B31" s="57"/>
-      <c r="C31" s="22" t="s">
+      <c r="A31" s="21"/>
+      <c r="B31" s="58"/>
+      <c r="C31" s="23" t="s">
         <v>54</v>
       </c>
-      <c r="D31" s="57" t="s">
+      <c r="D31" s="58" t="s">
         <v>55</v>
       </c>
-      <c r="E31" s="22"/>
-      <c r="F31" s="74"/>
-      <c r="G31" s="22"/>
-      <c r="H31" s="23"/>
+      <c r="E31" s="23"/>
+      <c r="F31" s="43"/>
+      <c r="G31" s="23"/>
+      <c r="H31" s="24"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="16" t="s">
+      <c r="A32" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="B32" s="18"/>
-      <c r="C32" s="18"/>
-      <c r="D32" s="18"/>
-      <c r="E32" s="18"/>
-      <c r="F32" s="18"/>
-      <c r="G32" s="54" t="s">
+      <c r="B32" s="19"/>
+      <c r="C32" s="19"/>
+      <c r="D32" s="19"/>
+      <c r="E32" s="19"/>
+      <c r="F32" s="19"/>
+      <c r="G32" s="55" t="s">
         <v>12</v>
       </c>
-      <c r="H32" s="19"/>
+      <c r="H32" s="20"/>
     </row>
     <row r="33" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="20"/>
-      <c r="B33" s="22"/>
-      <c r="C33" s="22"/>
-      <c r="D33" s="22"/>
-      <c r="E33" s="22"/>
-      <c r="F33" s="22"/>
-      <c r="G33" s="57" t="s">
+      <c r="A33" s="21"/>
+      <c r="B33" s="23"/>
+      <c r="C33" s="23"/>
+      <c r="D33" s="23"/>
+      <c r="E33" s="23"/>
+      <c r="F33" s="23"/>
+      <c r="G33" s="58" t="s">
         <v>13</v>
       </c>
-      <c r="H33" s="23"/>
+      <c r="H33" s="24"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="16" t="s">
+      <c r="A34" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="B34" s="18" t="s">
+      <c r="B34" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="C34" s="48" t="s">
+      <c r="C34" s="49" t="s">
         <v>58</v>
       </c>
-      <c r="D34" s="54" t="s">
+      <c r="D34" s="55" t="s">
         <v>59</v>
       </c>
-      <c r="E34" s="18" t="s">
+      <c r="E34" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="F34" s="18"/>
-      <c r="G34" s="18" t="s">
+      <c r="F34" s="19"/>
+      <c r="G34" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="H34" s="19" t="s">
+      <c r="H34" s="20" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" s="24"/>
-      <c r="B35" s="58" t="s">
-        <v>136</v>
-      </c>
-      <c r="C35" s="46" t="s">
+      <c r="A35" s="25"/>
+      <c r="B35" s="59" t="s">
+        <v>139</v>
+      </c>
+      <c r="C35" s="47" t="s">
         <v>60</v>
       </c>
-      <c r="D35" s="55" t="s">
+      <c r="D35" s="56" t="s">
         <v>61</v>
       </c>
-      <c r="E35" s="58" t="s">
-        <v>151</v>
+      <c r="E35" s="1" t="s">
+        <v>62</v>
       </c>
       <c r="F35" s="1"/>
       <c r="G35" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="H35" s="25" t="s">
         <v>63</v>
       </c>
+      <c r="H35" s="26" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="24"/>
+      <c r="A36" s="25"/>
       <c r="B36" s="1"/>
-      <c r="C36" s="46"/>
+      <c r="C36" s="47"/>
       <c r="D36" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E36" s="44" t="s">
+      <c r="E36" s="45" t="s">
         <v>15</v>
       </c>
       <c r="F36" s="1"/>
-      <c r="G36" s="44" t="s">
+      <c r="G36" s="45" t="s">
         <v>15</v>
       </c>
-      <c r="H36" s="25"/>
+      <c r="H36" s="26"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37" s="24"/>
+      <c r="A37" s="25"/>
       <c r="B37" s="1"/>
-      <c r="C37" s="46"/>
+      <c r="C37" s="47"/>
       <c r="D37" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="E37" s="43" t="s">
+        <v>65</v>
+      </c>
+      <c r="E37" s="44" t="s">
         <v>36</v>
       </c>
       <c r="F37" s="1"/>
-      <c r="G37" s="43" t="s">
-        <v>65</v>
-      </c>
-      <c r="H37" s="25"/>
+      <c r="G37" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="H37" s="26"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="24"/>
+      <c r="A38" s="25"/>
       <c r="B38" s="1"/>
-      <c r="C38" s="46"/>
-      <c r="D38" s="56" t="s">
+      <c r="C38" s="47"/>
+      <c r="D38" s="57" t="s">
         <v>59</v>
       </c>
-      <c r="E38" s="43"/>
+      <c r="E38" s="44"/>
       <c r="F38" s="1"/>
       <c r="G38" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="H38" s="25"/>
+      <c r="H38" s="26"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="24"/>
+      <c r="A39" s="25"/>
       <c r="B39" s="1"/>
-      <c r="C39" s="46"/>
-      <c r="D39" s="55" t="s">
-        <v>66</v>
-      </c>
-      <c r="E39" s="43"/>
+      <c r="C39" s="47"/>
+      <c r="D39" s="56" t="s">
+        <v>67</v>
+      </c>
+      <c r="E39" s="44"/>
       <c r="F39" s="1"/>
       <c r="G39" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="H39" s="25"/>
+      <c r="H39" s="26"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="24"/>
+      <c r="A40" s="25"/>
       <c r="B40" s="1"/>
-      <c r="C40" s="46"/>
-      <c r="D40" s="44" t="s">
-        <v>67</v>
-      </c>
-      <c r="E40" s="43"/>
+      <c r="C40" s="47"/>
+      <c r="D40" s="45" t="s">
+        <v>68</v>
+      </c>
+      <c r="E40" s="44"/>
       <c r="F40" s="1"/>
-      <c r="G40" s="45" t="s">
-        <v>68</v>
-      </c>
-      <c r="H40" s="25"/>
+      <c r="G40" s="46" t="s">
+        <v>69</v>
+      </c>
+      <c r="H40" s="26"/>
     </row>
     <row r="41" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="20"/>
-      <c r="B41" s="22"/>
-      <c r="C41" s="47"/>
-      <c r="D41" s="42" t="s">
-        <v>69</v>
-      </c>
-      <c r="E41" s="42"/>
-      <c r="F41" s="22"/>
-      <c r="G41" s="47" t="s">
+      <c r="A41" s="21"/>
+      <c r="B41" s="23"/>
+      <c r="C41" s="48"/>
+      <c r="D41" s="43" t="s">
         <v>70</v>
       </c>
-      <c r="H41" s="23"/>
+      <c r="E41" s="43"/>
+      <c r="F41" s="23"/>
+      <c r="G41" s="48" t="s">
+        <v>71</v>
+      </c>
+      <c r="H41" s="24"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" s="32" t="s">
-        <v>71</v>
+      <c r="A42" s="33" t="s">
+        <v>72</v>
       </c>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
@@ -7184,232 +6633,232 @@
       </c>
       <c r="F42" s="1"/>
       <c r="G42" s="1"/>
-      <c r="H42" s="25"/>
+      <c r="H42" s="26"/>
     </row>
     <row r="43" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="20"/>
-      <c r="B43" s="22"/>
-      <c r="C43" s="22"/>
-      <c r="D43" s="22"/>
-      <c r="E43" s="59" t="s">
-        <v>152</v>
-      </c>
-      <c r="F43" s="22"/>
-      <c r="G43" s="22"/>
-      <c r="H43" s="23"/>
+      <c r="A43" s="21"/>
+      <c r="B43" s="23"/>
+      <c r="C43" s="23"/>
+      <c r="D43" s="23"/>
+      <c r="E43" s="23" t="s">
+        <v>73</v>
+      </c>
+      <c r="F43" s="23"/>
+      <c r="G43" s="23"/>
+      <c r="H43" s="24"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="16" t="s">
-        <v>132</v>
-      </c>
-      <c r="B44" s="49" t="s">
-        <v>133</v>
-      </c>
-      <c r="C44" s="18"/>
-      <c r="D44" s="18" t="s">
+      <c r="A44" s="17" t="s">
+        <v>134</v>
+      </c>
+      <c r="B44" s="50" t="s">
+        <v>135</v>
+      </c>
+      <c r="C44" s="19"/>
+      <c r="D44" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="E44" s="18"/>
-      <c r="F44" s="18"/>
-      <c r="G44" s="51" t="s">
-        <v>73</v>
-      </c>
-      <c r="H44" s="19"/>
+      <c r="E44" s="19"/>
+      <c r="F44" s="19"/>
+      <c r="G44" s="52" t="s">
+        <v>75</v>
+      </c>
+      <c r="H44" s="20"/>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" s="24"/>
+      <c r="A45" s="25"/>
       <c r="B45" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C45" s="1"/>
       <c r="D45" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E45" s="1"/>
       <c r="F45" s="1"/>
-      <c r="G45" s="52" t="s">
-        <v>76</v>
-      </c>
-      <c r="H45" s="25"/>
+      <c r="G45" s="53" t="s">
+        <v>78</v>
+      </c>
+      <c r="H45" s="26"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="24"/>
-      <c r="B46" s="50" t="s">
-        <v>134</v>
+      <c r="A46" s="25"/>
+      <c r="B46" s="51" t="s">
+        <v>136</v>
       </c>
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
       <c r="E46" s="1"/>
       <c r="F46" s="1"/>
-      <c r="G46" s="52"/>
-      <c r="H46" s="25"/>
+      <c r="G46" s="53"/>
+      <c r="H46" s="26"/>
     </row>
     <row r="47" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="20"/>
-      <c r="B47" s="22" t="s">
+      <c r="A47" s="21"/>
+      <c r="B47" s="23" t="s">
+        <v>79</v>
+      </c>
+      <c r="C47" s="23"/>
+      <c r="D47" s="23"/>
+      <c r="E47" s="23"/>
+      <c r="F47" s="23"/>
+      <c r="G47" s="54"/>
+      <c r="H47" s="24"/>
+    </row>
+    <row r="48" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="27" t="s">
+        <v>80</v>
+      </c>
+      <c r="B48" s="28"/>
+      <c r="C48" s="29"/>
+      <c r="D48" s="29"/>
+      <c r="E48" s="29"/>
+      <c r="F48" s="29"/>
+      <c r="G48" s="29"/>
+      <c r="H48" s="30"/>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="B49" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C49" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D49" s="19"/>
+      <c r="E49" s="19"/>
+      <c r="F49" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="G49" s="19"/>
+      <c r="H49" s="20" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="21"/>
+      <c r="B50" s="64" t="s">
+        <v>140</v>
+      </c>
+      <c r="C50" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="C47" s="22"/>
-      <c r="D47" s="22"/>
-      <c r="E47" s="22"/>
-      <c r="F47" s="22"/>
-      <c r="G47" s="53"/>
-      <c r="H47" s="23"/>
-    </row>
-    <row r="48" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="26" t="s">
+      <c r="D50" s="23"/>
+      <c r="E50" s="23"/>
+      <c r="F50" s="23" t="s">
+        <v>82</v>
+      </c>
+      <c r="G50" s="23"/>
+      <c r="H50" s="24" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="B51" s="19"/>
+      <c r="C51" s="19"/>
+      <c r="D51" s="19"/>
+      <c r="E51" s="19"/>
+      <c r="F51" s="19"/>
+      <c r="G51" s="19"/>
+      <c r="H51" s="70" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="21"/>
+      <c r="B52" s="23"/>
+      <c r="C52" s="23"/>
+      <c r="D52" s="23"/>
+      <c r="E52" s="23"/>
+      <c r="F52" s="23"/>
+      <c r="G52" s="23"/>
+      <c r="H52" s="71" t="s">
         <v>78</v>
       </c>
-      <c r="B48" s="27"/>
-      <c r="C48" s="28"/>
-      <c r="D48" s="28"/>
-      <c r="E48" s="28"/>
-      <c r="F48" s="28"/>
-      <c r="G48" s="28"/>
-      <c r="H48" s="29"/>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="B49" s="18" t="s">
+    </row>
+    <row r="53" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="34" t="s">
+        <v>85</v>
+      </c>
+      <c r="B53" s="35"/>
+      <c r="C53" s="36"/>
+      <c r="D53" s="36"/>
+      <c r="E53" s="36"/>
+      <c r="F53" s="36"/>
+      <c r="G53" s="36"/>
+      <c r="H53" s="37"/>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="B54" s="19"/>
+      <c r="C54" s="49" t="s">
+        <v>58</v>
+      </c>
+      <c r="D54" s="42" t="s">
+        <v>68</v>
+      </c>
+      <c r="E54" s="19"/>
+      <c r="F54" s="19"/>
+      <c r="G54" s="49" t="s">
+        <v>58</v>
+      </c>
+      <c r="H54" s="20"/>
+    </row>
+    <row r="55" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="21"/>
+      <c r="B55" s="23"/>
+      <c r="C55" s="48" t="s">
+        <v>60</v>
+      </c>
+      <c r="D55" s="43" t="s">
+        <v>70</v>
+      </c>
+      <c r="E55" s="23"/>
+      <c r="F55" s="23"/>
+      <c r="G55" s="48" t="s">
+        <v>87</v>
+      </c>
+      <c r="H55" s="24"/>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="B56" s="19"/>
+      <c r="C56" s="19"/>
+      <c r="D56" s="19"/>
+      <c r="E56" s="19"/>
+      <c r="F56" s="19"/>
+      <c r="G56" s="52" t="s">
+        <v>75</v>
+      </c>
+      <c r="H56" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="C49" s="18" t="s">
-        <v>18</v>
-      </c>
-      <c r="D49" s="18"/>
-      <c r="E49" s="18"/>
-      <c r="F49" s="18" t="s">
-        <v>18</v>
-      </c>
-      <c r="G49" s="18"/>
-      <c r="H49" s="19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="20"/>
-      <c r="B50" s="59" t="s">
-        <v>137</v>
-      </c>
-      <c r="C50" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="D50" s="22"/>
-      <c r="E50" s="22"/>
-      <c r="F50" s="22" t="s">
-        <v>80</v>
-      </c>
-      <c r="G50" s="22"/>
-      <c r="H50" s="23" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A51" s="16" t="s">
-        <v>82</v>
-      </c>
-      <c r="B51" s="18"/>
-      <c r="C51" s="18"/>
-      <c r="D51" s="18"/>
-      <c r="E51" s="18"/>
-      <c r="F51" s="18"/>
-      <c r="G51" s="18"/>
-      <c r="H51" s="65" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="20"/>
-      <c r="B52" s="22"/>
-      <c r="C52" s="22"/>
-      <c r="D52" s="22"/>
-      <c r="E52" s="22"/>
-      <c r="F52" s="22"/>
-      <c r="G52" s="22"/>
-      <c r="H52" s="66" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="33" t="s">
-        <v>83</v>
-      </c>
-      <c r="B53" s="34"/>
-      <c r="C53" s="35"/>
-      <c r="D53" s="35"/>
-      <c r="E53" s="35"/>
-      <c r="F53" s="35"/>
-      <c r="G53" s="35"/>
-      <c r="H53" s="36"/>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A54" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="B54" s="18"/>
-      <c r="C54" s="48" t="s">
-        <v>58</v>
-      </c>
-      <c r="D54" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="E54" s="18"/>
-      <c r="F54" s="18"/>
-      <c r="G54" s="48" t="s">
-        <v>58</v>
-      </c>
-      <c r="H54" s="19"/>
-    </row>
-    <row r="55" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="20"/>
-      <c r="B55" s="22"/>
-      <c r="C55" s="47" t="s">
-        <v>60</v>
-      </c>
-      <c r="D55" s="42" t="s">
-        <v>69</v>
-      </c>
-      <c r="E55" s="22"/>
-      <c r="F55" s="22"/>
-      <c r="G55" s="47" t="s">
-        <v>85</v>
-      </c>
-      <c r="H55" s="23"/>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A56" s="16" t="s">
-        <v>86</v>
-      </c>
-      <c r="B56" s="18"/>
-      <c r="C56" s="18"/>
-      <c r="D56" s="18"/>
-      <c r="E56" s="18"/>
-      <c r="F56" s="18"/>
-      <c r="G56" s="51" t="s">
-        <v>73</v>
-      </c>
-      <c r="H56" s="19" t="s">
-        <v>18</v>
-      </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" s="24"/>
+      <c r="A57" s="25"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
       <c r="D57" s="1"/>
       <c r="E57" s="1"/>
       <c r="F57" s="1"/>
-      <c r="G57" s="52" t="s">
-        <v>87</v>
-      </c>
-      <c r="H57" s="25" t="s">
-        <v>88</v>
+      <c r="G57" s="53" t="s">
+        <v>89</v>
+      </c>
+      <c r="H57" s="26" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A58" s="24"/>
+      <c r="A58" s="25"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
       <c r="D58" s="1"/>
@@ -7418,151 +6867,151 @@
       <c r="G58" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="H58" s="67" t="s">
-        <v>73</v>
+      <c r="H58" s="72" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A59" s="24"/>
+      <c r="A59" s="25"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
       <c r="D59" s="1"/>
       <c r="E59" s="1"/>
       <c r="F59" s="1"/>
       <c r="G59" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="H59" s="68" t="s">
-        <v>90</v>
+        <v>91</v>
+      </c>
+      <c r="H59" s="73" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A60" s="24"/>
+      <c r="A60" s="25"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
       <c r="D60" s="1"/>
       <c r="E60" s="1"/>
       <c r="F60" s="1"/>
       <c r="G60" s="1"/>
-      <c r="H60" s="31" t="s">
+      <c r="H60" s="32" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61" s="24"/>
+      <c r="A61" s="25"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
       <c r="D61" s="1"/>
       <c r="E61" s="1"/>
       <c r="F61" s="1"/>
       <c r="G61" s="1"/>
-      <c r="H61" s="25" t="s">
-        <v>91</v>
+      <c r="H61" s="26" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A62" s="24"/>
+      <c r="A62" s="25"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
       <c r="D62" s="1"/>
       <c r="E62" s="1"/>
       <c r="F62" s="1"/>
       <c r="G62" s="1"/>
-      <c r="H62" s="31" t="s">
+      <c r="H62" s="32" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A63" s="24"/>
+      <c r="A63" s="25"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
       <c r="D63" s="1"/>
       <c r="E63" s="1"/>
       <c r="F63" s="1"/>
       <c r="G63" s="1"/>
-      <c r="H63" s="25" t="s">
-        <v>92</v>
+      <c r="H63" s="26" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A64" s="24"/>
+      <c r="A64" s="25"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
       <c r="D64" s="1"/>
       <c r="E64" s="1"/>
       <c r="F64" s="1"/>
       <c r="G64" s="1"/>
-      <c r="H64" s="67" t="s">
-        <v>73</v>
+      <c r="H64" s="72" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="65" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="20"/>
-      <c r="B65" s="22"/>
-      <c r="C65" s="22"/>
-      <c r="D65" s="22"/>
-      <c r="E65" s="22"/>
-      <c r="F65" s="22"/>
-      <c r="G65" s="22"/>
-      <c r="H65" s="66" t="s">
-        <v>87</v>
+      <c r="A65" s="21"/>
+      <c r="B65" s="23"/>
+      <c r="C65" s="23"/>
+      <c r="D65" s="23"/>
+      <c r="E65" s="23"/>
+      <c r="F65" s="23"/>
+      <c r="G65" s="23"/>
+      <c r="H65" s="71" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A66" s="16" t="s">
-        <v>93</v>
-      </c>
-      <c r="B66" s="18"/>
-      <c r="C66" s="18"/>
-      <c r="D66" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="E66" s="18"/>
-      <c r="F66" s="18"/>
-      <c r="G66" s="18"/>
-      <c r="H66" s="19"/>
+      <c r="A66" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="B66" s="19"/>
+      <c r="C66" s="19"/>
+      <c r="D66" s="42" t="s">
+        <v>68</v>
+      </c>
+      <c r="E66" s="19"/>
+      <c r="F66" s="19"/>
+      <c r="G66" s="19"/>
+      <c r="H66" s="20"/>
     </row>
     <row r="67" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="20"/>
-      <c r="B67" s="22"/>
-      <c r="C67" s="22"/>
-      <c r="D67" s="42" t="s">
-        <v>69</v>
-      </c>
-      <c r="E67" s="22"/>
-      <c r="F67" s="22"/>
-      <c r="G67" s="22"/>
-      <c r="H67" s="23"/>
+      <c r="A67" s="21"/>
+      <c r="B67" s="23"/>
+      <c r="C67" s="23"/>
+      <c r="D67" s="43" t="s">
+        <v>70</v>
+      </c>
+      <c r="E67" s="23"/>
+      <c r="F67" s="23"/>
+      <c r="G67" s="23"/>
+      <c r="H67" s="24"/>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A68" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="B68" s="18"/>
-      <c r="C68" s="18"/>
-      <c r="D68" s="18"/>
-      <c r="E68" s="18"/>
-      <c r="F68" s="18"/>
-      <c r="G68" s="18"/>
-      <c r="H68" s="65" t="s">
-        <v>73</v>
+      <c r="A68" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="B68" s="19"/>
+      <c r="C68" s="19"/>
+      <c r="D68" s="19"/>
+      <c r="E68" s="19"/>
+      <c r="F68" s="19"/>
+      <c r="G68" s="19"/>
+      <c r="H68" s="70" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="69" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="20"/>
-      <c r="B69" s="22"/>
-      <c r="C69" s="22"/>
-      <c r="D69" s="22"/>
-      <c r="E69" s="22"/>
-      <c r="F69" s="22"/>
-      <c r="G69" s="22"/>
-      <c r="H69" s="66" t="s">
-        <v>76</v>
+      <c r="A69" s="21"/>
+      <c r="B69" s="23"/>
+      <c r="C69" s="23"/>
+      <c r="D69" s="23"/>
+      <c r="E69" s="23"/>
+      <c r="F69" s="23"/>
+      <c r="G69" s="23"/>
+      <c r="H69" s="71" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A70" s="32" t="s">
-        <v>95</v>
+      <c r="A70" s="33" t="s">
+        <v>97</v>
       </c>
       <c r="B70" s="1"/>
       <c r="C70" s="1" t="s">
@@ -7578,28 +7027,28 @@
         <v>18</v>
       </c>
       <c r="G70" s="1"/>
-      <c r="H70" s="25"/>
+      <c r="H70" s="26"/>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A71" s="24"/>
+      <c r="A71" s="25"/>
       <c r="B71" s="1"/>
       <c r="C71" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="G71" s="1"/>
-      <c r="H71" s="25"/>
+      <c r="H71" s="26"/>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A72" s="24"/>
+      <c r="A72" s="25"/>
       <c r="B72" s="1"/>
       <c r="C72" s="1"/>
       <c r="D72" s="2" t="s">
@@ -7608,240 +7057,240 @@
       <c r="E72" s="1"/>
       <c r="F72" s="1"/>
       <c r="G72" s="1"/>
-      <c r="H72" s="25"/>
+      <c r="H72" s="26"/>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A73" s="24"/>
+      <c r="A73" s="25"/>
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
       <c r="D73" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E73" s="1"/>
       <c r="F73" s="1"/>
       <c r="G73" s="1"/>
-      <c r="H73" s="25"/>
+      <c r="H73" s="26"/>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A74" s="24"/>
+      <c r="A74" s="25"/>
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
-      <c r="D74" s="44" t="s">
+      <c r="D74" s="45" t="s">
         <v>15</v>
       </c>
       <c r="E74" s="1"/>
       <c r="F74" s="1"/>
       <c r="G74" s="1"/>
-      <c r="H74" s="25"/>
+      <c r="H74" s="26"/>
     </row>
     <row r="75" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="20"/>
-      <c r="B75" s="22"/>
-      <c r="C75" s="22"/>
-      <c r="D75" s="42" t="s">
-        <v>101</v>
-      </c>
-      <c r="E75" s="22"/>
-      <c r="F75" s="22"/>
-      <c r="G75" s="22"/>
-      <c r="H75" s="23"/>
+      <c r="A75" s="21"/>
+      <c r="B75" s="23"/>
+      <c r="C75" s="23"/>
+      <c r="D75" s="43" t="s">
+        <v>103</v>
+      </c>
+      <c r="E75" s="23"/>
+      <c r="F75" s="23"/>
+      <c r="G75" s="23"/>
+      <c r="H75" s="24"/>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A76" s="16" t="s">
-        <v>102</v>
-      </c>
-      <c r="B76" s="18"/>
-      <c r="C76" s="18"/>
-      <c r="D76" s="18"/>
-      <c r="E76" s="18"/>
-      <c r="F76" s="18"/>
-      <c r="G76" s="51" t="s">
-        <v>73</v>
-      </c>
-      <c r="H76" s="65" t="s">
-        <v>73</v>
+      <c r="A76" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="B76" s="19"/>
+      <c r="C76" s="19"/>
+      <c r="D76" s="19"/>
+      <c r="E76" s="19"/>
+      <c r="F76" s="19"/>
+      <c r="G76" s="52" t="s">
+        <v>75</v>
+      </c>
+      <c r="H76" s="70" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A77" s="24"/>
+      <c r="A77" s="25"/>
       <c r="B77" s="1"/>
       <c r="C77" s="1"/>
       <c r="D77" s="1"/>
       <c r="E77" s="1"/>
       <c r="F77" s="1"/>
-      <c r="G77" s="52" t="s">
-        <v>103</v>
-      </c>
-      <c r="H77" s="68" t="s">
-        <v>104</v>
+      <c r="G77" s="53" t="s">
+        <v>105</v>
+      </c>
+      <c r="H77" s="73" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A78" s="24"/>
+      <c r="A78" s="25"/>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
       <c r="D78" s="1"/>
       <c r="E78" s="1"/>
       <c r="F78" s="1"/>
-      <c r="G78" s="45" t="s">
+      <c r="G78" s="46" t="s">
         <v>58</v>
       </c>
-      <c r="H78" s="67" t="s">
-        <v>73</v>
+      <c r="H78" s="72" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A79" s="24"/>
+      <c r="A79" s="25"/>
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
       <c r="D79" s="1"/>
       <c r="E79" s="1"/>
       <c r="F79" s="1"/>
-      <c r="G79" s="46" t="s">
-        <v>85</v>
-      </c>
-      <c r="H79" s="68" t="s">
-        <v>105</v>
+      <c r="G79" s="47" t="s">
+        <v>87</v>
+      </c>
+      <c r="H79" s="73" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A80" s="24"/>
+      <c r="A80" s="25"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
       <c r="D80" s="1"/>
       <c r="E80" s="1"/>
       <c r="F80" s="1"/>
-      <c r="G80" s="46"/>
-      <c r="H80" s="67" t="s">
-        <v>106</v>
+      <c r="G80" s="47"/>
+      <c r="H80" s="72" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A81" s="24"/>
+      <c r="A81" s="25"/>
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
       <c r="D81" s="1"/>
       <c r="E81" s="1"/>
       <c r="F81" s="1"/>
-      <c r="G81" s="46"/>
-      <c r="H81" s="68" t="s">
-        <v>107</v>
+      <c r="G81" s="47"/>
+      <c r="H81" s="73" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A82" s="24"/>
+      <c r="A82" s="25"/>
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
       <c r="D82" s="1"/>
       <c r="E82" s="1"/>
       <c r="F82" s="1"/>
-      <c r="G82" s="46"/>
-      <c r="H82" s="31" t="s">
+      <c r="G82" s="47"/>
+      <c r="H82" s="32" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="83" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="20"/>
-      <c r="B83" s="22"/>
-      <c r="C83" s="22"/>
-      <c r="D83" s="22"/>
-      <c r="E83" s="22"/>
-      <c r="F83" s="22"/>
-      <c r="G83" s="47"/>
-      <c r="H83" s="23" t="s">
-        <v>108</v>
+      <c r="A83" s="21"/>
+      <c r="B83" s="23"/>
+      <c r="C83" s="23"/>
+      <c r="D83" s="23"/>
+      <c r="E83" s="23"/>
+      <c r="F83" s="23"/>
+      <c r="G83" s="48"/>
+      <c r="H83" s="24" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="84" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="26" t="s">
-        <v>109</v>
-      </c>
-      <c r="B84" s="27"/>
-      <c r="C84" s="28"/>
-      <c r="D84" s="28"/>
-      <c r="E84" s="28"/>
-      <c r="F84" s="28"/>
-      <c r="G84" s="28"/>
-      <c r="H84" s="29"/>
+      <c r="A84" s="27" t="s">
+        <v>111</v>
+      </c>
+      <c r="B84" s="28"/>
+      <c r="C84" s="29"/>
+      <c r="D84" s="29"/>
+      <c r="E84" s="29"/>
+      <c r="F84" s="29"/>
+      <c r="G84" s="29"/>
+      <c r="H84" s="30"/>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A85" s="16" t="s">
-        <v>110</v>
-      </c>
-      <c r="B85" s="18"/>
-      <c r="C85" s="18"/>
-      <c r="D85" s="18"/>
-      <c r="E85" s="18"/>
-      <c r="F85" s="18"/>
-      <c r="G85" s="54" t="s">
+      <c r="A85" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="B85" s="19"/>
+      <c r="C85" s="19"/>
+      <c r="D85" s="19"/>
+      <c r="E85" s="19"/>
+      <c r="F85" s="19"/>
+      <c r="G85" s="55" t="s">
         <v>12</v>
       </c>
-      <c r="H85" s="19"/>
+      <c r="H85" s="20"/>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A86" s="24"/>
+      <c r="A86" s="25"/>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
       <c r="D86" s="1"/>
       <c r="E86" s="1"/>
       <c r="F86" s="1"/>
-      <c r="G86" s="55" t="s">
+      <c r="G86" s="56" t="s">
         <v>13</v>
       </c>
-      <c r="H86" s="25"/>
+      <c r="H86" s="26"/>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A87" s="24"/>
+      <c r="A87" s="25"/>
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
       <c r="D87" s="1"/>
       <c r="E87" s="1"/>
       <c r="F87" s="1"/>
-      <c r="G87" s="56" t="s">
+      <c r="G87" s="57" t="s">
         <v>12</v>
       </c>
-      <c r="H87" s="25"/>
+      <c r="H87" s="26"/>
     </row>
     <row r="88" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="20"/>
-      <c r="B88" s="22"/>
-      <c r="C88" s="22"/>
-      <c r="D88" s="22"/>
-      <c r="E88" s="22"/>
-      <c r="F88" s="22"/>
-      <c r="G88" s="57" t="s">
+      <c r="A88" s="21"/>
+      <c r="B88" s="23"/>
+      <c r="C88" s="23"/>
+      <c r="D88" s="23"/>
+      <c r="E88" s="23"/>
+      <c r="F88" s="23"/>
+      <c r="G88" s="58" t="s">
         <v>41</v>
       </c>
-      <c r="H88" s="23"/>
+      <c r="H88" s="24"/>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A89" s="16" t="s">
-        <v>111</v>
-      </c>
-      <c r="B89" s="18"/>
-      <c r="C89" s="18"/>
-      <c r="D89" s="18"/>
-      <c r="E89" s="18"/>
-      <c r="F89" s="18"/>
-      <c r="G89" s="51" t="s">
-        <v>73</v>
-      </c>
-      <c r="H89" s="19"/>
+      <c r="A89" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="B89" s="19"/>
+      <c r="C89" s="19"/>
+      <c r="D89" s="19"/>
+      <c r="E89" s="19"/>
+      <c r="F89" s="19"/>
+      <c r="G89" s="52" t="s">
+        <v>75</v>
+      </c>
+      <c r="H89" s="20"/>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A90" s="24"/>
+      <c r="A90" s="25"/>
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
       <c r="D90" s="1"/>
       <c r="E90" s="1"/>
       <c r="F90" s="1"/>
-      <c r="G90" s="52" t="s">
+      <c r="G90" s="53" t="s">
         <v>27</v>
       </c>
-      <c r="H90" s="25"/>
+      <c r="H90" s="26"/>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A91" s="24"/>
+      <c r="A91" s="25"/>
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
       <c r="D91" s="1"/>
@@ -7850,48 +7299,48 @@
       <c r="G91" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="H91" s="25"/>
+      <c r="H91" s="26"/>
     </row>
     <row r="92" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="20"/>
-      <c r="B92" s="22"/>
-      <c r="C92" s="22"/>
-      <c r="D92" s="22"/>
-      <c r="E92" s="22"/>
-      <c r="F92" s="22"/>
-      <c r="G92" s="22" t="s">
-        <v>112</v>
-      </c>
-      <c r="H92" s="23"/>
+      <c r="A92" s="21"/>
+      <c r="B92" s="23"/>
+      <c r="C92" s="23"/>
+      <c r="D92" s="23"/>
+      <c r="E92" s="23"/>
+      <c r="F92" s="23"/>
+      <c r="G92" s="23" t="s">
+        <v>114</v>
+      </c>
+      <c r="H92" s="24"/>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A93" s="16" t="s">
-        <v>113</v>
-      </c>
-      <c r="B93" s="18"/>
-      <c r="C93" s="18"/>
-      <c r="D93" s="18" t="s">
+      <c r="A93" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="B93" s="19"/>
+      <c r="C93" s="19"/>
+      <c r="D93" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="E93" s="18"/>
-      <c r="F93" s="18"/>
-      <c r="G93" s="18"/>
-      <c r="H93" s="19"/>
+      <c r="E93" s="19"/>
+      <c r="F93" s="19"/>
+      <c r="G93" s="19"/>
+      <c r="H93" s="20"/>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A94" s="24"/>
+      <c r="A94" s="25"/>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
       <c r="D94" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E94" s="1"/>
       <c r="F94" s="1"/>
       <c r="G94" s="1"/>
-      <c r="H94" s="25"/>
+      <c r="H94" s="26"/>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A95" s="24"/>
+      <c r="A95" s="25"/>
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
       <c r="D95" s="2" t="s">
@@ -7900,106 +7349,106 @@
       <c r="E95" s="1"/>
       <c r="F95" s="1"/>
       <c r="G95" s="1"/>
-      <c r="H95" s="25"/>
+      <c r="H95" s="26"/>
     </row>
     <row r="96" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="20"/>
-      <c r="B96" s="22"/>
-      <c r="C96" s="22"/>
-      <c r="D96" s="22" t="s">
+      <c r="A96" s="21"/>
+      <c r="B96" s="23"/>
+      <c r="C96" s="23"/>
+      <c r="D96" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="E96" s="23"/>
+      <c r="F96" s="23"/>
+      <c r="G96" s="23"/>
+      <c r="H96" s="24"/>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" s="17" t="s">
+        <v>117</v>
+      </c>
+      <c r="B97" s="19"/>
+      <c r="C97" s="19"/>
+      <c r="D97" s="19"/>
+      <c r="E97" s="19"/>
+      <c r="F97" s="19"/>
+      <c r="G97" s="55" t="s">
+        <v>59</v>
+      </c>
+      <c r="H97" s="70" t="s">
         <v>75</v>
       </c>
-      <c r="E96" s="22"/>
-      <c r="F96" s="22"/>
-      <c r="G96" s="22"/>
-      <c r="H96" s="23"/>
-    </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A97" s="16" t="s">
-        <v>115</v>
-      </c>
-      <c r="B97" s="18"/>
-      <c r="C97" s="18"/>
-      <c r="D97" s="18"/>
-      <c r="E97" s="18"/>
-      <c r="F97" s="18"/>
-      <c r="G97" s="54" t="s">
-        <v>59</v>
-      </c>
-      <c r="H97" s="65" t="s">
-        <v>73</v>
-      </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A98" s="24"/>
+      <c r="A98" s="25"/>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
       <c r="D98" s="1"/>
       <c r="E98" s="1"/>
       <c r="F98" s="1"/>
-      <c r="G98" s="55" t="s">
-        <v>116</v>
-      </c>
-      <c r="H98" s="68" t="s">
-        <v>103</v>
+      <c r="G98" s="56" t="s">
+        <v>118</v>
+      </c>
+      <c r="H98" s="73" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A99" s="24"/>
+      <c r="A99" s="25"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
       <c r="D99" s="1"/>
       <c r="E99" s="1"/>
       <c r="F99" s="1"/>
-      <c r="G99" s="56" t="s">
+      <c r="G99" s="57" t="s">
         <v>12</v>
       </c>
-      <c r="H99" s="68"/>
+      <c r="H99" s="73"/>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A100" s="24"/>
+      <c r="A100" s="25"/>
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
       <c r="D100" s="1"/>
       <c r="E100" s="1"/>
       <c r="F100" s="1"/>
-      <c r="G100" s="55" t="s">
+      <c r="G100" s="56" t="s">
         <v>61</v>
       </c>
-      <c r="H100" s="68"/>
+      <c r="H100" s="73"/>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A101" s="24"/>
+      <c r="A101" s="25"/>
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
       <c r="D101" s="1"/>
       <c r="E101" s="1"/>
       <c r="F101" s="1"/>
-      <c r="G101" s="69" t="s">
-        <v>73</v>
-      </c>
-      <c r="H101" s="68"/>
+      <c r="G101" s="74" t="s">
+        <v>75</v>
+      </c>
+      <c r="H101" s="73"/>
     </row>
     <row r="102" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="20"/>
-      <c r="B102" s="22"/>
-      <c r="C102" s="22"/>
-      <c r="D102" s="22"/>
-      <c r="E102" s="22"/>
-      <c r="F102" s="22"/>
-      <c r="G102" s="53" t="s">
-        <v>117</v>
-      </c>
-      <c r="H102" s="66"/>
+      <c r="A102" s="21"/>
+      <c r="B102" s="23"/>
+      <c r="C102" s="23"/>
+      <c r="D102" s="23"/>
+      <c r="E102" s="23"/>
+      <c r="F102" s="23"/>
+      <c r="G102" s="54" t="s">
+        <v>119</v>
+      </c>
+      <c r="H102" s="71"/>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B103" s="30"/>
-      <c r="C103" s="30"/>
-      <c r="D103" s="30"/>
-      <c r="E103" s="30"/>
-      <c r="F103" s="30"/>
-      <c r="G103" s="30"/>
-      <c r="H103" s="30"/>
+      <c r="B103" s="31"/>
+      <c r="C103" s="31"/>
+      <c r="D103" s="31"/>
+      <c r="E103" s="31"/>
+      <c r="F103" s="31"/>
+      <c r="G103" s="31"/>
+      <c r="H103" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="30">
@@ -8051,36 +7500,36 @@
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B4" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
+      <c r="B4" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B5" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="C5" s="14"/>
-      <c r="D5" s="14"/>
-      <c r="E5" s="14"/>
+      <c r="B5" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>3</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -8255,7 +7704,7 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B17" s="7">
         <v>0</v>
@@ -8272,7 +7721,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B18" s="7">
         <v>0</v>
@@ -8289,7 +7738,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B19" s="7">
         <v>0</v>
@@ -8306,7 +7755,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B20" s="7">
         <v>0</v>
@@ -8323,7 +7772,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B21" s="7">
         <v>0</v>
@@ -8340,7 +7789,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B22" s="7">
         <v>0</v>
@@ -8357,7 +7806,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B23" s="7">
         <v>0</v>
@@ -8374,7 +7823,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B24" s="7">
         <v>0</v>
@@ -8391,7 +7840,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B25" s="7">
         <v>0</v>
@@ -8408,7 +7857,7 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B26" s="7">
         <v>0</v>
@@ -8425,7 +7874,7 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B27" s="7">
         <v>0</v>
@@ -8442,7 +7891,7 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B28" s="7">
         <v>0</v>
@@ -8459,7 +7908,7 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B29" s="7">
         <v>0</v>
@@ -8476,7 +7925,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B30" s="7">
         <v>0</v>
@@ -8493,7 +7942,7 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B31" s="7">
         <v>0</v>
@@ -8510,7 +7959,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B32" s="7">
         <v>0</v>
@@ -8527,7 +7976,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B33" s="7">
         <v>0</v>
@@ -8577,40 +8026,40 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B5" s="11"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
   </sheetData>
@@ -8785,13 +8234,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{237B6F2F-DDC0-43CB-AD4A-7D13B3C1AC2A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C9482BC0-D9A0-4F2E-A662-55F6A6E1E8C5}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{79ADD44D-1503-49B4-97A7-4450ECE9CCBB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DA586971-1ADE-4638-9DB3-7A0A07ABD948}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74364E4E-0E00-4523-B096-2A8C621F84C3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA842A77-17E4-4803-881D-F58312C9A224}"/>
 </file>
--- a/Plannings 2026 S26.xlsx
+++ b/Plannings 2026 S26.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="8_{A23AA2D1-9819-4B65-9C3A-D83FC30F8B22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5B285F09-A81C-42CB-AF32-5E43987A31CE}"/>
+  <xr:revisionPtr revIDLastSave="16" documentId="8_{A23AA2D1-9819-4B65-9C3A-D83FC30F8B22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9B802D4B-AF01-46F2-AB37-82BCCECC5D38}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -321,9 +321,6 @@
     <t>09:50/18:00</t>
   </si>
   <si>
-    <t>13:15/23:00</t>
-  </si>
-  <si>
     <t>18:00/19:50</t>
   </si>
   <si>
@@ -481,6 +478,9 @@
   </si>
   <si>
     <t>18:30/24:00</t>
+  </si>
+  <si>
+    <t>13:00/23:00</t>
   </si>
 </sst>
 </file>
@@ -6544,7 +6544,7 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B3" s="60" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C3" s="61"/>
       <c r="D3" s="61"/>
@@ -6555,22 +6555,22 @@
     </row>
     <row r="4" spans="1:8" s="63" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B4" s="64" t="s">
+        <v>138</v>
+      </c>
+      <c r="C4" s="64" t="s">
         <v>139</v>
       </c>
-      <c r="C4" s="64" t="s">
+      <c r="D4" s="64" t="s">
         <v>140</v>
       </c>
-      <c r="D4" s="64" t="s">
+      <c r="E4" s="64" t="s">
         <v>141</v>
       </c>
-      <c r="E4" s="64" t="s">
+      <c r="F4" s="64" t="s">
         <v>142</v>
       </c>
-      <c r="F4" s="64" t="s">
+      <c r="G4" s="64" t="s">
         <v>143</v>
-      </c>
-      <c r="G4" s="64" t="s">
-        <v>144</v>
       </c>
       <c r="H4" s="64" t="s">
         <v>73</v>
@@ -6688,10 +6688,10 @@
         <v>23</v>
       </c>
       <c r="E11" s="58" t="s">
+        <v>147</v>
+      </c>
+      <c r="F11" s="58" t="s">
         <v>148</v>
-      </c>
-      <c r="F11" s="58" t="s">
-        <v>149</v>
       </c>
       <c r="G11" s="58"/>
       <c r="H11" s="77"/>
@@ -6793,20 +6793,20 @@
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="24"/>
       <c r="B18" s="58" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C18" s="58" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D18" s="58" t="s">
         <v>33</v>
       </c>
       <c r="E18" s="58"/>
       <c r="F18" s="58" t="s">
+        <v>145</v>
+      </c>
+      <c r="G18" s="58" t="s">
         <v>146</v>
-      </c>
-      <c r="G18" s="58" t="s">
-        <v>147</v>
       </c>
       <c r="H18" s="77"/>
     </row>
@@ -6907,7 +6907,7 @@
         <v>43</v>
       </c>
       <c r="F25" s="58" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G25" s="1"/>
       <c r="H25" s="25"/>
@@ -7065,7 +7065,7 @@
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="24"/>
       <c r="B35" s="58" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C35" s="46" t="s">
         <v>60</v>
@@ -7074,7 +7074,7 @@
         <v>61</v>
       </c>
       <c r="E35" s="58" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F35" s="1"/>
       <c r="G35" s="1" t="s">
@@ -7192,7 +7192,7 @@
       <c r="C43" s="22"/>
       <c r="D43" s="22"/>
       <c r="E43" s="59" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F43" s="22"/>
       <c r="G43" s="22"/>
@@ -7200,10 +7200,10 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="B44" s="49" t="s">
         <v>132</v>
-      </c>
-      <c r="B44" s="49" t="s">
-        <v>133</v>
       </c>
       <c r="C44" s="18"/>
       <c r="D44" s="18" t="s">
@@ -7235,7 +7235,7 @@
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="24"/>
       <c r="B46" s="50" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
@@ -7291,7 +7291,7 @@
     <row r="50" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="20"/>
       <c r="B50" s="59" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C50" s="22" t="s">
         <v>75</v>
@@ -7592,8 +7592,8 @@
       <c r="E71" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="F71" s="1" t="s">
-        <v>99</v>
+      <c r="F71" s="58" t="s">
+        <v>152</v>
       </c>
       <c r="G71" s="1"/>
       <c r="H71" s="25"/>
@@ -7615,7 +7615,7 @@
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
       <c r="D73" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E73" s="1"/>
       <c r="F73" s="1"/>
@@ -7639,7 +7639,7 @@
       <c r="B75" s="22"/>
       <c r="C75" s="22"/>
       <c r="D75" s="42" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E75" s="22"/>
       <c r="F75" s="22"/>
@@ -7648,7 +7648,7 @@
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" s="16" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B76" s="18"/>
       <c r="C76" s="18"/>
@@ -7670,10 +7670,10 @@
       <c r="E77" s="1"/>
       <c r="F77" s="1"/>
       <c r="G77" s="52" t="s">
+        <v>102</v>
+      </c>
+      <c r="H77" s="68" t="s">
         <v>103</v>
-      </c>
-      <c r="H77" s="68" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
@@ -7701,7 +7701,7 @@
         <v>85</v>
       </c>
       <c r="H79" s="68" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
@@ -7713,7 +7713,7 @@
       <c r="F80" s="1"/>
       <c r="G80" s="46"/>
       <c r="H80" s="67" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
@@ -7725,7 +7725,7 @@
       <c r="F81" s="1"/>
       <c r="G81" s="46"/>
       <c r="H81" s="68" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
@@ -7749,12 +7749,12 @@
       <c r="F83" s="22"/>
       <c r="G83" s="47"/>
       <c r="H83" s="23" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="84" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="26" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B84" s="27"/>
       <c r="C84" s="28"/>
@@ -7766,7 +7766,7 @@
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" s="16" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B85" s="18"/>
       <c r="C85" s="18"/>
@@ -7816,7 +7816,7 @@
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" s="16" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B89" s="18"/>
       <c r="C89" s="18"/>
@@ -7860,17 +7860,17 @@
       <c r="E92" s="22"/>
       <c r="F92" s="22"/>
       <c r="G92" s="22" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H92" s="23"/>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" s="16" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B93" s="18"/>
       <c r="C93" s="18"/>
-      <c r="D93" s="18" t="s">
+      <c r="D93" s="54" t="s">
         <v>39</v>
       </c>
       <c r="E93" s="18"/>
@@ -7882,8 +7882,8 @@
       <c r="A94" s="24"/>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
-      <c r="D94" s="1" t="s">
-        <v>114</v>
+      <c r="D94" s="55" t="s">
+        <v>113</v>
       </c>
       <c r="E94" s="1"/>
       <c r="F94" s="1"/>
@@ -7916,7 +7916,7 @@
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" s="16" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B97" s="18"/>
       <c r="C97" s="18"/>
@@ -7938,10 +7938,10 @@
       <c r="E98" s="1"/>
       <c r="F98" s="1"/>
       <c r="G98" s="55" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H98" s="68" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
@@ -7988,7 +7988,7 @@
       <c r="E102" s="22"/>
       <c r="F102" s="22"/>
       <c r="G102" s="53" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H102" s="66"/>
     </row>
@@ -8052,7 +8052,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B4" s="13" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C4" s="13"/>
       <c r="D4" s="13"/>
@@ -8060,7 +8060,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B5" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C5" s="14"/>
       <c r="D5" s="14"/>
@@ -8071,16 +8071,16 @@
         <v>3</v>
       </c>
       <c r="B6" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="C6" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="D6" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="E6" s="6" t="s">
         <v>122</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -8442,7 +8442,7 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B28" s="7">
         <v>0</v>
@@ -8459,7 +8459,7 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B29" s="7">
         <v>0</v>
@@ -8476,7 +8476,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B30" s="7">
         <v>0</v>
@@ -8493,7 +8493,7 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B31" s="7">
         <v>0</v>
@@ -8510,7 +8510,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B32" s="7">
         <v>0</v>
@@ -8527,7 +8527,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B33" s="7">
         <v>0</v>
@@ -8577,21 +8577,21 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="B4" s="11" t="s">
         <v>124</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B5" s="11"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>95</v>
@@ -8599,18 +8599,18 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="B7" s="11" t="s">
         <v>128</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="B8" s="11" t="s">
         <v>130</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -8785,13 +8785,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{237B6F2F-DDC0-43CB-AD4A-7D13B3C1AC2A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{574719B2-3B79-4885-B0A8-0EB64E8DF50B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{79ADD44D-1503-49B4-97A7-4450ECE9CCBB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{51C725EF-523F-4D29-B493-0791DCF71EAA}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74364E4E-0E00-4523-B096-2A8C621F84C3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D867BE1-3343-4D33-8ADE-E24AA35C0BC6}"/>
 </file>
--- a/Plannings 2026 S26.xlsx
+++ b/Plannings 2026 S26.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="8_{A23AA2D1-9819-4B65-9C3A-D83FC30F8B22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9B802D4B-AF01-46F2-AB37-82BCCECC5D38}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="8_{A23AA2D1-9819-4B65-9C3A-D83FC30F8B22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B1710F38-0AC6-4914-B675-5AB1093980AC}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -171,9 +171,6 @@
     <t>17:15/19:15</t>
   </si>
   <si>
-    <t>14:15/16:45</t>
-  </si>
-  <si>
     <t>17:45/24:00</t>
   </si>
   <si>
@@ -183,9 +180,6 @@
     <t>19:15/21:15</t>
   </si>
   <si>
-    <t>16:45/18:30</t>
-  </si>
-  <si>
     <t>21:15/22:00</t>
   </si>
   <si>
@@ -481,6 +475,12 @@
   </si>
   <si>
     <t>13:00/23:00</t>
+  </si>
+  <si>
+    <t>17:15/18:30</t>
+  </si>
+  <si>
+    <t>14:15/17:15</t>
   </si>
 </sst>
 </file>
@@ -994,7 +994,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1231,6 +1231,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -6544,7 +6547,7 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B3" s="60" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C3" s="61"/>
       <c r="D3" s="61"/>
@@ -6555,25 +6558,25 @@
     </row>
     <row r="4" spans="1:8" s="63" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B4" s="64" t="s">
+        <v>136</v>
+      </c>
+      <c r="C4" s="64" t="s">
+        <v>137</v>
+      </c>
+      <c r="D4" s="64" t="s">
         <v>138</v>
       </c>
-      <c r="C4" s="64" t="s">
+      <c r="E4" s="64" t="s">
         <v>139</v>
       </c>
-      <c r="D4" s="64" t="s">
+      <c r="F4" s="64" t="s">
         <v>140</v>
       </c>
-      <c r="E4" s="64" t="s">
+      <c r="G4" s="64" t="s">
         <v>141</v>
       </c>
-      <c r="F4" s="64" t="s">
-        <v>142</v>
-      </c>
-      <c r="G4" s="64" t="s">
-        <v>143</v>
-      </c>
       <c r="H4" s="64" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -6688,10 +6691,10 @@
         <v>23</v>
       </c>
       <c r="E11" s="58" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F11" s="58" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="G11" s="58"/>
       <c r="H11" s="77"/>
@@ -6793,20 +6796,20 @@
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="24"/>
       <c r="B18" s="58" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C18" s="58" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D18" s="58" t="s">
         <v>33</v>
       </c>
       <c r="E18" s="58"/>
       <c r="F18" s="58" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="G18" s="58" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="H18" s="77"/>
     </row>
@@ -6907,7 +6910,7 @@
         <v>43</v>
       </c>
       <c r="F25" s="58" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="G25" s="1"/>
       <c r="H25" s="25"/>
@@ -6940,11 +6943,11 @@
       <c r="C27" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="D27" s="55" t="s">
+      <c r="D27" s="80" t="s">
+        <v>152</v>
+      </c>
+      <c r="E27" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>50</v>
       </c>
       <c r="F27" s="73" t="s">
         <v>44</v>
@@ -6971,13 +6974,13 @@
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="24"/>
       <c r="B29" s="55" t="s">
+        <v>50</v>
+      </c>
+      <c r="C29" s="55" t="s">
         <v>51</v>
       </c>
-      <c r="C29" s="55" t="s">
-        <v>52</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>53</v>
+      <c r="D29" s="58" t="s">
+        <v>151</v>
       </c>
       <c r="E29" s="1"/>
       <c r="F29" s="73"/>
@@ -7002,10 +7005,10 @@
       <c r="A31" s="20"/>
       <c r="B31" s="57"/>
       <c r="C31" s="22" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D31" s="57" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E31" s="22"/>
       <c r="F31" s="74"/>
@@ -7014,7 +7017,7 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="16" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B32" s="18"/>
       <c r="C32" s="18"/>
@@ -7040,16 +7043,16 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="16" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B34" s="18" t="s">
         <v>18</v>
       </c>
       <c r="C34" s="48" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D34" s="54" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E34" s="18" t="s">
         <v>18</v>
@@ -7065,23 +7068,23 @@
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="24"/>
       <c r="B35" s="58" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C35" s="46" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D35" s="55" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E35" s="58" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F35" s="1"/>
       <c r="G35" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="H35" s="25" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
@@ -7105,14 +7108,14 @@
       <c r="B37" s="1"/>
       <c r="C37" s="46"/>
       <c r="D37" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E37" s="43" t="s">
         <v>36</v>
       </c>
       <c r="F37" s="1"/>
       <c r="G37" s="43" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="H37" s="25"/>
     </row>
@@ -7121,7 +7124,7 @@
       <c r="B38" s="1"/>
       <c r="C38" s="46"/>
       <c r="D38" s="56" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E38" s="43"/>
       <c r="F38" s="1"/>
@@ -7135,7 +7138,7 @@
       <c r="B39" s="1"/>
       <c r="C39" s="46"/>
       <c r="D39" s="55" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E39" s="43"/>
       <c r="F39" s="1"/>
@@ -7149,12 +7152,12 @@
       <c r="B40" s="1"/>
       <c r="C40" s="46"/>
       <c r="D40" s="44" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E40" s="43"/>
       <c r="F40" s="1"/>
       <c r="G40" s="45" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="H40" s="25"/>
     </row>
@@ -7163,18 +7166,18 @@
       <c r="B41" s="22"/>
       <c r="C41" s="47"/>
       <c r="D41" s="42" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E41" s="42"/>
       <c r="F41" s="22"/>
       <c r="G41" s="47" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="H41" s="23"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="32" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
@@ -7192,7 +7195,7 @@
       <c r="C43" s="22"/>
       <c r="D43" s="22"/>
       <c r="E43" s="59" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="F43" s="22"/>
       <c r="G43" s="22"/>
@@ -7200,10 +7203,10 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="16" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B44" s="49" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C44" s="18"/>
       <c r="D44" s="18" t="s">
@@ -7212,30 +7215,30 @@
       <c r="E44" s="18"/>
       <c r="F44" s="18"/>
       <c r="G44" s="51" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="H44" s="19"/>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="24"/>
       <c r="B45" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C45" s="1"/>
       <c r="D45" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E45" s="1"/>
       <c r="F45" s="1"/>
       <c r="G45" s="52" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H45" s="25"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="24"/>
       <c r="B46" s="50" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
@@ -7247,7 +7250,7 @@
     <row r="47" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="20"/>
       <c r="B47" s="22" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C47" s="22"/>
       <c r="D47" s="22"/>
@@ -7258,7 +7261,7 @@
     </row>
     <row r="48" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="26" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B48" s="27"/>
       <c r="C48" s="28"/>
@@ -7270,7 +7273,7 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="16" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B49" s="18" t="s">
         <v>18</v>
@@ -7291,24 +7294,24 @@
     <row r="50" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="20"/>
       <c r="B50" s="59" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C50" s="22" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D50" s="22"/>
       <c r="E50" s="22"/>
       <c r="F50" s="22" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G50" s="22"/>
       <c r="H50" s="23" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="16" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B51" s="18"/>
       <c r="C51" s="18"/>
@@ -7317,7 +7320,7 @@
       <c r="F51" s="18"/>
       <c r="G51" s="18"/>
       <c r="H51" s="65" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -7329,12 +7332,12 @@
       <c r="F52" s="22"/>
       <c r="G52" s="22"/>
       <c r="H52" s="66" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="33" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B53" s="34"/>
       <c r="C53" s="35"/>
@@ -7346,19 +7349,19 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="16" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B54" s="18"/>
       <c r="C54" s="48" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D54" s="41" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E54" s="18"/>
       <c r="F54" s="18"/>
       <c r="G54" s="48" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H54" s="19"/>
     </row>
@@ -7366,21 +7369,21 @@
       <c r="A55" s="20"/>
       <c r="B55" s="22"/>
       <c r="C55" s="47" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D55" s="42" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E55" s="22"/>
       <c r="F55" s="22"/>
       <c r="G55" s="47" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H55" s="23"/>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="16" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B56" s="18"/>
       <c r="C56" s="18"/>
@@ -7388,7 +7391,7 @@
       <c r="E56" s="18"/>
       <c r="F56" s="18"/>
       <c r="G56" s="51" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="H56" s="19" t="s">
         <v>18</v>
@@ -7402,10 +7405,10 @@
       <c r="E57" s="1"/>
       <c r="F57" s="1"/>
       <c r="G57" s="52" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H57" s="25" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
@@ -7419,7 +7422,7 @@
         <v>18</v>
       </c>
       <c r="H58" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
@@ -7430,10 +7433,10 @@
       <c r="E59" s="1"/>
       <c r="F59" s="1"/>
       <c r="G59" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H59" s="68" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
@@ -7457,7 +7460,7 @@
       <c r="F61" s="1"/>
       <c r="G61" s="1"/>
       <c r="H61" s="25" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
@@ -7481,7 +7484,7 @@
       <c r="F63" s="1"/>
       <c r="G63" s="1"/>
       <c r="H63" s="25" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
@@ -7493,7 +7496,7 @@
       <c r="F64" s="1"/>
       <c r="G64" s="1"/>
       <c r="H64" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="65" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -7505,17 +7508,17 @@
       <c r="F65" s="22"/>
       <c r="G65" s="22"/>
       <c r="H65" s="66" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" s="16" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B66" s="18"/>
       <c r="C66" s="18"/>
       <c r="D66" s="41" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E66" s="18"/>
       <c r="F66" s="18"/>
@@ -7527,7 +7530,7 @@
       <c r="B67" s="22"/>
       <c r="C67" s="22"/>
       <c r="D67" s="42" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E67" s="22"/>
       <c r="F67" s="22"/>
@@ -7536,7 +7539,7 @@
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" s="16" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B68" s="18"/>
       <c r="C68" s="18"/>
@@ -7545,7 +7548,7 @@
       <c r="F68" s="18"/>
       <c r="G68" s="18"/>
       <c r="H68" s="65" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="69" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -7557,12 +7560,12 @@
       <c r="F69" s="22"/>
       <c r="G69" s="22"/>
       <c r="H69" s="66" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" s="32" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B70" s="1"/>
       <c r="C70" s="1" t="s">
@@ -7584,16 +7587,16 @@
       <c r="A71" s="24"/>
       <c r="B71" s="1"/>
       <c r="C71" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E71" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="D71" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="E71" s="1" t="s">
-        <v>98</v>
-      </c>
       <c r="F71" s="58" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="G71" s="1"/>
       <c r="H71" s="25"/>
@@ -7615,7 +7618,7 @@
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
       <c r="D73" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E73" s="1"/>
       <c r="F73" s="1"/>
@@ -7639,7 +7642,7 @@
       <c r="B75" s="22"/>
       <c r="C75" s="22"/>
       <c r="D75" s="42" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E75" s="22"/>
       <c r="F75" s="22"/>
@@ -7648,7 +7651,7 @@
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" s="16" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B76" s="18"/>
       <c r="C76" s="18"/>
@@ -7656,10 +7659,10 @@
       <c r="E76" s="18"/>
       <c r="F76" s="18"/>
       <c r="G76" s="51" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="H76" s="65" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
@@ -7670,10 +7673,10 @@
       <c r="E77" s="1"/>
       <c r="F77" s="1"/>
       <c r="G77" s="52" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H77" s="68" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
@@ -7684,10 +7687,10 @@
       <c r="E78" s="1"/>
       <c r="F78" s="1"/>
       <c r="G78" s="45" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H78" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
@@ -7698,10 +7701,10 @@
       <c r="E79" s="1"/>
       <c r="F79" s="1"/>
       <c r="G79" s="46" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H79" s="68" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
@@ -7713,7 +7716,7 @@
       <c r="F80" s="1"/>
       <c r="G80" s="46"/>
       <c r="H80" s="67" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
@@ -7725,7 +7728,7 @@
       <c r="F81" s="1"/>
       <c r="G81" s="46"/>
       <c r="H81" s="68" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
@@ -7749,12 +7752,12 @@
       <c r="F83" s="22"/>
       <c r="G83" s="47"/>
       <c r="H83" s="23" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="84" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="26" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B84" s="27"/>
       <c r="C84" s="28"/>
@@ -7766,7 +7769,7 @@
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" s="16" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B85" s="18"/>
       <c r="C85" s="18"/>
@@ -7816,7 +7819,7 @@
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" s="16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B89" s="18"/>
       <c r="C89" s="18"/>
@@ -7824,7 +7827,7 @@
       <c r="E89" s="18"/>
       <c r="F89" s="18"/>
       <c r="G89" s="51" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="H89" s="19"/>
     </row>
@@ -7860,13 +7863,13 @@
       <c r="E92" s="22"/>
       <c r="F92" s="22"/>
       <c r="G92" s="22" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H92" s="23"/>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" s="16" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B93" s="18"/>
       <c r="C93" s="18"/>
@@ -7883,7 +7886,7 @@
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
       <c r="D94" s="55" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E94" s="1"/>
       <c r="F94" s="1"/>
@@ -7907,7 +7910,7 @@
       <c r="B96" s="22"/>
       <c r="C96" s="22"/>
       <c r="D96" s="22" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E96" s="22"/>
       <c r="F96" s="22"/>
@@ -7916,7 +7919,7 @@
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" s="16" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B97" s="18"/>
       <c r="C97" s="18"/>
@@ -7924,10 +7927,10 @@
       <c r="E97" s="18"/>
       <c r="F97" s="18"/>
       <c r="G97" s="54" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="H97" s="65" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
@@ -7938,10 +7941,10 @@
       <c r="E98" s="1"/>
       <c r="F98" s="1"/>
       <c r="G98" s="55" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H98" s="68" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
@@ -7964,7 +7967,7 @@
       <c r="E100" s="1"/>
       <c r="F100" s="1"/>
       <c r="G100" s="55" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H100" s="68"/>
     </row>
@@ -7976,7 +7979,7 @@
       <c r="E101" s="1"/>
       <c r="F101" s="1"/>
       <c r="G101" s="69" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="H101" s="68"/>
     </row>
@@ -7988,7 +7991,7 @@
       <c r="E102" s="22"/>
       <c r="F102" s="22"/>
       <c r="G102" s="53" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H102" s="66"/>
     </row>
@@ -8052,7 +8055,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B4" s="13" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C4" s="13"/>
       <c r="D4" s="13"/>
@@ -8060,7 +8063,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B5" s="14" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C5" s="14"/>
       <c r="D5" s="14"/>
@@ -8071,16 +8074,16 @@
         <v>3</v>
       </c>
       <c r="B6" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="D6" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="E6" s="6" t="s">
         <v>120</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -8221,7 +8224,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B15" s="7">
         <v>0</v>
@@ -8238,7 +8241,7 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B16" s="7">
         <v>0</v>
@@ -8255,7 +8258,7 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B17" s="7">
         <v>0</v>
@@ -8272,7 +8275,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B18" s="7">
         <v>0</v>
@@ -8289,7 +8292,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B19" s="7">
         <v>0</v>
@@ -8306,7 +8309,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B20" s="7">
         <v>0</v>
@@ -8323,7 +8326,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B21" s="7">
         <v>0</v>
@@ -8340,7 +8343,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B22" s="7">
         <v>0</v>
@@ -8357,7 +8360,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B23" s="7">
         <v>0</v>
@@ -8374,7 +8377,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B24" s="7">
         <v>0</v>
@@ -8391,7 +8394,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B25" s="7">
         <v>0</v>
@@ -8408,7 +8411,7 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B26" s="7">
         <v>0</v>
@@ -8425,7 +8428,7 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B27" s="7">
         <v>0</v>
@@ -8442,7 +8445,7 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B28" s="7">
         <v>0</v>
@@ -8459,7 +8462,7 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B29" s="7">
         <v>0</v>
@@ -8476,7 +8479,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B30" s="7">
         <v>0</v>
@@ -8493,7 +8496,7 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B31" s="7">
         <v>0</v>
@@ -8510,7 +8513,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B32" s="7">
         <v>0</v>
@@ -8527,7 +8530,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B33" s="7">
         <v>0</v>
@@ -8577,40 +8580,40 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B5" s="11"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
   </sheetData>
@@ -8785,13 +8788,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{574719B2-3B79-4885-B0A8-0EB64E8DF50B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{75BDC7DA-B4D0-4CE7-A2D3-CAED3C639318}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{51C725EF-523F-4D29-B493-0791DCF71EAA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EF543838-1174-491A-80C6-4482E4FC1CCD}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D867BE1-3343-4D33-8ADE-E24AA35C0BC6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F6E19956-CE29-4840-BA4C-9F52FEF8F9B4}"/>
 </file>
--- a/Plannings 2026 S26.xlsx
+++ b/Plannings 2026 S26.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="18" documentId="8_{A23AA2D1-9819-4B65-9C3A-D83FC30F8B22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B1710F38-0AC6-4914-B675-5AB1093980AC}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{A23AA2D1-9819-4B65-9C3A-D83FC30F8B22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BE77D127-EEBA-4B11-B64D-E4268FA37DEA}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="151">
   <si>
     <t>Planning des salariés du 22/06/2026 au 28/06/2026</t>
   </si>
@@ -171,6 +171,9 @@
     <t>17:15/19:15</t>
   </si>
   <si>
+    <t>14:15/16:45</t>
+  </si>
+  <si>
     <t>17:45/24:00</t>
   </si>
   <si>
@@ -180,6 +183,9 @@
     <t>19:15/21:15</t>
   </si>
   <si>
+    <t>16:45/18:30</t>
+  </si>
+  <si>
     <t>21:15/22:00</t>
   </si>
   <si>
@@ -204,6 +210,9 @@
     <t>13:45/15:45</t>
   </si>
   <si>
+    <t>17:00/18:00</t>
+  </si>
+  <si>
     <t>08:50/10:00</t>
   </si>
   <si>
@@ -234,6 +243,9 @@
     <t>DOVINA Théo</t>
   </si>
   <si>
+    <t>20:00/24:00</t>
+  </si>
+  <si>
     <t>FREIXEDAS-BERENGUER Maxime</t>
   </si>
   <si>
@@ -315,6 +327,9 @@
     <t>09:50/18:00</t>
   </si>
   <si>
+    <t>13:15/23:00</t>
+  </si>
+  <si>
     <t>18:00/19:50</t>
   </si>
   <si>
@@ -420,6 +435,9 @@
     <t>FORP VDC</t>
   </si>
   <si>
+    <t>09:45/13:15</t>
+  </si>
+  <si>
     <t>11:45/17:00</t>
   </si>
   <si>
@@ -457,30 +475,6 @@
   </si>
   <si>
     <t>10:15/17:00</t>
-  </si>
-  <si>
-    <t>11:45/16:30</t>
-  </si>
-  <si>
-    <t>09:45/13:00</t>
-  </si>
-  <si>
-    <t>16:00/19:00</t>
-  </si>
-  <si>
-    <t>16:30/18:00</t>
-  </si>
-  <si>
-    <t>18:30/24:00</t>
-  </si>
-  <si>
-    <t>13:00/23:00</t>
-  </si>
-  <si>
-    <t>17:15/18:30</t>
-  </si>
-  <si>
-    <t>14:15/17:15</t>
   </si>
 </sst>
 </file>
@@ -994,7 +988,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1030,6 +1024,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1170,6 +1167,18 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1209,33 +1218,6 @@
     <xf numFmtId="0" fontId="16" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5608,534 +5590,6 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="3657600" y="4391025"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="110" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5E11E667-BCB5-4EB1-B679-508B36CE3BB1}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="609600" y="2295525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="111" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1F346B36-B49F-4C01-89C5-D785CB6802C5}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="609600" y="2676525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="112" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3D3A596E-3F14-4212-8CA9-41F8D2D79956}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1219200" y="2295525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="113" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9B0376B6-6366-408A-868E-C3E5B29CD7A2}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1828800" y="2295525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="114" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{257B316F-EE6B-4EF7-8F2B-89C2D483A2FF}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1828800" y="2676525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="115" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BFABF675-D5EE-496F-AFBA-1BBA689333F2}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1828800" y="3057525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="116" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{68A3E215-42C0-4FDA-BDF1-CFE864063B92}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2438400" y="2295525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="117" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{58FC21F7-F7BE-49C4-882A-2D9AF8FE52D4}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2438400" y="2676525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="118" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D8C9CF28-6387-4A30-BE59-F70C9EE8DC20}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2438400" y="3057525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="119" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8FB689B7-1847-4C5B-BC62-6E7A4F0E994B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3048000" y="2295525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="120" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1AD1DE96-4C49-40A8-BEB7-1693E16AFBC2}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3048000" y="5915025"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="121" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FDD7FE20-7B57-417D-A345-88667E1FD488}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3048000" y="6296025"/>
           <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -6546,311 +6000,307 @@
       <c r="H2" s="12"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B3" s="60" t="s">
-        <v>135</v>
-      </c>
-      <c r="C3" s="61"/>
-      <c r="D3" s="61"/>
-      <c r="E3" s="61"/>
-      <c r="F3" s="61"/>
-      <c r="G3" s="61"/>
-      <c r="H3" s="62"/>
-    </row>
-    <row r="4" spans="1:8" s="63" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="B4" s="64" t="s">
-        <v>136</v>
-      </c>
-      <c r="C4" s="64" t="s">
+      <c r="B3" s="65" t="s">
+        <v>141</v>
+      </c>
+      <c r="C3" s="66"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="66"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="66"/>
+      <c r="H3" s="67"/>
+    </row>
+    <row r="4" spans="1:8" s="68" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="B4" s="69" t="s">
+        <v>142</v>
+      </c>
+      <c r="C4" s="69" t="s">
+        <v>143</v>
+      </c>
+      <c r="D4" s="69" t="s">
+        <v>144</v>
+      </c>
+      <c r="E4" s="69" t="s">
+        <v>145</v>
+      </c>
+      <c r="F4" s="69" t="s">
+        <v>146</v>
+      </c>
+      <c r="G4" s="69" t="s">
+        <v>147</v>
+      </c>
+      <c r="H4" s="69" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="F5" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="G5" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="H5" s="16" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="18"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="55" t="s">
+        <v>12</v>
+      </c>
+      <c r="H6" s="20"/>
+    </row>
+    <row r="7" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="21"/>
+      <c r="B7" s="22"/>
+      <c r="C7" s="23"/>
+      <c r="D7" s="23"/>
+      <c r="E7" s="23"/>
+      <c r="F7" s="23"/>
+      <c r="G7" s="58" t="s">
+        <v>13</v>
+      </c>
+      <c r="H7" s="24"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="19"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="42" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" s="19"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="19"/>
+      <c r="H8" s="20"/>
+    </row>
+    <row r="9" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="21"/>
+      <c r="B9" s="23"/>
+      <c r="C9" s="23"/>
+      <c r="D9" s="43" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" s="23"/>
+      <c r="F9" s="23"/>
+      <c r="G9" s="23"/>
+      <c r="H9" s="24"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" s="63" t="s">
+        <v>19</v>
+      </c>
+      <c r="E10" s="42" t="s">
+        <v>20</v>
+      </c>
+      <c r="F10" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="G10" s="19"/>
+      <c r="H10" s="20"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="25"/>
+      <c r="B11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" s="61" t="s">
+        <v>23</v>
+      </c>
+      <c r="E11" s="44" t="s">
+        <v>24</v>
+      </c>
+      <c r="F11" s="59" t="s">
         <v>137</v>
       </c>
-      <c r="D4" s="64" t="s">
+      <c r="G11" s="1"/>
+      <c r="H11" s="26"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="25"/>
+      <c r="B12" s="60" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="1"/>
+      <c r="D12" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="26"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="25"/>
+      <c r="B13" s="61" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="26"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="25"/>
+      <c r="B14" s="61"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="45" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="26"/>
+    </row>
+    <row r="15" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="21"/>
+      <c r="B15" s="62"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="43" t="s">
+        <v>29</v>
+      </c>
+      <c r="E15" s="23"/>
+      <c r="F15" s="23"/>
+      <c r="G15" s="23"/>
+      <c r="H15" s="24"/>
+    </row>
+    <row r="16" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="27" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="28"/>
+      <c r="C16" s="29"/>
+      <c r="D16" s="29"/>
+      <c r="E16" s="29"/>
+      <c r="F16" s="29"/>
+      <c r="G16" s="29"/>
+      <c r="H16" s="30"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" s="51" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="51" t="s">
+        <v>18</v>
+      </c>
+      <c r="D17" s="51" t="s">
+        <v>18</v>
+      </c>
+      <c r="E17" s="59"/>
+      <c r="F17" s="51" t="s">
+        <v>18</v>
+      </c>
+      <c r="G17" s="51" t="s">
+        <v>18</v>
+      </c>
+      <c r="H17" s="59"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="13"/>
+      <c r="B18" s="59" t="s">
         <v>138</v>
       </c>
-      <c r="E4" s="64" t="s">
-        <v>139</v>
-      </c>
-      <c r="F4" s="64" t="s">
-        <v>140</v>
-      </c>
-      <c r="G4" s="64" t="s">
-        <v>141</v>
-      </c>
-      <c r="H4" s="64" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="D5" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E5" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="F5" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="G5" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="H5" s="15" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="17"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="18"/>
-      <c r="G6" s="54" t="s">
-        <v>12</v>
-      </c>
-      <c r="H6" s="19"/>
-    </row>
-    <row r="7" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="20"/>
-      <c r="B7" s="21"/>
-      <c r="C7" s="22"/>
-      <c r="D7" s="22"/>
-      <c r="E7" s="22"/>
-      <c r="F7" s="22"/>
-      <c r="G7" s="57" t="s">
-        <v>13</v>
-      </c>
-      <c r="H7" s="23"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="18"/>
-      <c r="C8" s="18"/>
-      <c r="D8" s="41" t="s">
-        <v>15</v>
-      </c>
-      <c r="E8" s="18"/>
-      <c r="F8" s="18"/>
-      <c r="G8" s="18"/>
-      <c r="H8" s="19"/>
-    </row>
-    <row r="9" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="20"/>
-      <c r="B9" s="22"/>
-      <c r="C9" s="22"/>
-      <c r="D9" s="42" t="s">
-        <v>16</v>
-      </c>
-      <c r="E9" s="22"/>
-      <c r="F9" s="22"/>
-      <c r="G9" s="22"/>
-      <c r="H9" s="23"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" s="49" t="s">
+      <c r="C18" s="59" t="s">
+        <v>148</v>
+      </c>
+      <c r="D18" s="59" t="s">
+        <v>33</v>
+      </c>
+      <c r="E18" s="59"/>
+      <c r="F18" s="59" t="s">
+        <v>149</v>
+      </c>
+      <c r="G18" s="59" t="s">
+        <v>150</v>
+      </c>
+      <c r="H18" s="59"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="13"/>
+      <c r="B19" s="59"/>
+      <c r="C19" s="59"/>
+      <c r="D19" s="75" t="s">
+        <v>34</v>
+      </c>
+      <c r="E19" s="59"/>
+      <c r="F19" s="59"/>
+      <c r="G19" s="59"/>
+      <c r="H19" s="59"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="13"/>
+      <c r="B20" s="59"/>
+      <c r="C20" s="59"/>
+      <c r="D20" s="76" t="s">
+        <v>35</v>
+      </c>
+      <c r="E20" s="59"/>
+      <c r="F20" s="59"/>
+      <c r="G20" s="59"/>
+      <c r="H20" s="59"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="13"/>
+      <c r="B21" s="59"/>
+      <c r="C21" s="59"/>
+      <c r="D21" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="49" t="s">
-        <v>18</v>
-      </c>
-      <c r="D10" s="75" t="s">
-        <v>19</v>
-      </c>
-      <c r="E10" s="49" t="s">
-        <v>18</v>
-      </c>
-      <c r="F10" s="49" t="s">
-        <v>18</v>
-      </c>
-      <c r="G10" s="49"/>
-      <c r="H10" s="76"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="24"/>
-      <c r="B11" s="58" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" s="58" t="s">
-        <v>22</v>
-      </c>
-      <c r="D11" s="71" t="s">
-        <v>23</v>
-      </c>
-      <c r="E11" s="58" t="s">
-        <v>145</v>
-      </c>
-      <c r="F11" s="58" t="s">
-        <v>146</v>
-      </c>
-      <c r="G11" s="58"/>
-      <c r="H11" s="77"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="24"/>
-      <c r="B12" s="70" t="s">
-        <v>19</v>
-      </c>
-      <c r="C12" s="58"/>
-      <c r="D12" s="50" t="s">
-        <v>18</v>
-      </c>
-      <c r="E12" s="72" t="s">
-        <v>20</v>
-      </c>
-      <c r="F12" s="58"/>
-      <c r="G12" s="58"/>
-      <c r="H12" s="77"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="24"/>
-      <c r="B13" s="71" t="s">
-        <v>26</v>
-      </c>
-      <c r="C13" s="58"/>
-      <c r="D13" s="58" t="s">
-        <v>27</v>
-      </c>
-      <c r="E13" s="73" t="s">
-        <v>24</v>
-      </c>
-      <c r="F13" s="58"/>
-      <c r="G13" s="58"/>
-      <c r="H13" s="77"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="24"/>
-      <c r="B14" s="71"/>
-      <c r="C14" s="58"/>
-      <c r="D14" s="72" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="50" t="s">
-        <v>18</v>
-      </c>
-      <c r="F14" s="58"/>
-      <c r="G14" s="58"/>
-      <c r="H14" s="77"/>
-    </row>
-    <row r="15" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="20"/>
-      <c r="B15" s="78"/>
-      <c r="C15" s="59"/>
-      <c r="D15" s="74" t="s">
-        <v>29</v>
-      </c>
-      <c r="E15" s="59" t="s">
-        <v>28</v>
-      </c>
-      <c r="F15" s="59"/>
-      <c r="G15" s="59"/>
-      <c r="H15" s="79"/>
-    </row>
-    <row r="16" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="B16" s="27"/>
-      <c r="C16" s="28"/>
-      <c r="D16" s="28"/>
-      <c r="E16" s="28"/>
-      <c r="F16" s="28"/>
-      <c r="G16" s="28"/>
-      <c r="H16" s="29"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="B17" s="49" t="s">
-        <v>18</v>
-      </c>
-      <c r="C17" s="49" t="s">
-        <v>18</v>
-      </c>
-      <c r="D17" s="49" t="s">
-        <v>18</v>
-      </c>
-      <c r="E17" s="49"/>
-      <c r="F17" s="49" t="s">
-        <v>18</v>
-      </c>
-      <c r="G17" s="49" t="s">
-        <v>18</v>
-      </c>
-      <c r="H17" s="76"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="24"/>
-      <c r="B18" s="58" t="s">
-        <v>132</v>
-      </c>
-      <c r="C18" s="58" t="s">
-        <v>142</v>
-      </c>
-      <c r="D18" s="58" t="s">
-        <v>33</v>
-      </c>
-      <c r="E18" s="58"/>
-      <c r="F18" s="58" t="s">
-        <v>143</v>
-      </c>
-      <c r="G18" s="58" t="s">
-        <v>144</v>
-      </c>
-      <c r="H18" s="77"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="24"/>
-      <c r="B19" s="58"/>
-      <c r="C19" s="58"/>
-      <c r="D19" s="70" t="s">
-        <v>34</v>
-      </c>
-      <c r="E19" s="58"/>
-      <c r="F19" s="58"/>
-      <c r="G19" s="58"/>
-      <c r="H19" s="77"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="24"/>
-      <c r="B20" s="58"/>
-      <c r="C20" s="58"/>
-      <c r="D20" s="71" t="s">
-        <v>35</v>
-      </c>
-      <c r="E20" s="58"/>
-      <c r="F20" s="58"/>
-      <c r="G20" s="58"/>
-      <c r="H20" s="77"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="24"/>
-      <c r="B21" s="58"/>
-      <c r="C21" s="58"/>
-      <c r="D21" s="50" t="s">
-        <v>18</v>
-      </c>
-      <c r="E21" s="58"/>
-      <c r="F21" s="58"/>
-      <c r="G21" s="58"/>
-      <c r="H21" s="77"/>
+      <c r="E21" s="59"/>
+      <c r="F21" s="59"/>
+      <c r="G21" s="59"/>
+      <c r="H21" s="59"/>
     </row>
     <row r="22" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="20"/>
+      <c r="A22" s="13"/>
       <c r="B22" s="59"/>
       <c r="C22" s="59"/>
       <c r="D22" s="59" t="s">
@@ -6859,325 +6309,321 @@
       <c r="E22" s="59"/>
       <c r="F22" s="59"/>
       <c r="G22" s="59"/>
-      <c r="H22" s="79"/>
+      <c r="H22" s="59"/>
     </row>
     <row r="23" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="37" t="s">
+      <c r="A23" s="38" t="s">
         <v>37</v>
       </c>
-      <c r="B23" s="38"/>
-      <c r="C23" s="39"/>
-      <c r="D23" s="39"/>
-      <c r="E23" s="39"/>
-      <c r="F23" s="39"/>
-      <c r="G23" s="39"/>
-      <c r="H23" s="40"/>
+      <c r="B23" s="39"/>
+      <c r="C23" s="40"/>
+      <c r="D23" s="40"/>
+      <c r="E23" s="40"/>
+      <c r="F23" s="40"/>
+      <c r="G23" s="40"/>
+      <c r="H23" s="41"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="16" t="s">
+      <c r="A24" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="B24" s="54" t="s">
+      <c r="B24" s="55" t="s">
         <v>39</v>
       </c>
-      <c r="C24" s="54" t="s">
+      <c r="C24" s="55" t="s">
         <v>39</v>
       </c>
-      <c r="D24" s="54" t="s">
+      <c r="D24" s="55" t="s">
         <v>39</v>
       </c>
-      <c r="E24" s="54" t="s">
+      <c r="E24" s="55" t="s">
         <v>39</v>
       </c>
-      <c r="F24" s="49" t="s">
-        <v>18</v>
-      </c>
-      <c r="G24" s="18"/>
-      <c r="H24" s="19"/>
+      <c r="F24" s="42" t="s">
+        <v>40</v>
+      </c>
+      <c r="G24" s="19"/>
+      <c r="H24" s="20"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="24"/>
-      <c r="B25" s="55" t="s">
+      <c r="A25" s="25"/>
+      <c r="B25" s="56" t="s">
         <v>41</v>
       </c>
-      <c r="C25" s="55" t="s">
+      <c r="C25" s="56" t="s">
         <v>41</v>
       </c>
-      <c r="D25" s="55" t="s">
+      <c r="D25" s="56" t="s">
         <v>42</v>
       </c>
-      <c r="E25" s="55" t="s">
+      <c r="E25" s="56" t="s">
         <v>43</v>
       </c>
-      <c r="F25" s="58" t="s">
-        <v>147</v>
+      <c r="F25" s="44" t="s">
+        <v>44</v>
       </c>
       <c r="G25" s="1"/>
-      <c r="H25" s="25"/>
+      <c r="H25" s="26"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="24"/>
+      <c r="A26" s="25"/>
       <c r="B26" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="D26" s="56" t="s">
+      <c r="D26" s="57" t="s">
         <v>39</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F26" s="72" t="s">
-        <v>40</v>
-      </c>
+      <c r="F26" s="44"/>
       <c r="G26" s="1"/>
-      <c r="H26" s="25"/>
+      <c r="H26" s="26"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="24"/>
+      <c r="A27" s="25"/>
       <c r="B27" s="1" t="s">
         <v>47</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="D27" s="80" t="s">
-        <v>152</v>
+      <c r="D27" s="56" t="s">
+        <v>49</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="F27" s="73" t="s">
-        <v>44</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="F27" s="44"/>
       <c r="G27" s="1"/>
-      <c r="H27" s="25"/>
+      <c r="H27" s="26"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="24"/>
-      <c r="B28" s="56" t="s">
+      <c r="A28" s="25"/>
+      <c r="B28" s="57" t="s">
         <v>39</v>
       </c>
-      <c r="C28" s="56" t="s">
+      <c r="C28" s="57" t="s">
         <v>39</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>46</v>
       </c>
       <c r="E28" s="1"/>
-      <c r="F28" s="73"/>
+      <c r="F28" s="44"/>
       <c r="G28" s="1"/>
-      <c r="H28" s="25"/>
+      <c r="H28" s="26"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="24"/>
-      <c r="B29" s="55" t="s">
-        <v>50</v>
-      </c>
-      <c r="C29" s="55" t="s">
+      <c r="A29" s="25"/>
+      <c r="B29" s="56" t="s">
         <v>51</v>
       </c>
-      <c r="D29" s="58" t="s">
-        <v>151</v>
+      <c r="C29" s="56" t="s">
+        <v>52</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>53</v>
       </c>
       <c r="E29" s="1"/>
-      <c r="F29" s="73"/>
+      <c r="F29" s="44"/>
       <c r="G29" s="1"/>
-      <c r="H29" s="25"/>
+      <c r="H29" s="26"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="24"/>
-      <c r="B30" s="55"/>
+      <c r="A30" s="25"/>
+      <c r="B30" s="56"/>
       <c r="C30" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D30" s="56" t="s">
+      <c r="D30" s="57" t="s">
         <v>39</v>
       </c>
       <c r="E30" s="1"/>
-      <c r="F30" s="73"/>
+      <c r="F30" s="44"/>
       <c r="G30" s="1"/>
-      <c r="H30" s="25"/>
+      <c r="H30" s="26"/>
     </row>
     <row r="31" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="20"/>
-      <c r="B31" s="57"/>
-      <c r="C31" s="22" t="s">
-        <v>52</v>
-      </c>
-      <c r="D31" s="57" t="s">
-        <v>53</v>
-      </c>
-      <c r="E31" s="22"/>
-      <c r="F31" s="74"/>
-      <c r="G31" s="22"/>
-      <c r="H31" s="23"/>
+      <c r="A31" s="21"/>
+      <c r="B31" s="58"/>
+      <c r="C31" s="23" t="s">
+        <v>54</v>
+      </c>
+      <c r="D31" s="58" t="s">
+        <v>55</v>
+      </c>
+      <c r="E31" s="23"/>
+      <c r="F31" s="43"/>
+      <c r="G31" s="23"/>
+      <c r="H31" s="24"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="B32" s="18"/>
-      <c r="C32" s="18"/>
-      <c r="D32" s="18"/>
-      <c r="E32" s="18"/>
-      <c r="F32" s="18"/>
-      <c r="G32" s="54" t="s">
+      <c r="A32" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="B32" s="19"/>
+      <c r="C32" s="19"/>
+      <c r="D32" s="19"/>
+      <c r="E32" s="19"/>
+      <c r="F32" s="19"/>
+      <c r="G32" s="55" t="s">
         <v>12</v>
       </c>
-      <c r="H32" s="19"/>
+      <c r="H32" s="20"/>
     </row>
     <row r="33" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="20"/>
-      <c r="B33" s="22"/>
-      <c r="C33" s="22"/>
-      <c r="D33" s="22"/>
-      <c r="E33" s="22"/>
-      <c r="F33" s="22"/>
-      <c r="G33" s="57" t="s">
+      <c r="A33" s="21"/>
+      <c r="B33" s="23"/>
+      <c r="C33" s="23"/>
+      <c r="D33" s="23"/>
+      <c r="E33" s="23"/>
+      <c r="F33" s="23"/>
+      <c r="G33" s="58" t="s">
         <v>13</v>
       </c>
-      <c r="H33" s="23"/>
+      <c r="H33" s="24"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="B34" s="18" t="s">
+      <c r="A34" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="B34" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="C34" s="48" t="s">
-        <v>56</v>
-      </c>
-      <c r="D34" s="54" t="s">
-        <v>57</v>
-      </c>
-      <c r="E34" s="18" t="s">
+      <c r="C34" s="49" t="s">
+        <v>58</v>
+      </c>
+      <c r="D34" s="55" t="s">
+        <v>59</v>
+      </c>
+      <c r="E34" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="F34" s="18"/>
-      <c r="G34" s="18" t="s">
+      <c r="F34" s="19"/>
+      <c r="G34" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="H34" s="19" t="s">
+      <c r="H34" s="20" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" s="24"/>
-      <c r="B35" s="58" t="s">
-        <v>133</v>
-      </c>
-      <c r="C35" s="46" t="s">
-        <v>58</v>
-      </c>
-      <c r="D35" s="55" t="s">
-        <v>59</v>
-      </c>
-      <c r="E35" s="58" t="s">
-        <v>148</v>
+      <c r="A35" s="25"/>
+      <c r="B35" s="59" t="s">
+        <v>139</v>
+      </c>
+      <c r="C35" s="47" t="s">
+        <v>60</v>
+      </c>
+      <c r="D35" s="56" t="s">
+        <v>61</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>62</v>
       </c>
       <c r="F35" s="1"/>
       <c r="G35" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="H35" s="25" t="s">
-        <v>61</v>
+        <v>63</v>
+      </c>
+      <c r="H35" s="26" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="24"/>
+      <c r="A36" s="25"/>
       <c r="B36" s="1"/>
-      <c r="C36" s="46"/>
+      <c r="C36" s="47"/>
       <c r="D36" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E36" s="44" t="s">
+      <c r="E36" s="45" t="s">
         <v>15</v>
       </c>
       <c r="F36" s="1"/>
-      <c r="G36" s="44" t="s">
+      <c r="G36" s="45" t="s">
         <v>15</v>
       </c>
-      <c r="H36" s="25"/>
+      <c r="H36" s="26"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37" s="24"/>
+      <c r="A37" s="25"/>
       <c r="B37" s="1"/>
-      <c r="C37" s="46"/>
+      <c r="C37" s="47"/>
       <c r="D37" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="E37" s="43" t="s">
+        <v>65</v>
+      </c>
+      <c r="E37" s="44" t="s">
         <v>36</v>
       </c>
       <c r="F37" s="1"/>
-      <c r="G37" s="43" t="s">
-        <v>63</v>
-      </c>
-      <c r="H37" s="25"/>
+      <c r="G37" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="H37" s="26"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="24"/>
+      <c r="A38" s="25"/>
       <c r="B38" s="1"/>
-      <c r="C38" s="46"/>
-      <c r="D38" s="56" t="s">
-        <v>57</v>
-      </c>
-      <c r="E38" s="43"/>
+      <c r="C38" s="47"/>
+      <c r="D38" s="57" t="s">
+        <v>59</v>
+      </c>
+      <c r="E38" s="44"/>
       <c r="F38" s="1"/>
       <c r="G38" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="H38" s="25"/>
+      <c r="H38" s="26"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="24"/>
+      <c r="A39" s="25"/>
       <c r="B39" s="1"/>
-      <c r="C39" s="46"/>
-      <c r="D39" s="55" t="s">
-        <v>64</v>
-      </c>
-      <c r="E39" s="43"/>
+      <c r="C39" s="47"/>
+      <c r="D39" s="56" t="s">
+        <v>67</v>
+      </c>
+      <c r="E39" s="44"/>
       <c r="F39" s="1"/>
       <c r="G39" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="H39" s="25"/>
+      <c r="H39" s="26"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="24"/>
+      <c r="A40" s="25"/>
       <c r="B40" s="1"/>
-      <c r="C40" s="46"/>
-      <c r="D40" s="44" t="s">
-        <v>65</v>
-      </c>
-      <c r="E40" s="43"/>
+      <c r="C40" s="47"/>
+      <c r="D40" s="45" t="s">
+        <v>68</v>
+      </c>
+      <c r="E40" s="44"/>
       <c r="F40" s="1"/>
-      <c r="G40" s="45" t="s">
-        <v>66</v>
-      </c>
-      <c r="H40" s="25"/>
+      <c r="G40" s="46" t="s">
+        <v>69</v>
+      </c>
+      <c r="H40" s="26"/>
     </row>
     <row r="41" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="20"/>
-      <c r="B41" s="22"/>
-      <c r="C41" s="47"/>
-      <c r="D41" s="42" t="s">
-        <v>67</v>
-      </c>
-      <c r="E41" s="42"/>
-      <c r="F41" s="22"/>
-      <c r="G41" s="47" t="s">
-        <v>68</v>
-      </c>
-      <c r="H41" s="23"/>
+      <c r="A41" s="21"/>
+      <c r="B41" s="23"/>
+      <c r="C41" s="48"/>
+      <c r="D41" s="43" t="s">
+        <v>70</v>
+      </c>
+      <c r="E41" s="43"/>
+      <c r="F41" s="23"/>
+      <c r="G41" s="48" t="s">
+        <v>71</v>
+      </c>
+      <c r="H41" s="24"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" s="32" t="s">
-        <v>69</v>
+      <c r="A42" s="33" t="s">
+        <v>72</v>
       </c>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
@@ -7187,232 +6633,232 @@
       </c>
       <c r="F42" s="1"/>
       <c r="G42" s="1"/>
-      <c r="H42" s="25"/>
+      <c r="H42" s="26"/>
     </row>
     <row r="43" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="20"/>
-      <c r="B43" s="22"/>
-      <c r="C43" s="22"/>
-      <c r="D43" s="22"/>
-      <c r="E43" s="59" t="s">
-        <v>149</v>
-      </c>
-      <c r="F43" s="22"/>
-      <c r="G43" s="22"/>
-      <c r="H43" s="23"/>
+      <c r="A43" s="21"/>
+      <c r="B43" s="23"/>
+      <c r="C43" s="23"/>
+      <c r="D43" s="23"/>
+      <c r="E43" s="23" t="s">
+        <v>73</v>
+      </c>
+      <c r="F43" s="23"/>
+      <c r="G43" s="23"/>
+      <c r="H43" s="24"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="16" t="s">
-        <v>129</v>
-      </c>
-      <c r="B44" s="49" t="s">
-        <v>130</v>
-      </c>
-      <c r="C44" s="18"/>
-      <c r="D44" s="18" t="s">
+      <c r="A44" s="17" t="s">
+        <v>134</v>
+      </c>
+      <c r="B44" s="50" t="s">
+        <v>135</v>
+      </c>
+      <c r="C44" s="19"/>
+      <c r="D44" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="E44" s="18"/>
-      <c r="F44" s="18"/>
-      <c r="G44" s="51" t="s">
-        <v>71</v>
-      </c>
-      <c r="H44" s="19"/>
+      <c r="E44" s="19"/>
+      <c r="F44" s="19"/>
+      <c r="G44" s="52" t="s">
+        <v>75</v>
+      </c>
+      <c r="H44" s="20"/>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" s="24"/>
+      <c r="A45" s="25"/>
       <c r="B45" s="1" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C45" s="1"/>
       <c r="D45" s="1" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E45" s="1"/>
       <c r="F45" s="1"/>
-      <c r="G45" s="52" t="s">
-        <v>74</v>
-      </c>
-      <c r="H45" s="25"/>
+      <c r="G45" s="53" t="s">
+        <v>78</v>
+      </c>
+      <c r="H45" s="26"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="24"/>
-      <c r="B46" s="50" t="s">
-        <v>131</v>
+      <c r="A46" s="25"/>
+      <c r="B46" s="51" t="s">
+        <v>136</v>
       </c>
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
       <c r="E46" s="1"/>
       <c r="F46" s="1"/>
-      <c r="G46" s="52"/>
-      <c r="H46" s="25"/>
+      <c r="G46" s="53"/>
+      <c r="H46" s="26"/>
     </row>
     <row r="47" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="20"/>
-      <c r="B47" s="22" t="s">
+      <c r="A47" s="21"/>
+      <c r="B47" s="23" t="s">
+        <v>79</v>
+      </c>
+      <c r="C47" s="23"/>
+      <c r="D47" s="23"/>
+      <c r="E47" s="23"/>
+      <c r="F47" s="23"/>
+      <c r="G47" s="54"/>
+      <c r="H47" s="24"/>
+    </row>
+    <row r="48" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="27" t="s">
+        <v>80</v>
+      </c>
+      <c r="B48" s="28"/>
+      <c r="C48" s="29"/>
+      <c r="D48" s="29"/>
+      <c r="E48" s="29"/>
+      <c r="F48" s="29"/>
+      <c r="G48" s="29"/>
+      <c r="H48" s="30"/>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="B49" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C49" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D49" s="19"/>
+      <c r="E49" s="19"/>
+      <c r="F49" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="G49" s="19"/>
+      <c r="H49" s="20" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="21"/>
+      <c r="B50" s="64" t="s">
+        <v>140</v>
+      </c>
+      <c r="C50" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="D50" s="23"/>
+      <c r="E50" s="23"/>
+      <c r="F50" s="23" t="s">
+        <v>82</v>
+      </c>
+      <c r="G50" s="23"/>
+      <c r="H50" s="24" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="B51" s="19"/>
+      <c r="C51" s="19"/>
+      <c r="D51" s="19"/>
+      <c r="E51" s="19"/>
+      <c r="F51" s="19"/>
+      <c r="G51" s="19"/>
+      <c r="H51" s="70" t="s">
         <v>75</v>
       </c>
-      <c r="C47" s="22"/>
-      <c r="D47" s="22"/>
-      <c r="E47" s="22"/>
-      <c r="F47" s="22"/>
-      <c r="G47" s="53"/>
-      <c r="H47" s="23"/>
-    </row>
-    <row r="48" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="26" t="s">
-        <v>76</v>
-      </c>
-      <c r="B48" s="27"/>
-      <c r="C48" s="28"/>
-      <c r="D48" s="28"/>
-      <c r="E48" s="28"/>
-      <c r="F48" s="28"/>
-      <c r="G48" s="28"/>
-      <c r="H48" s="29"/>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="B49" s="18" t="s">
+    </row>
+    <row r="52" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="21"/>
+      <c r="B52" s="23"/>
+      <c r="C52" s="23"/>
+      <c r="D52" s="23"/>
+      <c r="E52" s="23"/>
+      <c r="F52" s="23"/>
+      <c r="G52" s="23"/>
+      <c r="H52" s="71" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="34" t="s">
+        <v>85</v>
+      </c>
+      <c r="B53" s="35"/>
+      <c r="C53" s="36"/>
+      <c r="D53" s="36"/>
+      <c r="E53" s="36"/>
+      <c r="F53" s="36"/>
+      <c r="G53" s="36"/>
+      <c r="H53" s="37"/>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="B54" s="19"/>
+      <c r="C54" s="49" t="s">
+        <v>58</v>
+      </c>
+      <c r="D54" s="42" t="s">
+        <v>68</v>
+      </c>
+      <c r="E54" s="19"/>
+      <c r="F54" s="19"/>
+      <c r="G54" s="49" t="s">
+        <v>58</v>
+      </c>
+      <c r="H54" s="20"/>
+    </row>
+    <row r="55" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="21"/>
+      <c r="B55" s="23"/>
+      <c r="C55" s="48" t="s">
+        <v>60</v>
+      </c>
+      <c r="D55" s="43" t="s">
+        <v>70</v>
+      </c>
+      <c r="E55" s="23"/>
+      <c r="F55" s="23"/>
+      <c r="G55" s="48" t="s">
+        <v>87</v>
+      </c>
+      <c r="H55" s="24"/>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="B56" s="19"/>
+      <c r="C56" s="19"/>
+      <c r="D56" s="19"/>
+      <c r="E56" s="19"/>
+      <c r="F56" s="19"/>
+      <c r="G56" s="52" t="s">
+        <v>75</v>
+      </c>
+      <c r="H56" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="C49" s="18" t="s">
-        <v>18</v>
-      </c>
-      <c r="D49" s="18"/>
-      <c r="E49" s="18"/>
-      <c r="F49" s="18" t="s">
-        <v>18</v>
-      </c>
-      <c r="G49" s="18"/>
-      <c r="H49" s="19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="20"/>
-      <c r="B50" s="59" t="s">
-        <v>134</v>
-      </c>
-      <c r="C50" s="22" t="s">
-        <v>73</v>
-      </c>
-      <c r="D50" s="22"/>
-      <c r="E50" s="22"/>
-      <c r="F50" s="22" t="s">
-        <v>78</v>
-      </c>
-      <c r="G50" s="22"/>
-      <c r="H50" s="23" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A51" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="B51" s="18"/>
-      <c r="C51" s="18"/>
-      <c r="D51" s="18"/>
-      <c r="E51" s="18"/>
-      <c r="F51" s="18"/>
-      <c r="G51" s="18"/>
-      <c r="H51" s="65" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="20"/>
-      <c r="B52" s="22"/>
-      <c r="C52" s="22"/>
-      <c r="D52" s="22"/>
-      <c r="E52" s="22"/>
-      <c r="F52" s="22"/>
-      <c r="G52" s="22"/>
-      <c r="H52" s="66" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="33" t="s">
-        <v>81</v>
-      </c>
-      <c r="B53" s="34"/>
-      <c r="C53" s="35"/>
-      <c r="D53" s="35"/>
-      <c r="E53" s="35"/>
-      <c r="F53" s="35"/>
-      <c r="G53" s="35"/>
-      <c r="H53" s="36"/>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A54" s="16" t="s">
-        <v>82</v>
-      </c>
-      <c r="B54" s="18"/>
-      <c r="C54" s="48" t="s">
-        <v>56</v>
-      </c>
-      <c r="D54" s="41" t="s">
-        <v>65</v>
-      </c>
-      <c r="E54" s="18"/>
-      <c r="F54" s="18"/>
-      <c r="G54" s="48" t="s">
-        <v>56</v>
-      </c>
-      <c r="H54" s="19"/>
-    </row>
-    <row r="55" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="20"/>
-      <c r="B55" s="22"/>
-      <c r="C55" s="47" t="s">
-        <v>58</v>
-      </c>
-      <c r="D55" s="42" t="s">
-        <v>67</v>
-      </c>
-      <c r="E55" s="22"/>
-      <c r="F55" s="22"/>
-      <c r="G55" s="47" t="s">
-        <v>83</v>
-      </c>
-      <c r="H55" s="23"/>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A56" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="B56" s="18"/>
-      <c r="C56" s="18"/>
-      <c r="D56" s="18"/>
-      <c r="E56" s="18"/>
-      <c r="F56" s="18"/>
-      <c r="G56" s="51" t="s">
-        <v>71</v>
-      </c>
-      <c r="H56" s="19" t="s">
-        <v>18</v>
-      </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" s="24"/>
+      <c r="A57" s="25"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
       <c r="D57" s="1"/>
       <c r="E57" s="1"/>
       <c r="F57" s="1"/>
-      <c r="G57" s="52" t="s">
-        <v>85</v>
-      </c>
-      <c r="H57" s="25" t="s">
-        <v>86</v>
+      <c r="G57" s="53" t="s">
+        <v>89</v>
+      </c>
+      <c r="H57" s="26" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A58" s="24"/>
+      <c r="A58" s="25"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
       <c r="D58" s="1"/>
@@ -7421,151 +6867,151 @@
       <c r="G58" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="H58" s="67" t="s">
-        <v>71</v>
+      <c r="H58" s="72" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A59" s="24"/>
+      <c r="A59" s="25"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
       <c r="D59" s="1"/>
       <c r="E59" s="1"/>
       <c r="F59" s="1"/>
       <c r="G59" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="H59" s="68" t="s">
-        <v>88</v>
+        <v>91</v>
+      </c>
+      <c r="H59" s="73" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A60" s="24"/>
+      <c r="A60" s="25"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
       <c r="D60" s="1"/>
       <c r="E60" s="1"/>
       <c r="F60" s="1"/>
       <c r="G60" s="1"/>
-      <c r="H60" s="31" t="s">
+      <c r="H60" s="32" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61" s="24"/>
+      <c r="A61" s="25"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
       <c r="D61" s="1"/>
       <c r="E61" s="1"/>
       <c r="F61" s="1"/>
       <c r="G61" s="1"/>
-      <c r="H61" s="25" t="s">
-        <v>89</v>
+      <c r="H61" s="26" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A62" s="24"/>
+      <c r="A62" s="25"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
       <c r="D62" s="1"/>
       <c r="E62" s="1"/>
       <c r="F62" s="1"/>
       <c r="G62" s="1"/>
-      <c r="H62" s="31" t="s">
+      <c r="H62" s="32" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A63" s="24"/>
+      <c r="A63" s="25"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
       <c r="D63" s="1"/>
       <c r="E63" s="1"/>
       <c r="F63" s="1"/>
       <c r="G63" s="1"/>
-      <c r="H63" s="25" t="s">
-        <v>90</v>
+      <c r="H63" s="26" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A64" s="24"/>
+      <c r="A64" s="25"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
       <c r="D64" s="1"/>
       <c r="E64" s="1"/>
       <c r="F64" s="1"/>
       <c r="G64" s="1"/>
-      <c r="H64" s="67" t="s">
-        <v>71</v>
+      <c r="H64" s="72" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="65" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="20"/>
-      <c r="B65" s="22"/>
-      <c r="C65" s="22"/>
-      <c r="D65" s="22"/>
-      <c r="E65" s="22"/>
-      <c r="F65" s="22"/>
-      <c r="G65" s="22"/>
-      <c r="H65" s="66" t="s">
-        <v>85</v>
+      <c r="A65" s="21"/>
+      <c r="B65" s="23"/>
+      <c r="C65" s="23"/>
+      <c r="D65" s="23"/>
+      <c r="E65" s="23"/>
+      <c r="F65" s="23"/>
+      <c r="G65" s="23"/>
+      <c r="H65" s="71" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A66" s="16" t="s">
-        <v>91</v>
-      </c>
-      <c r="B66" s="18"/>
-      <c r="C66" s="18"/>
-      <c r="D66" s="41" t="s">
-        <v>65</v>
-      </c>
-      <c r="E66" s="18"/>
-      <c r="F66" s="18"/>
-      <c r="G66" s="18"/>
-      <c r="H66" s="19"/>
+      <c r="A66" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="B66" s="19"/>
+      <c r="C66" s="19"/>
+      <c r="D66" s="42" t="s">
+        <v>68</v>
+      </c>
+      <c r="E66" s="19"/>
+      <c r="F66" s="19"/>
+      <c r="G66" s="19"/>
+      <c r="H66" s="20"/>
     </row>
     <row r="67" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="20"/>
-      <c r="B67" s="22"/>
-      <c r="C67" s="22"/>
-      <c r="D67" s="42" t="s">
-        <v>67</v>
-      </c>
-      <c r="E67" s="22"/>
-      <c r="F67" s="22"/>
-      <c r="G67" s="22"/>
-      <c r="H67" s="23"/>
+      <c r="A67" s="21"/>
+      <c r="B67" s="23"/>
+      <c r="C67" s="23"/>
+      <c r="D67" s="43" t="s">
+        <v>70</v>
+      </c>
+      <c r="E67" s="23"/>
+      <c r="F67" s="23"/>
+      <c r="G67" s="23"/>
+      <c r="H67" s="24"/>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A68" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="B68" s="18"/>
-      <c r="C68" s="18"/>
-      <c r="D68" s="18"/>
-      <c r="E68" s="18"/>
-      <c r="F68" s="18"/>
-      <c r="G68" s="18"/>
-      <c r="H68" s="65" t="s">
-        <v>71</v>
+      <c r="A68" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="B68" s="19"/>
+      <c r="C68" s="19"/>
+      <c r="D68" s="19"/>
+      <c r="E68" s="19"/>
+      <c r="F68" s="19"/>
+      <c r="G68" s="19"/>
+      <c r="H68" s="70" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="69" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="20"/>
-      <c r="B69" s="22"/>
-      <c r="C69" s="22"/>
-      <c r="D69" s="22"/>
-      <c r="E69" s="22"/>
-      <c r="F69" s="22"/>
-      <c r="G69" s="22"/>
-      <c r="H69" s="66" t="s">
-        <v>74</v>
+      <c r="A69" s="21"/>
+      <c r="B69" s="23"/>
+      <c r="C69" s="23"/>
+      <c r="D69" s="23"/>
+      <c r="E69" s="23"/>
+      <c r="F69" s="23"/>
+      <c r="G69" s="23"/>
+      <c r="H69" s="71" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A70" s="32" t="s">
-        <v>93</v>
+      <c r="A70" s="33" t="s">
+        <v>97</v>
       </c>
       <c r="B70" s="1"/>
       <c r="C70" s="1" t="s">
@@ -7581,28 +7027,28 @@
         <v>18</v>
       </c>
       <c r="G70" s="1"/>
-      <c r="H70" s="25"/>
+      <c r="H70" s="26"/>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A71" s="24"/>
+      <c r="A71" s="25"/>
       <c r="B71" s="1"/>
       <c r="C71" s="1" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="F71" s="58" t="s">
-        <v>150</v>
+        <v>100</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>101</v>
       </c>
       <c r="G71" s="1"/>
-      <c r="H71" s="25"/>
+      <c r="H71" s="26"/>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A72" s="24"/>
+      <c r="A72" s="25"/>
       <c r="B72" s="1"/>
       <c r="C72" s="1"/>
       <c r="D72" s="2" t="s">
@@ -7611,240 +7057,240 @@
       <c r="E72" s="1"/>
       <c r="F72" s="1"/>
       <c r="G72" s="1"/>
-      <c r="H72" s="25"/>
+      <c r="H72" s="26"/>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A73" s="24"/>
+      <c r="A73" s="25"/>
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
       <c r="D73" s="1" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="E73" s="1"/>
       <c r="F73" s="1"/>
       <c r="G73" s="1"/>
-      <c r="H73" s="25"/>
+      <c r="H73" s="26"/>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A74" s="24"/>
+      <c r="A74" s="25"/>
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
-      <c r="D74" s="44" t="s">
+      <c r="D74" s="45" t="s">
         <v>15</v>
       </c>
       <c r="E74" s="1"/>
       <c r="F74" s="1"/>
       <c r="G74" s="1"/>
-      <c r="H74" s="25"/>
+      <c r="H74" s="26"/>
     </row>
     <row r="75" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="20"/>
-      <c r="B75" s="22"/>
-      <c r="C75" s="22"/>
-      <c r="D75" s="42" t="s">
-        <v>98</v>
-      </c>
-      <c r="E75" s="22"/>
-      <c r="F75" s="22"/>
-      <c r="G75" s="22"/>
-      <c r="H75" s="23"/>
+      <c r="A75" s="21"/>
+      <c r="B75" s="23"/>
+      <c r="C75" s="23"/>
+      <c r="D75" s="43" t="s">
+        <v>103</v>
+      </c>
+      <c r="E75" s="23"/>
+      <c r="F75" s="23"/>
+      <c r="G75" s="23"/>
+      <c r="H75" s="24"/>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A76" s="16" t="s">
-        <v>99</v>
-      </c>
-      <c r="B76" s="18"/>
-      <c r="C76" s="18"/>
-      <c r="D76" s="18"/>
-      <c r="E76" s="18"/>
-      <c r="F76" s="18"/>
-      <c r="G76" s="51" t="s">
-        <v>71</v>
-      </c>
-      <c r="H76" s="65" t="s">
-        <v>71</v>
+      <c r="A76" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="B76" s="19"/>
+      <c r="C76" s="19"/>
+      <c r="D76" s="19"/>
+      <c r="E76" s="19"/>
+      <c r="F76" s="19"/>
+      <c r="G76" s="52" t="s">
+        <v>75</v>
+      </c>
+      <c r="H76" s="70" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A77" s="24"/>
+      <c r="A77" s="25"/>
       <c r="B77" s="1"/>
       <c r="C77" s="1"/>
       <c r="D77" s="1"/>
       <c r="E77" s="1"/>
       <c r="F77" s="1"/>
-      <c r="G77" s="52" t="s">
-        <v>100</v>
-      </c>
-      <c r="H77" s="68" t="s">
-        <v>101</v>
+      <c r="G77" s="53" t="s">
+        <v>105</v>
+      </c>
+      <c r="H77" s="73" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A78" s="24"/>
+      <c r="A78" s="25"/>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
       <c r="D78" s="1"/>
       <c r="E78" s="1"/>
       <c r="F78" s="1"/>
-      <c r="G78" s="45" t="s">
-        <v>56</v>
-      </c>
-      <c r="H78" s="67" t="s">
-        <v>71</v>
+      <c r="G78" s="46" t="s">
+        <v>58</v>
+      </c>
+      <c r="H78" s="72" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A79" s="24"/>
+      <c r="A79" s="25"/>
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
       <c r="D79" s="1"/>
       <c r="E79" s="1"/>
       <c r="F79" s="1"/>
-      <c r="G79" s="46" t="s">
-        <v>83</v>
-      </c>
-      <c r="H79" s="68" t="s">
-        <v>102</v>
+      <c r="G79" s="47" t="s">
+        <v>87</v>
+      </c>
+      <c r="H79" s="73" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A80" s="24"/>
+      <c r="A80" s="25"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
       <c r="D80" s="1"/>
       <c r="E80" s="1"/>
       <c r="F80" s="1"/>
-      <c r="G80" s="46"/>
-      <c r="H80" s="67" t="s">
-        <v>103</v>
+      <c r="G80" s="47"/>
+      <c r="H80" s="72" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A81" s="24"/>
+      <c r="A81" s="25"/>
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
       <c r="D81" s="1"/>
       <c r="E81" s="1"/>
       <c r="F81" s="1"/>
-      <c r="G81" s="46"/>
-      <c r="H81" s="68" t="s">
-        <v>104</v>
+      <c r="G81" s="47"/>
+      <c r="H81" s="73" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A82" s="24"/>
+      <c r="A82" s="25"/>
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
       <c r="D82" s="1"/>
       <c r="E82" s="1"/>
       <c r="F82" s="1"/>
-      <c r="G82" s="46"/>
-      <c r="H82" s="31" t="s">
+      <c r="G82" s="47"/>
+      <c r="H82" s="32" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="83" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="20"/>
-      <c r="B83" s="22"/>
-      <c r="C83" s="22"/>
-      <c r="D83" s="22"/>
-      <c r="E83" s="22"/>
-      <c r="F83" s="22"/>
-      <c r="G83" s="47"/>
-      <c r="H83" s="23" t="s">
-        <v>105</v>
+      <c r="A83" s="21"/>
+      <c r="B83" s="23"/>
+      <c r="C83" s="23"/>
+      <c r="D83" s="23"/>
+      <c r="E83" s="23"/>
+      <c r="F83" s="23"/>
+      <c r="G83" s="48"/>
+      <c r="H83" s="24" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="84" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="26" t="s">
-        <v>106</v>
-      </c>
-      <c r="B84" s="27"/>
-      <c r="C84" s="28"/>
-      <c r="D84" s="28"/>
-      <c r="E84" s="28"/>
-      <c r="F84" s="28"/>
-      <c r="G84" s="28"/>
-      <c r="H84" s="29"/>
+      <c r="A84" s="27" t="s">
+        <v>111</v>
+      </c>
+      <c r="B84" s="28"/>
+      <c r="C84" s="29"/>
+      <c r="D84" s="29"/>
+      <c r="E84" s="29"/>
+      <c r="F84" s="29"/>
+      <c r="G84" s="29"/>
+      <c r="H84" s="30"/>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A85" s="16" t="s">
-        <v>107</v>
-      </c>
-      <c r="B85" s="18"/>
-      <c r="C85" s="18"/>
-      <c r="D85" s="18"/>
-      <c r="E85" s="18"/>
-      <c r="F85" s="18"/>
-      <c r="G85" s="54" t="s">
+      <c r="A85" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="B85" s="19"/>
+      <c r="C85" s="19"/>
+      <c r="D85" s="19"/>
+      <c r="E85" s="19"/>
+      <c r="F85" s="19"/>
+      <c r="G85" s="55" t="s">
         <v>12</v>
       </c>
-      <c r="H85" s="19"/>
+      <c r="H85" s="20"/>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A86" s="24"/>
+      <c r="A86" s="25"/>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
       <c r="D86" s="1"/>
       <c r="E86" s="1"/>
       <c r="F86" s="1"/>
-      <c r="G86" s="55" t="s">
+      <c r="G86" s="56" t="s">
         <v>13</v>
       </c>
-      <c r="H86" s="25"/>
+      <c r="H86" s="26"/>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A87" s="24"/>
+      <c r="A87" s="25"/>
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
       <c r="D87" s="1"/>
       <c r="E87" s="1"/>
       <c r="F87" s="1"/>
-      <c r="G87" s="56" t="s">
+      <c r="G87" s="57" t="s">
         <v>12</v>
       </c>
-      <c r="H87" s="25"/>
+      <c r="H87" s="26"/>
     </row>
     <row r="88" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="20"/>
-      <c r="B88" s="22"/>
-      <c r="C88" s="22"/>
-      <c r="D88" s="22"/>
-      <c r="E88" s="22"/>
-      <c r="F88" s="22"/>
-      <c r="G88" s="57" t="s">
+      <c r="A88" s="21"/>
+      <c r="B88" s="23"/>
+      <c r="C88" s="23"/>
+      <c r="D88" s="23"/>
+      <c r="E88" s="23"/>
+      <c r="F88" s="23"/>
+      <c r="G88" s="58" t="s">
         <v>41</v>
       </c>
-      <c r="H88" s="23"/>
+      <c r="H88" s="24"/>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A89" s="16" t="s">
-        <v>108</v>
-      </c>
-      <c r="B89" s="18"/>
-      <c r="C89" s="18"/>
-      <c r="D89" s="18"/>
-      <c r="E89" s="18"/>
-      <c r="F89" s="18"/>
-      <c r="G89" s="51" t="s">
-        <v>71</v>
-      </c>
-      <c r="H89" s="19"/>
+      <c r="A89" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="B89" s="19"/>
+      <c r="C89" s="19"/>
+      <c r="D89" s="19"/>
+      <c r="E89" s="19"/>
+      <c r="F89" s="19"/>
+      <c r="G89" s="52" t="s">
+        <v>75</v>
+      </c>
+      <c r="H89" s="20"/>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A90" s="24"/>
+      <c r="A90" s="25"/>
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
       <c r="D90" s="1"/>
       <c r="E90" s="1"/>
       <c r="F90" s="1"/>
-      <c r="G90" s="52" t="s">
+      <c r="G90" s="53" t="s">
         <v>27</v>
       </c>
-      <c r="H90" s="25"/>
+      <c r="H90" s="26"/>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A91" s="24"/>
+      <c r="A91" s="25"/>
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
       <c r="D91" s="1"/>
@@ -7853,48 +7299,48 @@
       <c r="G91" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="H91" s="25"/>
+      <c r="H91" s="26"/>
     </row>
     <row r="92" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="20"/>
-      <c r="B92" s="22"/>
-      <c r="C92" s="22"/>
-      <c r="D92" s="22"/>
-      <c r="E92" s="22"/>
-      <c r="F92" s="22"/>
-      <c r="G92" s="22" t="s">
-        <v>109</v>
-      </c>
-      <c r="H92" s="23"/>
+      <c r="A92" s="21"/>
+      <c r="B92" s="23"/>
+      <c r="C92" s="23"/>
+      <c r="D92" s="23"/>
+      <c r="E92" s="23"/>
+      <c r="F92" s="23"/>
+      <c r="G92" s="23" t="s">
+        <v>114</v>
+      </c>
+      <c r="H92" s="24"/>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A93" s="16" t="s">
-        <v>110</v>
-      </c>
-      <c r="B93" s="18"/>
-      <c r="C93" s="18"/>
-      <c r="D93" s="54" t="s">
+      <c r="A93" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="B93" s="19"/>
+      <c r="C93" s="19"/>
+      <c r="D93" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="E93" s="18"/>
-      <c r="F93" s="18"/>
-      <c r="G93" s="18"/>
-      <c r="H93" s="19"/>
+      <c r="E93" s="19"/>
+      <c r="F93" s="19"/>
+      <c r="G93" s="19"/>
+      <c r="H93" s="20"/>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A94" s="24"/>
+      <c r="A94" s="25"/>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
-      <c r="D94" s="55" t="s">
-        <v>111</v>
+      <c r="D94" s="1" t="s">
+        <v>116</v>
       </c>
       <c r="E94" s="1"/>
       <c r="F94" s="1"/>
       <c r="G94" s="1"/>
-      <c r="H94" s="25"/>
+      <c r="H94" s="26"/>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A95" s="24"/>
+      <c r="A95" s="25"/>
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
       <c r="D95" s="2" t="s">
@@ -7903,106 +7349,106 @@
       <c r="E95" s="1"/>
       <c r="F95" s="1"/>
       <c r="G95" s="1"/>
-      <c r="H95" s="25"/>
+      <c r="H95" s="26"/>
     </row>
     <row r="96" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="20"/>
-      <c r="B96" s="22"/>
-      <c r="C96" s="22"/>
-      <c r="D96" s="22" t="s">
-        <v>73</v>
-      </c>
-      <c r="E96" s="22"/>
-      <c r="F96" s="22"/>
-      <c r="G96" s="22"/>
-      <c r="H96" s="23"/>
+      <c r="A96" s="21"/>
+      <c r="B96" s="23"/>
+      <c r="C96" s="23"/>
+      <c r="D96" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="E96" s="23"/>
+      <c r="F96" s="23"/>
+      <c r="G96" s="23"/>
+      <c r="H96" s="24"/>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A97" s="16" t="s">
-        <v>112</v>
-      </c>
-      <c r="B97" s="18"/>
-      <c r="C97" s="18"/>
-      <c r="D97" s="18"/>
-      <c r="E97" s="18"/>
-      <c r="F97" s="18"/>
-      <c r="G97" s="54" t="s">
-        <v>57</v>
-      </c>
-      <c r="H97" s="65" t="s">
-        <v>71</v>
+      <c r="A97" s="17" t="s">
+        <v>117</v>
+      </c>
+      <c r="B97" s="19"/>
+      <c r="C97" s="19"/>
+      <c r="D97" s="19"/>
+      <c r="E97" s="19"/>
+      <c r="F97" s="19"/>
+      <c r="G97" s="55" t="s">
+        <v>59</v>
+      </c>
+      <c r="H97" s="70" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A98" s="24"/>
+      <c r="A98" s="25"/>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
       <c r="D98" s="1"/>
       <c r="E98" s="1"/>
       <c r="F98" s="1"/>
-      <c r="G98" s="55" t="s">
-        <v>113</v>
-      </c>
-      <c r="H98" s="68" t="s">
-        <v>100</v>
+      <c r="G98" s="56" t="s">
+        <v>118</v>
+      </c>
+      <c r="H98" s="73" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A99" s="24"/>
+      <c r="A99" s="25"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
       <c r="D99" s="1"/>
       <c r="E99" s="1"/>
       <c r="F99" s="1"/>
-      <c r="G99" s="56" t="s">
+      <c r="G99" s="57" t="s">
         <v>12</v>
       </c>
-      <c r="H99" s="68"/>
+      <c r="H99" s="73"/>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A100" s="24"/>
+      <c r="A100" s="25"/>
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
       <c r="D100" s="1"/>
       <c r="E100" s="1"/>
       <c r="F100" s="1"/>
-      <c r="G100" s="55" t="s">
-        <v>59</v>
-      </c>
-      <c r="H100" s="68"/>
+      <c r="G100" s="56" t="s">
+        <v>61</v>
+      </c>
+      <c r="H100" s="73"/>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A101" s="24"/>
+      <c r="A101" s="25"/>
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
       <c r="D101" s="1"/>
       <c r="E101" s="1"/>
       <c r="F101" s="1"/>
-      <c r="G101" s="69" t="s">
-        <v>71</v>
-      </c>
-      <c r="H101" s="68"/>
+      <c r="G101" s="74" t="s">
+        <v>75</v>
+      </c>
+      <c r="H101" s="73"/>
     </row>
     <row r="102" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="20"/>
-      <c r="B102" s="22"/>
-      <c r="C102" s="22"/>
-      <c r="D102" s="22"/>
-      <c r="E102" s="22"/>
-      <c r="F102" s="22"/>
-      <c r="G102" s="53" t="s">
-        <v>114</v>
-      </c>
-      <c r="H102" s="66"/>
+      <c r="A102" s="21"/>
+      <c r="B102" s="23"/>
+      <c r="C102" s="23"/>
+      <c r="D102" s="23"/>
+      <c r="E102" s="23"/>
+      <c r="F102" s="23"/>
+      <c r="G102" s="54" t="s">
+        <v>119</v>
+      </c>
+      <c r="H102" s="71"/>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B103" s="30"/>
-      <c r="C103" s="30"/>
-      <c r="D103" s="30"/>
-      <c r="E103" s="30"/>
-      <c r="F103" s="30"/>
-      <c r="G103" s="30"/>
-      <c r="H103" s="30"/>
+      <c r="B103" s="31"/>
+      <c r="C103" s="31"/>
+      <c r="D103" s="31"/>
+      <c r="E103" s="31"/>
+      <c r="F103" s="31"/>
+      <c r="G103" s="31"/>
+      <c r="H103" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="30">
@@ -8054,36 +7500,36 @@
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B4" s="13" t="s">
-        <v>115</v>
-      </c>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
+      <c r="B4" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B5" s="14" t="s">
-        <v>116</v>
-      </c>
-      <c r="C5" s="14"/>
-      <c r="D5" s="14"/>
-      <c r="E5" s="14"/>
+      <c r="B5" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>3</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -8224,7 +7670,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B15" s="7">
         <v>0</v>
@@ -8241,7 +7687,7 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B16" s="7">
         <v>0</v>
@@ -8258,7 +7704,7 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B17" s="7">
         <v>0</v>
@@ -8275,7 +7721,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B18" s="7">
         <v>0</v>
@@ -8292,7 +7738,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B19" s="7">
         <v>0</v>
@@ -8309,7 +7755,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B20" s="7">
         <v>0</v>
@@ -8326,7 +7772,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B21" s="7">
         <v>0</v>
@@ -8343,7 +7789,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="B22" s="7">
         <v>0</v>
@@ -8360,7 +7806,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="B23" s="7">
         <v>0</v>
@@ -8377,7 +7823,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B24" s="7">
         <v>0</v>
@@ -8394,7 +7840,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="B25" s="7">
         <v>0</v>
@@ -8411,7 +7857,7 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B26" s="7">
         <v>0</v>
@@ -8428,7 +7874,7 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="B27" s="7">
         <v>0</v>
@@ -8445,7 +7891,7 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="B28" s="7">
         <v>0</v>
@@ -8462,7 +7908,7 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="B29" s="7">
         <v>0</v>
@@ -8479,7 +7925,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="B30" s="7">
         <v>0</v>
@@ -8496,7 +7942,7 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="B31" s="7">
         <v>0</v>
@@ -8513,7 +7959,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="B32" s="7">
         <v>0</v>
@@ -8530,7 +7976,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="B33" s="7">
         <v>0</v>
@@ -8580,40 +8026,40 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B5" s="11"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
     </row>
   </sheetData>
@@ -8788,13 +8234,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{75BDC7DA-B4D0-4CE7-A2D3-CAED3C639318}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C9482BC0-D9A0-4F2E-A662-55F6A6E1E8C5}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EF543838-1174-491A-80C6-4482E4FC1CCD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DA586971-1ADE-4638-9DB3-7A0A07ABD948}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F6E19956-CE29-4840-BA4C-9F52FEF8F9B4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA842A77-17E4-4803-881D-F58312C9A224}"/>
 </file>
--- a/Plannings 2026 S26.xlsx
+++ b/Plannings 2026 S26.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="8_{A23AA2D1-9819-4B65-9C3A-D83FC30F8B22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5B285F09-A81C-42CB-AF32-5E43987A31CE}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="8_{A23AA2D1-9819-4B65-9C3A-D83FC30F8B22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B1710F38-0AC6-4914-B675-5AB1093980AC}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -171,9 +171,6 @@
     <t>17:15/19:15</t>
   </si>
   <si>
-    <t>14:15/16:45</t>
-  </si>
-  <si>
     <t>17:45/24:00</t>
   </si>
   <si>
@@ -183,9 +180,6 @@
     <t>19:15/21:15</t>
   </si>
   <si>
-    <t>16:45/18:30</t>
-  </si>
-  <si>
     <t>21:15/22:00</t>
   </si>
   <si>
@@ -321,9 +315,6 @@
     <t>09:50/18:00</t>
   </si>
   <si>
-    <t>13:15/23:00</t>
-  </si>
-  <si>
     <t>18:00/19:50</t>
   </si>
   <si>
@@ -481,6 +472,15 @@
   </si>
   <si>
     <t>18:30/24:00</t>
+  </si>
+  <si>
+    <t>13:00/23:00</t>
+  </si>
+  <si>
+    <t>17:15/18:30</t>
+  </si>
+  <si>
+    <t>14:15/17:15</t>
   </si>
 </sst>
 </file>
@@ -994,7 +994,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1231,6 +1231,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -6544,7 +6547,7 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B3" s="60" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C3" s="61"/>
       <c r="D3" s="61"/>
@@ -6555,25 +6558,25 @@
     </row>
     <row r="4" spans="1:8" s="63" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B4" s="64" t="s">
+        <v>136</v>
+      </c>
+      <c r="C4" s="64" t="s">
+        <v>137</v>
+      </c>
+      <c r="D4" s="64" t="s">
+        <v>138</v>
+      </c>
+      <c r="E4" s="64" t="s">
         <v>139</v>
       </c>
-      <c r="C4" s="64" t="s">
+      <c r="F4" s="64" t="s">
         <v>140</v>
       </c>
-      <c r="D4" s="64" t="s">
+      <c r="G4" s="64" t="s">
         <v>141</v>
       </c>
-      <c r="E4" s="64" t="s">
-        <v>142</v>
-      </c>
-      <c r="F4" s="64" t="s">
-        <v>143</v>
-      </c>
-      <c r="G4" s="64" t="s">
-        <v>144</v>
-      </c>
       <c r="H4" s="64" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -6688,10 +6691,10 @@
         <v>23</v>
       </c>
       <c r="E11" s="58" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F11" s="58" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="G11" s="58"/>
       <c r="H11" s="77"/>
@@ -6793,20 +6796,20 @@
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="24"/>
       <c r="B18" s="58" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C18" s="58" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D18" s="58" t="s">
         <v>33</v>
       </c>
       <c r="E18" s="58"/>
       <c r="F18" s="58" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="G18" s="58" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="H18" s="77"/>
     </row>
@@ -6907,7 +6910,7 @@
         <v>43</v>
       </c>
       <c r="F25" s="58" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="G25" s="1"/>
       <c r="H25" s="25"/>
@@ -6940,11 +6943,11 @@
       <c r="C27" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="D27" s="55" t="s">
+      <c r="D27" s="80" t="s">
+        <v>152</v>
+      </c>
+      <c r="E27" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>50</v>
       </c>
       <c r="F27" s="73" t="s">
         <v>44</v>
@@ -6971,13 +6974,13 @@
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="24"/>
       <c r="B29" s="55" t="s">
+        <v>50</v>
+      </c>
+      <c r="C29" s="55" t="s">
         <v>51</v>
       </c>
-      <c r="C29" s="55" t="s">
-        <v>52</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>53</v>
+      <c r="D29" s="58" t="s">
+        <v>151</v>
       </c>
       <c r="E29" s="1"/>
       <c r="F29" s="73"/>
@@ -7002,10 +7005,10 @@
       <c r="A31" s="20"/>
       <c r="B31" s="57"/>
       <c r="C31" s="22" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D31" s="57" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E31" s="22"/>
       <c r="F31" s="74"/>
@@ -7014,7 +7017,7 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="16" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B32" s="18"/>
       <c r="C32" s="18"/>
@@ -7040,16 +7043,16 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="16" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B34" s="18" t="s">
         <v>18</v>
       </c>
       <c r="C34" s="48" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D34" s="54" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E34" s="18" t="s">
         <v>18</v>
@@ -7065,23 +7068,23 @@
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="24"/>
       <c r="B35" s="58" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C35" s="46" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D35" s="55" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E35" s="58" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="F35" s="1"/>
       <c r="G35" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="H35" s="25" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
@@ -7105,14 +7108,14 @@
       <c r="B37" s="1"/>
       <c r="C37" s="46"/>
       <c r="D37" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E37" s="43" t="s">
         <v>36</v>
       </c>
       <c r="F37" s="1"/>
       <c r="G37" s="43" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="H37" s="25"/>
     </row>
@@ -7121,7 +7124,7 @@
       <c r="B38" s="1"/>
       <c r="C38" s="46"/>
       <c r="D38" s="56" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E38" s="43"/>
       <c r="F38" s="1"/>
@@ -7135,7 +7138,7 @@
       <c r="B39" s="1"/>
       <c r="C39" s="46"/>
       <c r="D39" s="55" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E39" s="43"/>
       <c r="F39" s="1"/>
@@ -7149,12 +7152,12 @@
       <c r="B40" s="1"/>
       <c r="C40" s="46"/>
       <c r="D40" s="44" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E40" s="43"/>
       <c r="F40" s="1"/>
       <c r="G40" s="45" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="H40" s="25"/>
     </row>
@@ -7163,18 +7166,18 @@
       <c r="B41" s="22"/>
       <c r="C41" s="47"/>
       <c r="D41" s="42" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E41" s="42"/>
       <c r="F41" s="22"/>
       <c r="G41" s="47" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="H41" s="23"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="32" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
@@ -7192,7 +7195,7 @@
       <c r="C43" s="22"/>
       <c r="D43" s="22"/>
       <c r="E43" s="59" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="F43" s="22"/>
       <c r="G43" s="22"/>
@@ -7200,10 +7203,10 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="16" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B44" s="49" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C44" s="18"/>
       <c r="D44" s="18" t="s">
@@ -7212,30 +7215,30 @@
       <c r="E44" s="18"/>
       <c r="F44" s="18"/>
       <c r="G44" s="51" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="H44" s="19"/>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="24"/>
       <c r="B45" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C45" s="1"/>
       <c r="D45" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E45" s="1"/>
       <c r="F45" s="1"/>
       <c r="G45" s="52" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H45" s="25"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="24"/>
       <c r="B46" s="50" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
@@ -7247,7 +7250,7 @@
     <row r="47" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="20"/>
       <c r="B47" s="22" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C47" s="22"/>
       <c r="D47" s="22"/>
@@ -7258,7 +7261,7 @@
     </row>
     <row r="48" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="26" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B48" s="27"/>
       <c r="C48" s="28"/>
@@ -7270,7 +7273,7 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="16" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B49" s="18" t="s">
         <v>18</v>
@@ -7291,24 +7294,24 @@
     <row r="50" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="20"/>
       <c r="B50" s="59" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C50" s="22" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D50" s="22"/>
       <c r="E50" s="22"/>
       <c r="F50" s="22" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G50" s="22"/>
       <c r="H50" s="23" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="16" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B51" s="18"/>
       <c r="C51" s="18"/>
@@ -7317,7 +7320,7 @@
       <c r="F51" s="18"/>
       <c r="G51" s="18"/>
       <c r="H51" s="65" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -7329,12 +7332,12 @@
       <c r="F52" s="22"/>
       <c r="G52" s="22"/>
       <c r="H52" s="66" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="33" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B53" s="34"/>
       <c r="C53" s="35"/>
@@ -7346,19 +7349,19 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="16" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B54" s="18"/>
       <c r="C54" s="48" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D54" s="41" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E54" s="18"/>
       <c r="F54" s="18"/>
       <c r="G54" s="48" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H54" s="19"/>
     </row>
@@ -7366,21 +7369,21 @@
       <c r="A55" s="20"/>
       <c r="B55" s="22"/>
       <c r="C55" s="47" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D55" s="42" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E55" s="22"/>
       <c r="F55" s="22"/>
       <c r="G55" s="47" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H55" s="23"/>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="16" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B56" s="18"/>
       <c r="C56" s="18"/>
@@ -7388,7 +7391,7 @@
       <c r="E56" s="18"/>
       <c r="F56" s="18"/>
       <c r="G56" s="51" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="H56" s="19" t="s">
         <v>18</v>
@@ -7402,10 +7405,10 @@
       <c r="E57" s="1"/>
       <c r="F57" s="1"/>
       <c r="G57" s="52" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H57" s="25" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
@@ -7419,7 +7422,7 @@
         <v>18</v>
       </c>
       <c r="H58" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
@@ -7430,10 +7433,10 @@
       <c r="E59" s="1"/>
       <c r="F59" s="1"/>
       <c r="G59" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H59" s="68" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
@@ -7457,7 +7460,7 @@
       <c r="F61" s="1"/>
       <c r="G61" s="1"/>
       <c r="H61" s="25" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
@@ -7481,7 +7484,7 @@
       <c r="F63" s="1"/>
       <c r="G63" s="1"/>
       <c r="H63" s="25" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
@@ -7493,7 +7496,7 @@
       <c r="F64" s="1"/>
       <c r="G64" s="1"/>
       <c r="H64" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="65" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -7505,17 +7508,17 @@
       <c r="F65" s="22"/>
       <c r="G65" s="22"/>
       <c r="H65" s="66" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" s="16" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B66" s="18"/>
       <c r="C66" s="18"/>
       <c r="D66" s="41" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E66" s="18"/>
       <c r="F66" s="18"/>
@@ -7527,7 +7530,7 @@
       <c r="B67" s="22"/>
       <c r="C67" s="22"/>
       <c r="D67" s="42" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E67" s="22"/>
       <c r="F67" s="22"/>
@@ -7536,7 +7539,7 @@
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" s="16" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B68" s="18"/>
       <c r="C68" s="18"/>
@@ -7545,7 +7548,7 @@
       <c r="F68" s="18"/>
       <c r="G68" s="18"/>
       <c r="H68" s="65" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="69" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -7557,12 +7560,12 @@
       <c r="F69" s="22"/>
       <c r="G69" s="22"/>
       <c r="H69" s="66" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" s="32" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B70" s="1"/>
       <c r="C70" s="1" t="s">
@@ -7584,16 +7587,16 @@
       <c r="A71" s="24"/>
       <c r="B71" s="1"/>
       <c r="C71" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E71" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="D71" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="E71" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="F71" s="1" t="s">
-        <v>99</v>
+      <c r="F71" s="58" t="s">
+        <v>150</v>
       </c>
       <c r="G71" s="1"/>
       <c r="H71" s="25"/>
@@ -7615,7 +7618,7 @@
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
       <c r="D73" s="1" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E73" s="1"/>
       <c r="F73" s="1"/>
@@ -7639,7 +7642,7 @@
       <c r="B75" s="22"/>
       <c r="C75" s="22"/>
       <c r="D75" s="42" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E75" s="22"/>
       <c r="F75" s="22"/>
@@ -7648,7 +7651,7 @@
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" s="16" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B76" s="18"/>
       <c r="C76" s="18"/>
@@ -7656,10 +7659,10 @@
       <c r="E76" s="18"/>
       <c r="F76" s="18"/>
       <c r="G76" s="51" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="H76" s="65" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
@@ -7670,10 +7673,10 @@
       <c r="E77" s="1"/>
       <c r="F77" s="1"/>
       <c r="G77" s="52" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="H77" s="68" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
@@ -7684,10 +7687,10 @@
       <c r="E78" s="1"/>
       <c r="F78" s="1"/>
       <c r="G78" s="45" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H78" s="67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
@@ -7698,10 +7701,10 @@
       <c r="E79" s="1"/>
       <c r="F79" s="1"/>
       <c r="G79" s="46" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H79" s="68" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
@@ -7713,7 +7716,7 @@
       <c r="F80" s="1"/>
       <c r="G80" s="46"/>
       <c r="H80" s="67" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
@@ -7725,7 +7728,7 @@
       <c r="F81" s="1"/>
       <c r="G81" s="46"/>
       <c r="H81" s="68" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
@@ -7749,12 +7752,12 @@
       <c r="F83" s="22"/>
       <c r="G83" s="47"/>
       <c r="H83" s="23" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="84" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="26" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B84" s="27"/>
       <c r="C84" s="28"/>
@@ -7766,7 +7769,7 @@
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" s="16" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B85" s="18"/>
       <c r="C85" s="18"/>
@@ -7816,7 +7819,7 @@
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" s="16" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B89" s="18"/>
       <c r="C89" s="18"/>
@@ -7824,7 +7827,7 @@
       <c r="E89" s="18"/>
       <c r="F89" s="18"/>
       <c r="G89" s="51" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="H89" s="19"/>
     </row>
@@ -7860,17 +7863,17 @@
       <c r="E92" s="22"/>
       <c r="F92" s="22"/>
       <c r="G92" s="22" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="H92" s="23"/>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" s="16" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B93" s="18"/>
       <c r="C93" s="18"/>
-      <c r="D93" s="18" t="s">
+      <c r="D93" s="54" t="s">
         <v>39</v>
       </c>
       <c r="E93" s="18"/>
@@ -7882,8 +7885,8 @@
       <c r="A94" s="24"/>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
-      <c r="D94" s="1" t="s">
-        <v>114</v>
+      <c r="D94" s="55" t="s">
+        <v>111</v>
       </c>
       <c r="E94" s="1"/>
       <c r="F94" s="1"/>
@@ -7907,7 +7910,7 @@
       <c r="B96" s="22"/>
       <c r="C96" s="22"/>
       <c r="D96" s="22" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E96" s="22"/>
       <c r="F96" s="22"/>
@@ -7916,7 +7919,7 @@
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" s="16" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B97" s="18"/>
       <c r="C97" s="18"/>
@@ -7924,10 +7927,10 @@
       <c r="E97" s="18"/>
       <c r="F97" s="18"/>
       <c r="G97" s="54" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="H97" s="65" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
@@ -7938,10 +7941,10 @@
       <c r="E98" s="1"/>
       <c r="F98" s="1"/>
       <c r="G98" s="55" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="H98" s="68" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
@@ -7964,7 +7967,7 @@
       <c r="E100" s="1"/>
       <c r="F100" s="1"/>
       <c r="G100" s="55" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H100" s="68"/>
     </row>
@@ -7976,7 +7979,7 @@
       <c r="E101" s="1"/>
       <c r="F101" s="1"/>
       <c r="G101" s="69" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="H101" s="68"/>
     </row>
@@ -7988,7 +7991,7 @@
       <c r="E102" s="22"/>
       <c r="F102" s="22"/>
       <c r="G102" s="53" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="H102" s="66"/>
     </row>
@@ -8052,7 +8055,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B4" s="13" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C4" s="13"/>
       <c r="D4" s="13"/>
@@ -8060,7 +8063,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B5" s="14" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C5" s="14"/>
       <c r="D5" s="14"/>
@@ -8071,16 +8074,16 @@
         <v>3</v>
       </c>
       <c r="B6" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="E6" s="6" t="s">
         <v>120</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -8221,7 +8224,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B15" s="7">
         <v>0</v>
@@ -8238,7 +8241,7 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B16" s="7">
         <v>0</v>
@@ -8255,7 +8258,7 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B17" s="7">
         <v>0</v>
@@ -8272,7 +8275,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B18" s="7">
         <v>0</v>
@@ -8289,7 +8292,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B19" s="7">
         <v>0</v>
@@ -8306,7 +8309,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B20" s="7">
         <v>0</v>
@@ -8323,7 +8326,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B21" s="7">
         <v>0</v>
@@ -8340,7 +8343,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B22" s="7">
         <v>0</v>
@@ -8357,7 +8360,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B23" s="7">
         <v>0</v>
@@ -8374,7 +8377,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B24" s="7">
         <v>0</v>
@@ -8391,7 +8394,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B25" s="7">
         <v>0</v>
@@ -8408,7 +8411,7 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B26" s="7">
         <v>0</v>
@@ -8425,7 +8428,7 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B27" s="7">
         <v>0</v>
@@ -8442,7 +8445,7 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B28" s="7">
         <v>0</v>
@@ -8459,7 +8462,7 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B29" s="7">
         <v>0</v>
@@ -8476,7 +8479,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B30" s="7">
         <v>0</v>
@@ -8493,7 +8496,7 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B31" s="7">
         <v>0</v>
@@ -8510,7 +8513,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B32" s="7">
         <v>0</v>
@@ -8527,7 +8530,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B33" s="7">
         <v>0</v>
@@ -8577,40 +8580,40 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B5" s="11"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
   </sheetData>
@@ -8785,13 +8788,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{237B6F2F-DDC0-43CB-AD4A-7D13B3C1AC2A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{75BDC7DA-B4D0-4CE7-A2D3-CAED3C639318}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{79ADD44D-1503-49B4-97A7-4450ECE9CCBB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EF543838-1174-491A-80C6-4482E4FC1CCD}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74364E4E-0E00-4523-B096-2A8C621F84C3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F6E19956-CE29-4840-BA4C-9F52FEF8F9B4}"/>
 </file>